--- a/GYMS/hobiday_gym_photo_tracker_2026-08-28.xlsx
+++ b/GYMS/hobiday_gym_photo_tracker_2026-08-28.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실사용_FINAL_요약" sheetId="1" r:id="R562cefa8a4bc474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOBIDAY_실사용_암장" sheetId="2" r:id="Rbde92ae65dd04b01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claude_Code_Import" sheetId="3" r:id="R72c323fb1df448ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사진수집_큐" sheetId="4" r:id="R50e2dd0d22314ec0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외_참고" sheetId="5" r:id="Re8423f429c53402e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지역커버리지" sheetId="6" r:id="R7deab21e94644e98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대표사진_매핑" sheetId="7" r:id="Rfd0b5337b3054788"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실사용_FINAL_요약" sheetId="1" r:id="R4e5909d1939c4ff8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOBIDAY_실사용_암장" sheetId="2" r:id="Rfbdb2b9f8e444bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claude_Code_Import" sheetId="3" r:id="R0b97650fc59a44ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사진수집_큐" sheetId="4" r:id="R144eba390d424e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제외_참고" sheetId="5" r:id="R21e94e98bd634c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지역커버리지" sheetId="6" r:id="Rdee77cad75ea4864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대표사진_매핑" sheetId="7" r:id="R080df892d8de44b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="0.0%"/>
+    <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -63,7 +64,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -110,6 +111,16 @@
         <x:fgColor rgb="FFDCEEFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F2937"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5E7EB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -118,7 +129,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="68">
+  <x:cellXfs count="91">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -275,11 +286,68 @@
     <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="8">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -309,6 +377,48 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF991B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF6B7280"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF3F4F6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -11225,7 +11335,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R784a79a366e94d97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26c1badc4413460a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18301,7 +18411,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf25b93c66b8f42ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb84adae46df24d3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25383,7 +25493,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb293d20e40a849fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R194911710a804903"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26508,7 +26618,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9885d8095f6d4693"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4d95a3655624d36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27227,7 +27337,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62235638fc544939"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac78d55ddd746c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27236,3851 +27346,5066 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="3" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="63" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="71" t="str">
         <x:v>photo_priority</x:v>
       </x:c>
-      <x:c r="B1" s="63" t="str">
+      <x:c r="B1" s="71" t="str">
         <x:v>gym_code</x:v>
       </x:c>
-      <x:c r="C1" s="63" t="str">
+      <x:c r="C1" s="71" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="D1" s="63" t="str">
+      <x:c r="D1" s="71" t="str">
         <x:v>photo_status</x:v>
       </x:c>
-      <x:c r="E1" s="63" t="str">
+      <x:c r="E1" s="71" t="str">
         <x:v>photo_url</x:v>
       </x:c>
-      <x:c r="F1" s="63" t="str">
+      <x:c r="F1" s="71" t="str">
         <x:v>source_page_url</x:v>
       </x:c>
-      <x:c r="G1" s="63" t="str">
+      <x:c r="G1" s="71" t="str">
         <x:v>notes</x:v>
       </x:c>
-      <x:c r="I1" s="65" t="str">
-        <x:v>진행 현황</x:v>
-      </x:c>
-      <x:c r="J1" s="65" t="str">
+      <x:c r="H1" s="81"/>
+      <x:c r="I1" s="75" t="str">
+        <x:v>진척 현황</x:v>
+      </x:c>
+      <x:c r="J1" s="75" t="str">
         <x:v>값</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="19" t="str">
+      <x:c r="A2" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B2" s="19" t="str">
+      <x:c r="B2" s="82" t="str">
         <x:v>HBD-GYM-0001</x:v>
       </x:c>
-      <x:c r="C2" s="19" t="str">
+      <x:c r="C2" s="82" t="str">
         <x:v>강남클라이밍</x:v>
       </x:c>
-      <x:c r="D2" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E2" s="19" t="str"/>
-      <x:c r="F2" s="19" t="str"/>
-      <x:c r="G2" s="19" t="str"/>
-      <x:c r="I2" s="66" t="str">
+      <x:c r="D2" s="82" t="str">
+        <x:v>운영재검증</x:v>
+      </x:c>
+      <x:c r="E2" s="82" t="str">
+        <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEi4G8rLCZP-1Aw_RBCdi4xHHgoE65Vh_8wfNrkeFq2VBxWK7iazFwL64yOAnd76WX378yxlNAbGzhuUCUqsOnHLUU3pAhA6KPdQ2TiZdG_X2WD9ZZGI9QtZ6nZosbqFSddLUw7igWL23GX2/s320/Gangnam%2BSports%2BClimbing%2B%28%E1%84%80%E1%85%A1%E1%86%BC%E1%84%82%E1%85%A1%E1%86%B7%2B%E1%84%8F%E1%85%B3%E1%86%AF%E1%84%85%E1%85%A1%E1%84%8B%E1%85%B5%E1%84%86%E1%85%B5%E1%86%BC%2B%E1%84%8C%E1%85%B5%E1%86%B7%29.jpg</x:v>
+      </x:c>
+      <x:c r="F2" s="82" t="str">
+        <x:v>https://koreaclimbing.blogspot.com/2018/05/blog-post_685.html</x:v>
+      </x:c>
+      <x:c r="G2" s="82" t="str">
+        <x:v>주소 일치 과거 지점 이미지 · 현재 운영상태는 재검증 필요</x:v>
+      </x:c>
+      <x:c r="H2" s="81"/>
+      <x:c r="I2" s="80" t="str">
         <x:v>전체 암장</x:v>
       </x:c>
-      <x:c r="J2" t="n">
+      <x:c r="J2" s="88" t="n">
         <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="19" t="str">
+      <x:c r="A3" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B3" s="19" t="str">
+      <x:c r="B3" s="82" t="str">
         <x:v>HBD-GYM-0002</x:v>
       </x:c>
-      <x:c r="C3" s="19" t="str">
+      <x:c r="C3" s="82" t="str">
         <x:v>더클라임 강남점</x:v>
       </x:c>
-      <x:c r="D3" s="19" t="str">
+      <x:c r="D3" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E3" s="19" t="str">
+      <x:c r="E3" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/KuRJ4FTe6dgxqo0DjzQgkMFMOSkZPwJdk7HCy3tZIxJuChxqJPmQFBcySluwSfm0qlHGkWDv7rr-xW2wJQ6gPXj0aVpK115wV7gIy8RkUQjW8pL6KfsZ2cii9ShJEOstQBaaIQplDKboIKziyluyNMIXpmR53235n9u7cSRewwqfncq-NYfCupHQAkSBZtJ4?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F3" s="19" t="str"/>
-      <x:c r="G3" s="19" t="str"/>
-      <x:c r="I3" s="66" t="str">
-        <x:v>사진 매핑</x:v>
-      </x:c>
-      <x:c r="J3" t="n">
-        <x:v>84</x:v>
+      <x:c r="F3" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/gangnam</x:v>
+      </x:c>
+      <x:c r="G3" s="82" t="str"/>
+      <x:c r="H3" s="81"/>
+      <x:c r="I3" s="80" t="str">
+        <x:v>출처/상태 매핑</x:v>
+      </x:c>
+      <x:c r="J3" s="88" t="n">
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="19" t="str">
+      <x:c r="A4" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B4" s="19" t="str">
+      <x:c r="B4" s="82" t="str">
         <x:v>HBD-GYM-0003</x:v>
       </x:c>
-      <x:c r="C4" s="19" t="str">
+      <x:c r="C4" s="82" t="str">
         <x:v>더클라임 신사점</x:v>
       </x:c>
-      <x:c r="D4" s="19" t="str">
+      <x:c r="D4" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E4" s="19" t="str">
+      <x:c r="E4" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/BseAW/btsCwbSkiUW/AAAAAAAAAAAAAAAAAAAAABkxGssduaBuuSaGJmQw6LNd70hPKma1585IbeTFcFSg/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=07SjvBRqaMPNaTH8EnlkPZczGDc%3D</x:v>
       </x:c>
-      <x:c r="F4" s="19" t="str">
+      <x:c r="F4" s="82" t="str">
         <x:v>https://skewed.tistory.com/75</x:v>
       </x:c>
-      <x:c r="G4" s="19" t="str">
+      <x:c r="G4" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
-      <x:c r="I4" s="66" t="str">
-        <x:v>잔여</x:v>
-      </x:c>
-      <x:c r="J4" t="n">
+      <x:c r="H4" s="81"/>
+      <x:c r="I4" s="80" t="str">
+        <x:v>직접 대표사진 URL</x:v>
+      </x:c>
+      <x:c r="J4" s="88" t="n">
         <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="19" t="str">
+      <x:c r="A5" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B5" s="19" t="str">
+      <x:c r="B5" s="82" t="str">
         <x:v>HBD-GYM-0004</x:v>
       </x:c>
-      <x:c r="C5" s="19" t="str">
+      <x:c r="C5" s="82" t="str">
         <x:v>더클라임 양재점</x:v>
       </x:c>
-      <x:c r="D5" s="19" t="str">
+      <x:c r="D5" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E5" s="19" t="str">
+      <x:c r="E5" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/MYg0R/btrBZy65eud/AAAAAAAAAAAAAAAAAAAAADifjNF3Qt4T4xixM77nz3kgr8omFNc7yBo5m5XfbmdF/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1767193199&amp;signature=xEjta3vocVYI3yfhg4Ci3yCxrWw%3D</x:v>
       </x:c>
-      <x:c r="F5" s="19" t="str">
+      <x:c r="F5" s="82" t="str">
         <x:v>https://blumay.tistory.com/entry/%EB%8D%94-%ED%81%B4%EB%9D%BC%EC%9E%84-%EC%96%91%EC%9E%AC-%EC%98%88%EC%81%9C-%ED%99%80%EB%93%9C%EC%99%80-%EC%9E%AC%EB%B0%8C%EB%8A%94-%EB%AC%B8%EC%A0%9C%EB%A1%9C-%EA%B0%80%EB%93%9D%ED%96%88%EB%8D%98-%EC%96%91%EC%9E%AC-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%9E%A5</x:v>
       </x:c>
-      <x:c r="G5" s="19" t="str">
+      <x:c r="G5" s="82" t="str">
         <x:v>내부 볼더링 벽</x:v>
       </x:c>
-      <x:c r="I5" s="66" t="str">
-        <x:v>진행률</x:v>
-      </x:c>
-      <x:c r="J5" s="67" t="n">
-        <x:v>0.42</x:v>
+      <x:c r="H5" s="81"/>
+      <x:c r="I5" s="80" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="J5" s="89" t="n">
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="19" t="str">
+      <x:c r="A6" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B6" s="19" t="str">
+      <x:c r="B6" s="82" t="str">
         <x:v>HBD-GYM-0005</x:v>
       </x:c>
-      <x:c r="C6" s="19" t="str">
+      <x:c r="C6" s="82" t="str">
         <x:v>무중력클라이밍</x:v>
       </x:c>
-      <x:c r="D6" s="19" t="str">
+      <x:c r="D6" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="str">
+      <x:c r="E6" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/kLciO/btsFJ3vK7MF/AAAAAAAAAAAAAAAAAAAAAD-SxcnDuZyvFF83ceKntANSQYtuxMOoHWVAn-iZGSfD/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1785509999&amp;signature=%2BjQZzYg5NfaDSLf6J4W5oNHFqTE%3D</x:v>
       </x:c>
-      <x:c r="F6" s="19" t="str">
+      <x:c r="F6" s="82" t="str">
         <x:v>https://skewed.tistory.com/85</x:v>
       </x:c>
-      <x:c r="G6" s="19" t="str">
+      <x:c r="G6" s="82" t="str">
         <x:v>볼더링 벽</x:v>
       </x:c>
+      <x:c r="H6" s="81"/>
+      <x:c r="I6" s="80" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="J6" s="88" t="n">
+        <x:v>89</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="19" t="str">
+      <x:c r="A7" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B7" s="19" t="str">
+      <x:c r="B7" s="82" t="str">
         <x:v>HBD-GYM-0006</x:v>
       </x:c>
-      <x:c r="C7" s="19" t="str">
+      <x:c r="C7" s="82" t="str">
         <x:v>역삼클라이밍랩</x:v>
       </x:c>
-      <x:c r="D7" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E7" s="19" t="str"/>
-      <x:c r="F7" s="19" t="str"/>
-      <x:c r="G7" s="19" t="str"/>
+      <x:c r="D7" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E7" s="82"/>
+      <x:c r="F7" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/gangnam</x:v>
+      </x:c>
+      <x:c r="G7" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H7" s="81"/>
+      <x:c r="I7" s="80" t="str">
+        <x:v>운영재검증</x:v>
+      </x:c>
+      <x:c r="J7" s="88" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="19" t="str">
+      <x:c r="A8" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B8" s="19" t="str">
+      <x:c r="B8" s="82" t="str">
         <x:v>HBD-GYM-0007</x:v>
       </x:c>
-      <x:c r="C8" s="19" t="str">
+      <x:c r="C8" s="82" t="str">
         <x:v>클라이밍파크 강남점</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="str">
+      <x:c r="D8" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="str">
+      <x:c r="E8" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/4H0HFwPdqgmMjmW-nn4xoFDVc7dKmXqCKnY4iDx2DY_GUyfCtl7R02mKAdBjXSUQZy87gfIHUohbHbMcDAw0dq-k07wN-TTVurHsu-NQ0s7kL6FZ-onGCHoX8rfB2AJ7Ue5h3DhtRPAKM6MA7c2AuDxydpQdbYTO1kHs4YcNtHaFWfaLd9_RnbkDmMTVlHxK?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F8" s="19" t="str"/>
-      <x:c r="G8" s="19" t="str"/>
+      <x:c r="F8" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/gangnam</x:v>
+      </x:c>
+      <x:c r="G8" s="82" t="str"/>
+      <x:c r="H8" s="81"/>
+      <x:c r="I8" s="80" t="str">
+        <x:v>미수집</x:v>
+      </x:c>
+      <x:c r="J8" s="88" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="19" t="str">
+      <x:c r="A9" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B9" s="19" t="str">
+      <x:c r="B9" s="82" t="str">
         <x:v>HBD-GYM-0008</x:v>
       </x:c>
-      <x:c r="C9" s="19" t="str">
+      <x:c r="C9" s="82" t="str">
         <x:v>클라이밍파크 신논현점</x:v>
       </x:c>
-      <x:c r="D9" s="19" t="str">
+      <x:c r="D9" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E9" s="19" t="str">
+      <x:c r="E9" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/WKEIX/btrD5SB5kiH/AAAAAAAAAAAAAAAAAAAAAOHWkhH7Rcfhlb1MB2_d6wlVeWNJs9uELeINOdOHyucg/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1774969199&amp;signature=S5HzgTgLjOSNWuitFJ2rd6I5Mfk%3D</x:v>
       </x:c>
-      <x:c r="F9" s="19" t="str">
+      <x:c r="F9" s="82" t="str">
         <x:v>https://climbtourtv.com/entry/%EC%84%9C%EC%9A%B8-%EA%B0%95%EB%82%A8-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%ED%8C%8C%ED%81%AC-%EC%95%94%EC%9E%A5%ED%88%AC%EC%96%B4</x:v>
       </x:c>
-      <x:c r="G9" s="19" t="str">
+      <x:c r="G9" s="82" t="str">
         <x:v>신논현점 볼더링 벽</x:v>
       </x:c>
+      <x:c r="H9" s="81"/>
+      <x:c r="I9" s="80" t="str">
+        <x:v>출처 연결률</x:v>
+      </x:c>
+      <x:c r="J9" s="90" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="19" t="str">
+      <x:c r="A10" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B10" s="19" t="str">
+      <x:c r="B10" s="82" t="str">
         <x:v>HBD-GYM-0009</x:v>
       </x:c>
-      <x:c r="C10" s="19" t="str">
+      <x:c r="C10" s="82" t="str">
         <x:v>클라이밍파크 한티점</x:v>
       </x:c>
-      <x:c r="D10" s="19" t="str">
+      <x:c r="D10" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E10" s="19" t="str">
+      <x:c r="E10" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/ec2eIp/btrIOwiBq7k/AAAAAAAAAAAAAAAAAAAAAOjtUl3zJ4jON56NOJTMHmcYsA2fJ42FzYQ9Va4ae8sp/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=%2Bm3HdmK9gC5SV71BZ%2BmhKq5M4Zg%3D</x:v>
       </x:c>
-      <x:c r="F10" s="19" t="str">
+      <x:c r="F10" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%ED%95%9C%ED%8B%B0%EC%97%AD-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%ED%8C%8C%ED%81%AC</x:v>
       </x:c>
-      <x:c r="G10" s="19" t="str">
+      <x:c r="G10" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H10" s="81"/>
+      <x:c r="I10" s="80" t="str">
+        <x:v>사진 URL 확보율</x:v>
+      </x:c>
+      <x:c r="J10" s="90" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="19" t="str">
+      <x:c r="A11" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B11" s="19" t="str">
+      <x:c r="B11" s="82" t="str">
         <x:v>HBD-GYM-0010</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="str">
+      <x:c r="C11" s="82" t="str">
         <x:v>클라임이모션</x:v>
       </x:c>
-      <x:c r="D11" s="19" t="str">
+      <x:c r="D11" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E11" s="19" t="str">
+      <x:c r="E11" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/dmH0fI/btsq2kyoOk2/AAAAAAAAAAAAAAAAAAAAAIMeeaWTJLNBEhPH65ngjezcBpiMLso2bvhdy2VmQFqV/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1782831599&amp;signature=voHx4zV0Np7pCaOG%2BhsG%2FUqT%2FNI%3D</x:v>
       </x:c>
-      <x:c r="F11" s="19" t="str">
+      <x:c r="F11" s="82" t="str">
         <x:v>https://than-today.tistory.com/5</x:v>
       </x:c>
-      <x:c r="G11" s="19" t="str">
+      <x:c r="G11" s="82" t="str">
         <x:v>오버행/지구력 벽</x:v>
       </x:c>
+      <x:c r="H11" s="81"/>
+      <x:c r="I11" s="81"/>
+      <x:c r="J11" s="81"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="19" t="str">
+      <x:c r="A12" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B12" s="19" t="str">
+      <x:c r="B12" s="82" t="str">
         <x:v>HBD-GYM-0011</x:v>
       </x:c>
-      <x:c r="C12" s="19" t="str">
+      <x:c r="C12" s="82" t="str">
         <x:v>강동클라이밍짐</x:v>
       </x:c>
-      <x:c r="D12" s="19" t="str">
+      <x:c r="D12" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E12" s="19" t="str">
+      <x:c r="E12" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/AuQ3t/btsMaPqeouL/AAAAAAAAAAAAAAAAAAAAAPL4NTkVLiHRM-EK8Vp5TJ9m-j__1YoB8mg8BiwD-x05/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1780239599&amp;signature=HeXeS1T0epndCRrJQX5VmHSas94%3D</x:v>
       </x:c>
-      <x:c r="F12" s="19" t="str">
+      <x:c r="F12" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EA%B0%95%EB%8F%99%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90-%EB%8F%84%EC%8B%AC-%EC%86%8D-%EC%95%94%EB%B2%BD-%EC%A0%95%EB%B3%B5%EC%9D%98-%EC%8B%9C%EC%9E%91</x:v>
       </x:c>
-      <x:c r="G12" s="19" t="str">
+      <x:c r="G12" s="82" t="str">
         <x:v>내부 클라이밍 벽</x:v>
       </x:c>
+      <x:c r="H12" s="81"/>
+      <x:c r="I12" s="81"/>
+      <x:c r="J12" s="81"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="19" t="str">
+      <x:c r="A13" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B13" s="19" t="str">
+      <x:c r="B13" s="82" t="str">
         <x:v>HBD-GYM-0012</x:v>
       </x:c>
-      <x:c r="C13" s="19" t="str">
+      <x:c r="C13" s="82" t="str">
         <x:v>알레 클라이밍 강동</x:v>
       </x:c>
-      <x:c r="D13" s="19" t="str">
+      <x:c r="D13" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E13" s="19" t="str">
+      <x:c r="E13" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/Yxbb2AbuAaZWZ8YL57X4VrXg5q8uGi8FRwROuZf2zcNSBNN1U4ydLbQv1_td0SRe0vpI3m8beqUNmvafif2zUT9sbWdaxHxMngVzpcehhEl1mHQoRjJ5OrI_wd7dKUbP4hio9GJg_KQV67AT23exMNcUYZ8xRfT4FPCgpsVEHgO8JT8oSfwxtk4hsYe6QjeK?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F13" s="19" t="str"/>
-      <x:c r="G13" s="19" t="str"/>
+      <x:c r="F13" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%95%8C%EB%A0%88%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EA%B0%95%EB%8F%99</x:v>
+      </x:c>
+      <x:c r="G13" s="82" t="str"/>
+      <x:c r="H13" s="81"/>
+      <x:c r="I13" s="81"/>
+      <x:c r="J13" s="81"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="19" t="str">
+      <x:c r="A14" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B14" s="19" t="str">
+      <x:c r="B14" s="82" t="str">
         <x:v>HBD-GYM-0013</x:v>
       </x:c>
-      <x:c r="C14" s="19" t="str">
+      <x:c r="C14" s="82" t="str">
         <x:v>온플릭 클라이밍 천호점</x:v>
       </x:c>
-      <x:c r="D14" s="19" t="str">
+      <x:c r="D14" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E14" s="19" t="str">
+      <x:c r="E14" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/coerlQ/btsvdoEfhwa/AAAAAAAAAAAAAAAAAAAAAEnjWbPQPFGSgc_u75mK0ZlinAgfQer2brDuzjgLEDfE/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=b1eKnpXN%2BDeyKpgs7wwCSG7x8H0%3D</x:v>
       </x:c>
-      <x:c r="F14" s="19" t="str">
+      <x:c r="F14" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EC%98%A8%ED%94%8C%EB%A6%AD</x:v>
       </x:c>
-      <x:c r="G14" s="19" t="str">
+      <x:c r="G14" s="82" t="str">
         <x:v>볼더링 벽</x:v>
       </x:c>
+      <x:c r="H14" s="81"/>
+      <x:c r="I14" s="81"/>
+      <x:c r="J14" s="81"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="19" t="str">
+      <x:c r="A15" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B15" s="19" t="str">
+      <x:c r="B15" s="82" t="str">
         <x:v>HBD-GYM-0014</x:v>
       </x:c>
-      <x:c r="C15" s="19" t="str">
+      <x:c r="C15" s="82" t="str">
         <x:v>쿠키즈클라이밍</x:v>
       </x:c>
-      <x:c r="D15" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E15" s="19" t="str"/>
-      <x:c r="F15" s="19" t="str"/>
-      <x:c r="G15" s="19" t="str"/>
+      <x:c r="D15" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E15" s="82"/>
+      <x:c r="F15" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G15" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H15" s="81"/>
+      <x:c r="I15" s="81"/>
+      <x:c r="J15" s="81"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="19" t="str">
+      <x:c r="A16" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B16" s="19" t="str">
+      <x:c r="B16" s="82" t="str">
         <x:v>HBD-GYM-0015</x:v>
       </x:c>
-      <x:c r="C16" s="19" t="str">
+      <x:c r="C16" s="82" t="str">
         <x:v>락랜드</x:v>
       </x:c>
-      <x:c r="D16" s="19" t="str">
+      <x:c r="D16" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E16" s="19" t="str">
+      <x:c r="E16" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dn/upkcT/btsL76eBgH9/RtQtvFzuGdr0KSumYi1NU0/img.jpg</x:v>
       </x:c>
-      <x:c r="F16" s="19" t="str">
+      <x:c r="F16" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EC%84%9C%EC%9A%B8-%EA%B0%95%EB%B6%81%EA%B5%AC%EC%97%90%EC%84%9C-%EA%B0%80%EC%9E%A5-%EC%A7%9C%EB%A6%BF%ED%95%9C-%EB%8F%84%EC%A0%84-%EB%9D%BD%EB%9E%9C%EB%93%9C-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90-%EC%99%84%EC%A0%84-%EB%B6%84%EC%84%9D</x:v>
       </x:c>
-      <x:c r="G16" s="19" t="str">
+      <x:c r="G16" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H16" s="81"/>
+      <x:c r="I16" s="81"/>
+      <x:c r="J16" s="81"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="19" t="str">
+      <x:c r="A17" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B17" s="19" t="str">
+      <x:c r="B17" s="82" t="str">
         <x:v>HBD-GYM-0016</x:v>
       </x:c>
-      <x:c r="C17" s="19" t="str">
+      <x:c r="C17" s="82" t="str">
         <x:v>강서클라이밍센터</x:v>
       </x:c>
-      <x:c r="D17" s="19" t="str">
+      <x:c r="D17" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E17" s="19" t="str">
+      <x:c r="E17" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/c06DE8/btsL53XtVwa/AAAAAAAAAAAAAAAAAAAAAGc49abcNLEMEZHfgSkk96es9FTIOHO0exeLdzJ7pkK-/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1782831599&amp;signature=ixbLkSl8NPevdwcUXoNM8uwBbCs%3D</x:v>
       </x:c>
-      <x:c r="F17" s="19" t="str">
+      <x:c r="F17" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EC%9A%B4%EB%8F%99%EA%B3%BC-%EC%9E%AC%EB%AF%B8%EB%A5%BC-%EB%8F%99%EC%8B%9C%EC%97%90-%EA%B0%95%EC%84%9C%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0%EC%97%90%EC%84%9C-%ED%95%9C%EA%B3%84%EB%A5%BC-%EB%9B%B0%EC%96%B4%EB%84%98%EB%8B%A4</x:v>
       </x:c>
-      <x:c r="G17" s="19" t="str">
+      <x:c r="G17" s="82" t="str">
         <x:v>내부 루트 전경</x:v>
       </x:c>
+      <x:c r="H17" s="81"/>
+      <x:c r="I17" s="81"/>
+      <x:c r="J17" s="81"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="19" t="str">
+      <x:c r="A18" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B18" s="19" t="str">
+      <x:c r="B18" s="82" t="str">
         <x:v>HBD-GYM-0017</x:v>
       </x:c>
-      <x:c r="C18" s="19" t="str">
+      <x:c r="C18" s="82" t="str">
         <x:v>더클라임 마곡점</x:v>
       </x:c>
-      <x:c r="D18" s="19" t="str">
+      <x:c r="D18" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E18" s="19" t="str">
+      <x:c r="E18" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/bzmsJX/btrJhzS9pZx/AAAAAAAAAAAAAAAAAAAAAPGRrabihPZxhm196rCSJf3sqWEkka23aHaLYv5-Nn7K/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1774969199&amp;signature=jVLbJdn5P%2B0oQJ7CBAfFgyXQGzc%3D</x:v>
       </x:c>
-      <x:c r="F18" s="19" t="str">
+      <x:c r="F18" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EB%A7%88%EA%B3%A1-%EB%8D%94%ED%81%B4%EB%9D%BC%EC%9E%84?category=1114083</x:v>
       </x:c>
-      <x:c r="G18" s="19" t="str">
+      <x:c r="G18" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H18" s="81"/>
+      <x:c r="I18" s="81"/>
+      <x:c r="J18" s="81"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="19" t="str">
+      <x:c r="A19" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B19" s="19" t="str">
+      <x:c r="B19" s="82" t="str">
         <x:v>HBD-GYM-0018</x:v>
       </x:c>
-      <x:c r="C19" s="19" t="str">
+      <x:c r="C19" s="82" t="str">
         <x:v>더플라스틱클라이밍 염창점</x:v>
       </x:c>
-      <x:c r="D19" s="19" t="str">
+      <x:c r="D19" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E19" s="19" t="str">
+      <x:c r="E19" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/ebTfo0/btsCZ6IepRW/AAAAAAAAAAAAAAAAAAAAANN8jsxG3Elq9f6nTZ1JLaj4AjoEcmNACsSaKFoCt5uM/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1785509999&amp;signature=qP4BUV9cHwd0i8zfYNJTon%2FVtZM%3D</x:v>
       </x:c>
-      <x:c r="F19" s="19" t="str">
+      <x:c r="F19" s="82" t="str">
         <x:v>https://ss901104.tistory.com/688</x:v>
       </x:c>
-      <x:c r="G19" s="19" t="str">
+      <x:c r="G19" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H19" s="81"/>
+      <x:c r="I19" s="81"/>
+      <x:c r="J19" s="81"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="19" t="str">
+      <x:c r="A20" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B20" s="19" t="str">
+      <x:c r="B20" s="82" t="str">
         <x:v>HBD-GYM-0019</x:v>
       </x:c>
-      <x:c r="C20" s="19" t="str">
+      <x:c r="C20" s="82" t="str">
         <x:v>어거스트 클라이밍 가양점</x:v>
       </x:c>
-      <x:c r="D20" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E20" s="19" t="str"/>
-      <x:c r="F20" s="19" t="str"/>
-      <x:c r="G20" s="19" t="str"/>
+      <x:c r="D20" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E20" s="82"/>
+      <x:c r="F20" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%96%B4%EA%B1%B0%EC%8A%A4%ED%8A%B8%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EA%B0%80%EC%96%91%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G20" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H20" s="81"/>
+      <x:c r="I20" s="81"/>
+      <x:c r="J20" s="81"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="19" t="str">
+      <x:c r="A21" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B21" s="19" t="str">
+      <x:c r="B21" s="82" t="str">
         <x:v>HBD-GYM-0020</x:v>
       </x:c>
-      <x:c r="C21" s="19" t="str">
+      <x:c r="C21" s="82" t="str">
         <x:v>클라이밍88</x:v>
       </x:c>
-      <x:c r="D21" s="19" t="str">
+      <x:c r="D21" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E21" s="19" t="str">
+      <x:c r="E21" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/4E9BgPYfn3eSMG3ZXGSAjLrSWKDN85Ie2fZLXXsZeFCWhGO_mY7Az5Bn2ZeVGHn-w20x4pRLf9cXGnxRmrn_NvPV9QVfgv3px_ISCARdTuZ132huumPrSkbt7LX-281JJ6ttxt7sGjBiFqqK8GY5B15YFlFpzVxZgdxqHLshRAglawWc4HfOkMGZyjU4FWWB?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F21" s="19" t="str"/>
-      <x:c r="G21" s="19" t="str"/>
+      <x:c r="F21" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G21" s="82" t="str"/>
+      <x:c r="H21" s="81"/>
+      <x:c r="I21" s="81"/>
+      <x:c r="J21" s="81"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="19" t="str">
+      <x:c r="A22" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B22" s="19" t="str">
+      <x:c r="B22" s="82" t="str">
         <x:v>HBD-GYM-0021</x:v>
       </x:c>
-      <x:c r="C22" s="19" t="str">
+      <x:c r="C22" s="82" t="str">
         <x:v>더클라임 사당점</x:v>
       </x:c>
-      <x:c r="D22" s="19" t="str">
+      <x:c r="D22" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E22" s="19" t="str">
+      <x:c r="E22" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/EtoQj/btsH2neyYVd/AAAAAAAAAAAAAAAAAAAAAED2BAH6iJMjfv7VeG4X2Z4USgINnptBEE9tAUhaABUl/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1774969199&amp;signature=fY798W%2BlsOb9TXMZyWYViNoSSyY%3D</x:v>
       </x:c>
-      <x:c r="F22" s="19" t="str">
+      <x:c r="F22" s="82" t="str">
         <x:v>https://jjiyo.com/entry/%EC%8B%A4%EB%82%B4-%EB%B3%BC%EB%8D%94%EB%A7%81-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%9E%A5-%EB%8D%94%ED%81%B4%EB%9D%BC%EC%9E%84-%EC%A7%80%EC%A0%90%EB%B3%84-%ED%8A%B9%EC%A7%95-1</x:v>
       </x:c>
-      <x:c r="G22" s="19" t="str">
+      <x:c r="G22" s="82" t="str">
         <x:v>사당점 볼더링 벽</x:v>
       </x:c>
+      <x:c r="H22" s="81"/>
+      <x:c r="I22" s="81"/>
+      <x:c r="J22" s="81"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="19" t="str">
+      <x:c r="A23" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B23" s="19" t="str">
+      <x:c r="B23" s="82" t="str">
         <x:v>HBD-GYM-0022</x:v>
       </x:c>
-      <x:c r="C23" s="19" t="str">
+      <x:c r="C23" s="82" t="str">
         <x:v>더클라임 서울대점</x:v>
       </x:c>
-      <x:c r="D23" s="19" t="str">
+      <x:c r="D23" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E23" s="19" t="str">
+      <x:c r="E23" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/qZrAc/btrICOPIw9W/AAAAAAAAAAAAAAAAAAAAAPYOhax1Cjdr6NFF128n7Da219WpZ1yHYYZmzXhcu2ph/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=GHPNIuuqlrK4g%2Bf9YEcoMYMGGZM%3D</x:v>
       </x:c>
-      <x:c r="F23" s="19" t="str">
+      <x:c r="F23" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EC%84%9C%EC%9A%B8%EB%8C%80-%EB%8D%94%ED%81%B4%EB%9D%BC%EC%9E%84</x:v>
       </x:c>
-      <x:c r="G23" s="19" t="str">
+      <x:c r="G23" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H23" s="81"/>
+      <x:c r="I23" s="81"/>
+      <x:c r="J23" s="81"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="19" t="str">
+      <x:c r="A24" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B24" s="19" t="str">
+      <x:c r="B24" s="82" t="str">
         <x:v>HBD-GYM-0023</x:v>
       </x:c>
-      <x:c r="C24" s="19" t="str">
+      <x:c r="C24" s="82" t="str">
         <x:v>더클라임 신림점</x:v>
       </x:c>
-      <x:c r="D24" s="19" t="str">
+      <x:c r="D24" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E24" s="19" t="str">
+      <x:c r="E24" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/EJEhB7Y0BRbUOlGkby4-tL-x8yY21KylSOcp7Xoi5u1B46l9AIEofzUMMg2HV4ixqlvjoPWgivy9le1rgsLtaMmdJbTzk28cMO4YwXKrEWZrQZTPK7mpLMc3eUd3kaYm5SXzzubltWiEu27yn-bXOqGSWpxZLDM4F5REjVxABRuPUxk053SdusK8ws6KHRa0?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F24" s="19" t="str"/>
-      <x:c r="G24" s="19" t="str"/>
+      <x:c r="F24" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G24" s="82" t="str"/>
+      <x:c r="H24" s="81"/>
+      <x:c r="I24" s="81"/>
+      <x:c r="J24" s="81"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="19" t="str">
+      <x:c r="A25" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B25" s="19" t="str">
+      <x:c r="B25" s="82" t="str">
         <x:v>HBD-GYM-0024</x:v>
       </x:c>
-      <x:c r="C25" s="19" t="str">
+      <x:c r="C25" s="82" t="str">
         <x:v>보라매스포츠클라이밍</x:v>
       </x:c>
-      <x:c r="D25" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E25" s="19" t="str"/>
-      <x:c r="F25" s="19" t="str"/>
-      <x:c r="G25" s="19" t="str"/>
+      <x:c r="D25" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E25" s="82"/>
+      <x:c r="F25" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G25" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H25" s="81"/>
+      <x:c r="I25" s="81"/>
+      <x:c r="J25" s="81"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="19" t="str">
+      <x:c r="A26" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B26" s="19" t="str">
+      <x:c r="B26" s="82" t="str">
         <x:v>HBD-GYM-0025</x:v>
       </x:c>
-      <x:c r="C26" s="19" t="str">
+      <x:c r="C26" s="82" t="str">
         <x:v>인클라이밍</x:v>
       </x:c>
-      <x:c r="D26" s="19" t="str">
+      <x:c r="D26" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E26" s="19" t="str">
+      <x:c r="E26" s="82" t="str">
         <x:v>https://img.kr.gcp-karroter.net/local_business_ugc/local_business_ugc/undefined/26676943/1756956830332/R25mQ2IyWjFLR29KdEQ4eDRLUm9H.jpeg</x:v>
       </x:c>
-      <x:c r="F26" s="19" t="str">
+      <x:c r="F26" s="82" t="str">
         <x:v>https://www.daangn.com/kr/local-profile/%EC%9D%B8%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-k7933scdki2r/</x:v>
       </x:c>
-      <x:c r="G26" s="19" t="str">
+      <x:c r="G26" s="82" t="str">
         <x:v>업체 외관/간판. 내부 전경보다 식별 우선</x:v>
       </x:c>
+      <x:c r="H26" s="81"/>
+      <x:c r="I26" s="81"/>
+      <x:c r="J26" s="81"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="19" t="str">
+      <x:c r="A27" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B27" s="19" t="str">
+      <x:c r="B27" s="82" t="str">
         <x:v>HBD-GYM-0026</x:v>
       </x:c>
-      <x:c r="C27" s="19" t="str">
+      <x:c r="C27" s="82" t="str">
         <x:v>인클라이밍센터</x:v>
       </x:c>
-      <x:c r="D27" s="19" t="str">
+      <x:c r="D27" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E27" s="19" t="str">
+      <x:c r="E27" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/Cozmh/btsL9rYh57F/AAAAAAAAAAAAAAAAAAAAAGN6cI1GLIdeHTLy5RWxWkfIhEv7qZtfCktXdhf1QCUs/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=g6ByzXf6sK%2F2GVIS23IB7Gxiaqk%3D</x:v>
       </x:c>
-      <x:c r="F27" s="19" t="str">
+      <x:c r="F27" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EC%84%9C%EC%9A%B8-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EB%AA%85%EC%86%8C-%EC%9D%B8%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0%EC%97%90%EC%84%9C-%EC%83%88%EB%A1%9C%EC%9A%B4-%EB%8F%84%EC%A0%84%EC%9D%84-%EC%8B%9C%EC%9E%91%ED%95%98%EC%84%B8%EC%9A%94</x:v>
       </x:c>
-      <x:c r="G27" s="19" t="str">
+      <x:c r="G27" s="82" t="str">
         <x:v>내부 볼더링 벽</x:v>
       </x:c>
+      <x:c r="H27" s="81"/>
+      <x:c r="I27" s="81"/>
+      <x:c r="J27" s="81"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="19" t="str">
+      <x:c r="A28" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B28" s="19" t="str">
+      <x:c r="B28" s="82" t="str">
         <x:v>HBD-GYM-0027</x:v>
       </x:c>
-      <x:c r="C28" s="19" t="str">
+      <x:c r="C28" s="82" t="str">
         <x:v>정지현클라이밍짐</x:v>
       </x:c>
-      <x:c r="D28" s="19" t="str">
+      <x:c r="D28" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E28" s="19" t="str">
+      <x:c r="E28" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/cYB4z6/btsL8bNERTF/AAAAAAAAAAAAAAAAAAAAAN0pqEdVNLT_yso6VVp65Rhafilya4AAoaY17HEukxWp/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=a0AYy2NdjoMN8pCOd0n1MTen1N8%3D</x:v>
       </x:c>
-      <x:c r="F28" s="19" t="str">
+      <x:c r="F28" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EC%84%9C%EC%9A%B8%EB%8C%80%EC%9E%85%EA%B5%AC-%EC%B5%9C%EA%B3%A0%EC%9D%98-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EB%AA%85%EC%86%8C-%EC%A0%95%EC%A7%80%ED%98%84-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90-%EC%99%84%EB%B2%BD-%EB%B6%84%EC%84%9D</x:v>
       </x:c>
-      <x:c r="G28" s="19" t="str">
+      <x:c r="G28" s="82" t="str">
         <x:v>정지현클라이밍짐 내부</x:v>
       </x:c>
+      <x:c r="H28" s="81"/>
+      <x:c r="I28" s="81"/>
+      <x:c r="J28" s="81"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="19" t="str">
+      <x:c r="A29" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B29" s="19" t="str">
+      <x:c r="B29" s="82" t="str">
         <x:v>HBD-GYM-0028</x:v>
       </x:c>
-      <x:c r="C29" s="19" t="str">
+      <x:c r="C29" s="82" t="str">
         <x:v>레드포인트클라이밍</x:v>
       </x:c>
-      <x:c r="D29" s="19" t="str">
+      <x:c r="D29" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E29" s="19" t="str">
+      <x:c r="E29" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/b021ar/btsMcJwKaH3/AAAAAAAAAAAAAAAAAAAAABB1zcfoEi1PirNBaW9tp0IdtSQiRWm9zPJxltWba_Ot/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1782831599&amp;signature=pzdHEegIcEz0JWlLF1C7IFbW4z4%3D</x:v>
       </x:c>
-      <x:c r="F29" s="19" t="str">
+      <x:c r="F29" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EA%B4%91%EC%A7%84%EA%B5%AC-%EC%B5%9C%EA%B3%A0%EC%9D%98-%EC%8B%A4%EB%82%B4-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%84%BC%ED%84%B0-%EB%A0%88%EB%93%9C%ED%8F%AC%EC%9D%B8%ED%8A%B8%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%A7%91%EC%A4%91-%EB%B6%84%EC%84%9D</x:v>
       </x:c>
-      <x:c r="G29" s="19" t="str">
+      <x:c r="G29" s="82" t="str">
         <x:v>내부 클라이밍 벽</x:v>
       </x:c>
+      <x:c r="H29" s="81"/>
+      <x:c r="I29" s="81"/>
+      <x:c r="J29" s="81"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="19" t="str">
+      <x:c r="A30" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B30" s="19" t="str">
+      <x:c r="B30" s="82" t="str">
         <x:v>HBD-GYM-0029</x:v>
       </x:c>
-      <x:c r="C30" s="19" t="str">
+      <x:c r="C30" s="82" t="str">
         <x:v>버티고클라이밍짐</x:v>
       </x:c>
-      <x:c r="D30" s="19" t="str">
+      <x:c r="D30" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E30" s="19" t="str">
+      <x:c r="E30" s="82" t="str">
         <x:v>https://climbatlas.app/api/places/photo/ChIJ7Xbn1dS6fDURkmjF6cDfr4s/Ab43m-vOxpduZmRx4hTOGo1Fg-WKRQ7GrS2hF6qwovPrGe9kiwZr2waLGmX4hN3jZ9Fn92sO0-UCdngaVowyLG9oz5BPvEFFyhyDIrbXY9bxuSlRR3y-5KkFle72VhlUOU5dQQB3eK_bwUvx0MTMUM0JQwkxKqvQEN42PR6UJe3P3pRp-J-YKKhk_fCGFEU4fMmlw5iSqZxSQMpACXTVgYV3QlQNLrLXhXPP-ZE6JWiJCQp4FVw838PMR361OJoWrRr5i9jKRrLGKthvd0b15boAnouYI6YnMDEnHLrHJR8yJ0ZI_A</x:v>
       </x:c>
-      <x:c r="F30" s="19" t="str">
+      <x:c r="F30" s="82" t="str">
         <x:v>https://climbatlas.app/indoor/bouldering/kr/seoulteugbyeolsi/20163/beotigokeullaimingjim</x:v>
       </x:c>
-      <x:c r="G30" s="19" t="str">
+      <x:c r="G30" s="82" t="str">
         <x:v>ClimbAtlas 대표사진</x:v>
       </x:c>
+      <x:c r="H30" s="81"/>
+      <x:c r="I30" s="81"/>
+      <x:c r="J30" s="81"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="19" t="str">
+      <x:c r="A31" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B31" s="19" t="str">
+      <x:c r="B31" s="82" t="str">
         <x:v>HBD-GYM-0030</x:v>
       </x:c>
-      <x:c r="C31" s="19" t="str">
+      <x:c r="C31" s="82" t="str">
         <x:v>조규복클라이밍센터 강변점</x:v>
       </x:c>
-      <x:c r="D31" s="19" t="str">
+      <x:c r="D31" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E31" s="19" t="str">
+      <x:c r="E31" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/CVKaQ/btsL452qnZK/AAAAAAAAAAAAAAAAAAAAAP-xCawx0pExqbIa5hY8pR6lDLsgTAIfym3u2P-HPYBW/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1780239599&amp;signature=bxJPZwLJ6qOsQyG7I6srAZtceAg%3D</x:v>
       </x:c>
-      <x:c r="F31" s="19" t="str">
+      <x:c r="F31" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EC%84%9C%EC%9A%B8-%EA%B4%91%EC%A7%84%EA%B5%AC%EC%97%90%EC%84%9C-%EC%B0%BE%EC%9D%80-%EC%A7%9C%EB%A6%BF%ED%95%9C-%EB%8F%84%EC%A0%84-%EC%A1%B0%EA%B7%9C%EB%B3%B5%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0-%EA%B0%95%EB%B3%80%EC%A0%90-%EC%99%84%EB%B2%BD-%EA%B0%80%EC%9D%B4%EB%93%9C</x:v>
       </x:c>
-      <x:c r="G31" s="19" t="str">
+      <x:c r="G31" s="82" t="str">
         <x:v>강변점 내부 벽</x:v>
       </x:c>
+      <x:c r="H31" s="81"/>
+      <x:c r="I31" s="81"/>
+      <x:c r="J31" s="81"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="19" t="str">
+      <x:c r="A32" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B32" s="19" t="str">
+      <x:c r="B32" s="82" t="str">
         <x:v>HBD-GYM-0031</x:v>
       </x:c>
-      <x:c r="C32" s="19" t="str">
+      <x:c r="C32" s="82" t="str">
         <x:v>서울숲클라이밍 구로점</x:v>
       </x:c>
-      <x:c r="D32" s="19" t="str">
+      <x:c r="D32" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E32" s="19" t="str">
+      <x:c r="E32" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/4S8B9JuxTQ7ESa4ez2mOu0KcKFJbiw66b95jyihz4qWy5LPYWNo8mxeNhiS9UD6goNQpScokfCQMqMOgUCKZr6Oc6Dck_Dq7-_vHf5H7O1yTmOwGZlXtqvcSMPH0ncvZ5hiKx--DVZXCT16ptAk7a2DOS02rzQKEshGIhm6aheQnxsjEUgY2gokdcrafUG1_?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F32" s="19" t="str"/>
-      <x:c r="G32" s="19" t="str"/>
+      <x:c r="F32" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G32" s="82" t="str"/>
+      <x:c r="H32" s="81"/>
+      <x:c r="I32" s="81"/>
+      <x:c r="J32" s="81"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="19" t="str">
+      <x:c r="A33" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B33" s="19" t="str">
+      <x:c r="B33" s="82" t="str">
         <x:v>HBD-GYM-0032</x:v>
       </x:c>
-      <x:c r="C33" s="19" t="str">
+      <x:c r="C33" s="82" t="str">
         <x:v>스튜디오 볼더</x:v>
       </x:c>
-      <x:c r="D33" s="19" t="str">
+      <x:c r="D33" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E33" s="19" t="str">
+      <x:c r="E33" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/t96XaBArCKX6YTbZfk4KPdql1SY6ls4uPFs_tRIuvMmM7rSiZmoneFvjX7xAFkWQ6F-kDsnTnvEJi5LUYeHm4Os8iBQ7oIFgEVL1GpTLiKG-S-1bVUtK4H9GzgneLHpBGJhXEm5UU3lHurp1Cm_tHPHjLUR6dtDAbIOoGu8D6DytW8BKh1oYjiHNVBwOcPYB?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F33" s="19" t="str"/>
-      <x:c r="G33" s="19" t="str"/>
+      <x:c r="F33" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%8A%A4%ED%8A%9C%EB%94%94%EC%98%A4%20%EB%B3%BC%EB%8D%94</x:v>
+      </x:c>
+      <x:c r="G33" s="82" t="str"/>
+      <x:c r="H33" s="81"/>
+      <x:c r="I33" s="81"/>
+      <x:c r="J33" s="81"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="19" t="str">
+      <x:c r="A34" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B34" s="19" t="str">
+      <x:c r="B34" s="82" t="str">
         <x:v>HBD-GYM-0033</x:v>
       </x:c>
-      <x:c r="C34" s="19" t="str">
+      <x:c r="C34" s="82" t="str">
         <x:v>썬 클라이밍 짐</x:v>
       </x:c>
-      <x:c r="D34" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E34" s="19" t="str"/>
-      <x:c r="F34" s="19" t="str"/>
-      <x:c r="G34" s="19" t="str"/>
+      <x:c r="D34" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E34" s="82"/>
+      <x:c r="F34" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G34" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H34" s="81"/>
+      <x:c r="I34" s="81"/>
+      <x:c r="J34" s="81"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="19" t="str">
+      <x:c r="A35" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B35" s="19" t="str">
+      <x:c r="B35" s="82" t="str">
         <x:v>HBD-GYM-0034</x:v>
       </x:c>
-      <x:c r="C35" s="19" t="str">
+      <x:c r="C35" s="82" t="str">
         <x:v>위클리클라이밍</x:v>
       </x:c>
-      <x:c r="D35" s="19" t="str">
+      <x:c r="D35" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E35" s="19" t="str">
+      <x:c r="E35" s="82" t="str">
         <x:v>https://t1.daumcdn.net/cfile/tistory/991D59355D345FAF1A</x:v>
       </x:c>
-      <x:c r="F35" s="19" t="str">
+      <x:c r="F35" s="82" t="str">
         <x:v>https://kkaint.tistory.com/637</x:v>
       </x:c>
-      <x:c r="G35" s="19" t="str">
+      <x:c r="G35" s="82" t="str">
         <x:v>구일/구로 내부</x:v>
       </x:c>
+      <x:c r="H35" s="81"/>
+      <x:c r="I35" s="81"/>
+      <x:c r="J35" s="81"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="19" t="str">
+      <x:c r="A36" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B36" s="19" t="str">
+      <x:c r="B36" s="82" t="str">
         <x:v>HBD-GYM-0035</x:v>
       </x:c>
-      <x:c r="C36" s="19" t="str">
+      <x:c r="C36" s="82" t="str">
         <x:v>클라임잇 구로점</x:v>
       </x:c>
-      <x:c r="D36" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E36" s="19" t="str"/>
-      <x:c r="F36" s="19" t="str"/>
-      <x:c r="G36" s="19" t="str"/>
+      <x:c r="D36" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E36" s="82"/>
+      <x:c r="F36" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9E%84%EC%9E%87%20%EA%B5%AC%EB%A1%9C%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G36" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H36" s="81"/>
+      <x:c r="I36" s="81"/>
+      <x:c r="J36" s="81"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="19" t="str">
+      <x:c r="A37" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B37" s="19" t="str">
+      <x:c r="B37" s="82" t="str">
         <x:v>HBD-GYM-0036</x:v>
       </x:c>
-      <x:c r="C37" s="19" t="str">
+      <x:c r="C37" s="82" t="str">
         <x:v>피커스 클라이밍 구로점</x:v>
       </x:c>
-      <x:c r="D37" s="19" t="str">
+      <x:c r="D37" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E37" s="19" t="str">
+      <x:c r="E37" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/YnOHS4idXwMXMOYQ_wIGBTrvYM2VnSi823aZiY2avw2tHXyKkN99ABZQkRv57ELbKyd1VjHogLAVJzNmGttcKbhuUcUL0ejiD6d73x_xIv59GWn9PSKFprSBL2YxZnnEGeW24FcMBpvFDRIsNIWJlXafQQozQ25H-XrQbyytqL13T8yshf7QQ2u8VUvkHUVY?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F37" s="19" t="str"/>
-      <x:c r="G37" s="19" t="str"/>
+      <x:c r="F37" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%94%BC%EC%BB%A4%EC%8A%A4%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EA%B5%AC%EB%A1%9C%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G37" s="82" t="str"/>
+      <x:c r="H37" s="81"/>
+      <x:c r="I37" s="81"/>
+      <x:c r="J37" s="81"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="19" t="str">
+      <x:c r="A38" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B38" s="19" t="str">
+      <x:c r="B38" s="82" t="str">
         <x:v>HBD-GYM-0037</x:v>
       </x:c>
-      <x:c r="C38" s="19" t="str">
+      <x:c r="C38" s="82" t="str">
         <x:v>어거스트 클라이밍 가산점</x:v>
       </x:c>
-      <x:c r="D38" s="19" t="str">
+      <x:c r="D38" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E38" s="19" t="str">
+      <x:c r="E38" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/btUYnt/btrDYoPJdYj/AAAAAAAAAAAAAAAAAAAAANMUS-LwGg2qVRyuEeMV7r1E2y9y2uv4phXJam60HoYq/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1769871599&amp;signature=mn5b9T0Wys%2Fl3KK%2FTgf7%2FiP61p8%3D</x:v>
       </x:c>
-      <x:c r="F38" s="19" t="str">
+      <x:c r="F38" s="82" t="str">
         <x:v>https://climbtourtv.com/entry/%EA%B0%80%EC%82%B0%EB%94%94%EC%A7%80%ED%84%B8%EB%8B%A8%EC%A7%80-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%9E%A5-%EC%96%B4%EA%B1%B0%EC%8A%A4%ED%8A%B8-%EB%AF%BC%ED%98%84%EB%B9%88</x:v>
       </x:c>
-      <x:c r="G38" s="19" t="str">
+      <x:c r="G38" s="82" t="str">
         <x:v>A벽 내부 전경</x:v>
       </x:c>
+      <x:c r="H38" s="81"/>
+      <x:c r="I38" s="81"/>
+      <x:c r="J38" s="81"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="19" t="str">
+      <x:c r="A39" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B39" s="19" t="str">
+      <x:c r="B39" s="82" t="str">
         <x:v>HBD-GYM-0038</x:v>
       </x:c>
-      <x:c r="C39" s="19" t="str">
+      <x:c r="C39" s="82" t="str">
         <x:v>드림캐처 클라이밍</x:v>
       </x:c>
-      <x:c r="D39" s="19" t="str">
+      <x:c r="D39" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E39" s="19" t="str">
+      <x:c r="E39" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/BFc551j2jGilLpi5p2cJ04USESMoPSaNd2Jw5XsCKm4-TZO-LN2W3q8JZQ6ds1wskY-o5tu3oFhUJP_m0bTDCPBAi38sQgMZk6erYIfMFsIq03AlVMEa_LDjWMlP0YNihzxtvEVofgz42fThXNEPjeKlhapI7K9N49fntkpbzJBKxan7a_SLvh9v37rUOEHn?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F39" s="19" t="str"/>
-      <x:c r="G39" s="19" t="str"/>
+      <x:c r="F39" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%93%9C%EB%A6%BC%EC%BA%90%EC%B2%98%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G39" s="82" t="str"/>
+      <x:c r="H39" s="81"/>
+      <x:c r="I39" s="81"/>
+      <x:c r="J39" s="81"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="19" t="str">
+      <x:c r="A40" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B40" s="19" t="str">
+      <x:c r="B40" s="82" t="str">
         <x:v>HBD-GYM-0039</x:v>
       </x:c>
-      <x:c r="C40" s="19" t="str">
+      <x:c r="C40" s="82" t="str">
         <x:v>볼더 클라이밍 짐</x:v>
       </x:c>
-      <x:c r="D40" s="19" t="str">
+      <x:c r="D40" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E40" s="19" t="str">
+      <x:c r="E40" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/UesXp/btsL8dtfSTt/AAAAAAAAAAAAAAAAAAAAAP6_esdNgkAWaPKEx2EMSk_iqFjlcKRtdDsthcNVNQke/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=arqZGp0427eJdHAs%2BYiCOGW8vLE%3D</x:v>
       </x:c>
-      <x:c r="F40" s="19" t="str">
+      <x:c r="F40" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EC%84%9C%EC%9A%B8-%EB%85%B8%EC%9B%90%EA%B5%AC-%EB%B3%BC%EB%8D%94-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%A7%90-%EB%8F%84%EC%8B%AC-%EC%86%8D-%EC%A7%9C%EB%A6%BF%ED%95%9C-%EB%8F%84%EC%A0%84</x:v>
       </x:c>
-      <x:c r="G40" s="19" t="str">
+      <x:c r="G40" s="82" t="str">
         <x:v>수락산 내부</x:v>
       </x:c>
+      <x:c r="H40" s="81"/>
+      <x:c r="I40" s="81"/>
+      <x:c r="J40" s="81"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="19" t="str">
+      <x:c r="A41" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B41" s="19" t="str">
+      <x:c r="B41" s="82" t="str">
         <x:v>HBD-GYM-0040</x:v>
       </x:c>
-      <x:c r="C41" s="19" t="str">
+      <x:c r="C41" s="82" t="str">
         <x:v>비숍 클라이밍</x:v>
       </x:c>
-      <x:c r="D41" s="19" t="str">
+      <x:c r="D41" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E41" s="19" t="str">
+      <x:c r="E41" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/WCp1qUWAJ4_0wiH-yteREYz5FXfUUDIIVpm_ZPRAHgekyg-wEXIxUjQFkwkih8IAGJcRFCdNIUz_8MymQCdM85D-Ucsv11UjPPN3fSn4-2DvhNbFEFkeUgtVBspsxmdE3qlVaw1eBweIlqXZQbV9PPBsrA5tfelHThP85WN8Hhx5U7RB3_7y8oMaEQ4FgVae?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F41" s="19" t="str"/>
-      <x:c r="G41" s="19" t="str"/>
+      <x:c r="F41" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%B9%84%EC%88%8D%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G41" s="82" t="str"/>
+      <x:c r="H41" s="81"/>
+      <x:c r="I41" s="81"/>
+      <x:c r="J41" s="81"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="19" t="str">
+      <x:c r="A42" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B42" s="19" t="str">
+      <x:c r="B42" s="82" t="str">
         <x:v>HBD-GYM-0041</x:v>
       </x:c>
-      <x:c r="C42" s="19" t="str">
+      <x:c r="C42" s="82" t="str">
         <x:v>오름클라이밍</x:v>
       </x:c>
-      <x:c r="D42" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E42" s="19" t="str"/>
-      <x:c r="F42" s="19" t="str"/>
-      <x:c r="G42" s="19" t="str"/>
+      <x:c r="D42" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E42" s="82"/>
+      <x:c r="F42" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G42" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H42" s="81"/>
+      <x:c r="I42" s="81"/>
+      <x:c r="J42" s="81"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="19" t="str">
+      <x:c r="A43" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B43" s="19" t="str">
+      <x:c r="B43" s="82" t="str">
         <x:v>HBD-GYM-0042</x:v>
       </x:c>
-      <x:c r="C43" s="19" t="str">
+      <x:c r="C43" s="82" t="str">
         <x:v>태릉스파이더스 클라이밍센터</x:v>
       </x:c>
-      <x:c r="D43" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E43" s="19" t="str"/>
-      <x:c r="F43" s="19" t="str"/>
-      <x:c r="G43" s="19" t="str"/>
+      <x:c r="D43" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E43" s="82"/>
+      <x:c r="F43" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%83%9C%EB%A6%89%EC%8A%A4%ED%8C%8C%EC%9D%B4%EB%8D%94%EC%8A%A4%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G43" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H43" s="81"/>
+      <x:c r="I43" s="81"/>
+      <x:c r="J43" s="81"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="19" t="str">
+      <x:c r="A44" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B44" s="19" t="str">
+      <x:c r="B44" s="82" t="str">
         <x:v>HBD-GYM-0043</x:v>
       </x:c>
-      <x:c r="C44" s="19" t="str">
+      <x:c r="C44" s="82" t="str">
         <x:v>도봉파워클라이밍센터</x:v>
       </x:c>
-      <x:c r="D44" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E44" s="19" t="str"/>
-      <x:c r="F44" s="19" t="str"/>
-      <x:c r="G44" s="19" t="str"/>
+      <x:c r="D44" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E44" s="82" t="str">
+        <x:v>https://img2.daumcdn.net/thumb/R658x0.q70/?fname=https%3A%2F%2Ft1.daumcdn.net%2Fnews%2F202603%2F12%2Fsan%2F20260312075709310okbj.jpg</x:v>
+      </x:c>
+      <x:c r="F44" s="82" t="str">
+        <x:v>https://v.daum.net/v/20260312075643531</x:v>
+      </x:c>
+      <x:c r="G44" s="82" t="str">
+        <x:v>내부 전경 · 2026.03 기사에서 암장명/주소/사진 캡션 매칭</x:v>
+      </x:c>
+      <x:c r="H44" s="81"/>
+      <x:c r="I44" s="81"/>
+      <x:c r="J44" s="81"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="19" t="str">
+      <x:c r="A45" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B45" s="19" t="str">
+      <x:c r="B45" s="82" t="str">
         <x:v>HBD-GYM-0044</x:v>
       </x:c>
-      <x:c r="C45" s="19" t="str">
+      <x:c r="C45" s="82" t="str">
         <x:v>산타클라이밍짐</x:v>
       </x:c>
-      <x:c r="D45" s="19" t="str">
+      <x:c r="D45" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E45" s="19" t="str">
+      <x:c r="E45" s="82" t="str">
         <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEhfNLrlVSDwP9Jho20lk2e_69n_HKjihug_hZNQpxfrwNub-BPee1_0ozIf-OyOtzX7KSHXI9cnmdQgUr1Q6XQwD6buI2xskj5ht6WYj6RLrW6yOumO20DR6UmhbojBtY8Jq-mWuuyclsAg/s400/Santa%2Bclimbing%2Bgym%2B%2528%25E1%2584%2589%25E1%2585%25A1%25E1%2586%25AB%25E1%2584%2590%25E1%2585%25A1%25E1%2584%258F%25E1%2585%25B3%25E1%2586%25AF%25E1%2584%2585%25E1%2585%25A1%25E1%2584%258B%25E1%2585%25B5%25E1%2584%2586%25E1%2585%25B5%25E1%2586%25BC%25E1%2584%258C%25E1%2585%25B5%25E1%2586%25B7%2529.png</x:v>
       </x:c>
-      <x:c r="F45" s="19" t="str">
+      <x:c r="F45" s="82" t="str">
         <x:v>https://climbinginkorea.blogspot.com/2018/04/santa-climbing-gym.html</x:v>
       </x:c>
-      <x:c r="G45" s="19" t="str">
+      <x:c r="G45" s="82" t="str">
         <x:v>대표 시설 사진</x:v>
       </x:c>
+      <x:c r="H45" s="81"/>
+      <x:c r="I45" s="81"/>
+      <x:c r="J45" s="81"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="19" t="str">
+      <x:c r="A46" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B46" s="19" t="str">
+      <x:c r="B46" s="82" t="str">
         <x:v>HBD-GYM-0045</x:v>
       </x:c>
-      <x:c r="C46" s="19" t="str">
+      <x:c r="C46" s="82" t="str">
         <x:v>서울클라이밍센터</x:v>
       </x:c>
-      <x:c r="D46" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E46" s="19" t="str"/>
-      <x:c r="F46" s="19" t="str"/>
-      <x:c r="G46" s="19" t="str"/>
+      <x:c r="D46" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E46" s="82" t="str">
+        <x:v>https://img1.daumcdn.net/thumb/R658x0.q70/?fname=https%3A%2F%2Ft1.daumcdn.net%2Fnews%2F202603%2F12%2Fsan%2F20260312075658154tytl.jpg</x:v>
+      </x:c>
+      <x:c r="F46" s="82" t="str">
+        <x:v>https://v.daum.net/v/20260312075643531</x:v>
+      </x:c>
+      <x:c r="G46" s="82" t="str">
+        <x:v>내부 전경 · 2026.03 기사에서 서울클라이밍센터(무학로 130) 사진 캡션 매칭</x:v>
+      </x:c>
+      <x:c r="H46" s="81"/>
+      <x:c r="I46" s="81"/>
+      <x:c r="J46" s="81"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="19" t="str">
+      <x:c r="A47" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B47" s="19" t="str">
+      <x:c r="B47" s="82" t="str">
         <x:v>HBD-GYM-0046</x:v>
       </x:c>
-      <x:c r="C47" s="19" t="str">
+      <x:c r="C47" s="82" t="str">
         <x:v>웨어하우스 볼더링</x:v>
       </x:c>
-      <x:c r="D47" s="19" t="str">
+      <x:c r="D47" s="82" t="str">
         <x:v>운영재검증</x:v>
       </x:c>
-      <x:c r="E47" s="19" t="str">
+      <x:c r="E47" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/Cdsyo/btsyTyivoUc/AAAAAAAAAAAAAAAAAAAAAMVDflM9cAr9gJbaIZEsbyDb5mqT8pNR9nSKPBVREAWY/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=y8IuEkRB1eguVYwprbIa%2Bw%2F28Z4%3D</x:v>
       </x:c>
-      <x:c r="F47" s="19" t="str">
+      <x:c r="F47" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EC%9B%A8%EC%96%B4%ED%95%98%EC%9A%B0%EC%8A%A4</x:v>
       </x:c>
-      <x:c r="G47" s="19" t="str">
+      <x:c r="G47" s="82" t="str">
         <x:v>사진은 확보. 최근 ClimbAtlas에서 Closed 표기되어 운영 여부 재확인 필요</x:v>
       </x:c>
+      <x:c r="H47" s="81"/>
+      <x:c r="I47" s="81"/>
+      <x:c r="J47" s="81"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="19" t="str">
+      <x:c r="A48" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B48" s="19" t="str">
+      <x:c r="B48" s="82" t="str">
         <x:v>HBD-GYM-0047</x:v>
       </x:c>
-      <x:c r="C48" s="19" t="str">
+      <x:c r="C48" s="82" t="str">
         <x:v>클라임 어스 장한평점</x:v>
       </x:c>
-      <x:c r="D48" s="19" t="str">
+      <x:c r="D48" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E48" s="19" t="str">
+      <x:c r="E48" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/LMwmB/btsMb0TQyKT/AAAAAAAAAAAAAAAAAAAAAFxu5kinhqQfAUawAF_Gr4vjwWzwMBdVnvVzfJbbpF2N/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1785509999&amp;signature=RTk48Dj1MQDNbR%2B0%2FHiubTf3Pns%3D</x:v>
       </x:c>
-      <x:c r="F48" s="19" t="str">
+      <x:c r="F48" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%B4%88%EB%B3%B4%EB%B6%80%ED%84%B0-%EB%A7%88%EC%8A%A4%ED%84%B0%EA%B9%8C%EC%A7%80-%ED%81%B4%EB%9D%BC%EC%9E%84-%EC%96%B4%EC%8A%A4-%EC%9E%A5%ED%95%9C%ED%8F%89%EC%A0%90-%EB%AA%A8%EB%93%A0-%EA%B2%83</x:v>
       </x:c>
-      <x:c r="G48" s="19" t="str">
+      <x:c r="G48" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H48" s="81"/>
+      <x:c r="I48" s="81"/>
+      <x:c r="J48" s="81"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="19" t="str">
+      <x:c r="A49" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B49" s="19" t="str">
+      <x:c r="B49" s="82" t="str">
         <x:v>HBD-GYM-0048</x:v>
       </x:c>
-      <x:c r="C49" s="19" t="str">
+      <x:c r="C49" s="82" t="str">
         <x:v>더클라임 이수점</x:v>
       </x:c>
-      <x:c r="D49" s="19" t="str">
+      <x:c r="D49" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E49" s="19" t="str">
+      <x:c r="E49" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/bf5l62/dJMcaaEqzXO/AAAAAAAAAAAAAAAAAAAAAPBk7U7Xg4eRVc_s3y4hwTNebIkkgCtgdZYgDZvxWQdu/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=HRsJSAyIJuctSs4Y1bdAZC5fuP4%3D</x:v>
       </x:c>
-      <x:c r="F49" s="19" t="str">
+      <x:c r="F49" s="82" t="str">
         <x:v>https://wowoyong.tistory.com/104</x:v>
       </x:c>
-      <x:c r="G49" s="19" t="str">
+      <x:c r="G49" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H49" s="81"/>
+      <x:c r="I49" s="81"/>
+      <x:c r="J49" s="81"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="19" t="str">
+      <x:c r="A50" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B50" s="19" t="str">
+      <x:c r="B50" s="82" t="str">
         <x:v>HBD-GYM-0049</x:v>
       </x:c>
-      <x:c r="C50" s="19" t="str">
+      <x:c r="C50" s="82" t="str">
         <x:v>볼더생활</x:v>
       </x:c>
-      <x:c r="D50" s="19" t="str">
+      <x:c r="D50" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E50" s="19" t="str">
+      <x:c r="E50" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/MtZOB/btrIddYtbWD/AAAAAAAAAAAAAAAAAAAAAOrYcR5B4vBGRQrWSj10Gyk85AARDh1wFZPVQ19gWlm-/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1785509999&amp;signature=ya%2BWC%2B6OG165%2FDh81Sd%2FlmesLF0%3D</x:v>
       </x:c>
-      <x:c r="F50" s="19" t="str">
+      <x:c r="F50" s="82" t="str">
         <x:v>https://career-review.tistory.com/entry/%EB%B3%BC%EB%8D%94%EC%83%9D%ED%99%9C</x:v>
       </x:c>
-      <x:c r="G50" s="19" t="str">
+      <x:c r="G50" s="82" t="str">
         <x:v>볼더링 벽</x:v>
       </x:c>
+      <x:c r="H50" s="81"/>
+      <x:c r="I50" s="81"/>
+      <x:c r="J50" s="81"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="19" t="str">
+      <x:c r="A51" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B51" s="19" t="str">
+      <x:c r="B51" s="82" t="str">
         <x:v>HBD-GYM-0050</x:v>
       </x:c>
-      <x:c r="C51" s="19" t="str">
+      <x:c r="C51" s="82" t="str">
         <x:v>더클라임 B홍대점</x:v>
       </x:c>
-      <x:c r="D51" s="19" t="str">
+      <x:c r="D51" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E51" s="19" t="str">
+      <x:c r="E51" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/kLScj/btrLk4v7qLN/AAAAAAAAAAAAAAAAAAAAAAQHBMsdWWX-DQ_bBytESFeN3By1tHR87Iouv37k9YgU/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=ZKf3f%2BiBzA5ozP3GPcH26SpRSIQ%3D</x:v>
       </x:c>
-      <x:c r="F51" s="19" t="str">
+      <x:c r="F51" s="82" t="str">
         <x:v>https://dangkachu.tistory.com/271</x:v>
       </x:c>
-      <x:c r="G51" s="19" t="str">
+      <x:c r="G51" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H51" s="81"/>
+      <x:c r="I51" s="81"/>
+      <x:c r="J51" s="81"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="19" t="str">
+      <x:c r="A52" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B52" s="19" t="str">
+      <x:c r="B52" s="82" t="str">
         <x:v>HBD-GYM-0051</x:v>
       </x:c>
-      <x:c r="C52" s="19" t="str">
+      <x:c r="C52" s="82" t="str">
         <x:v>더클라임 연남점</x:v>
       </x:c>
-      <x:c r="D52" s="19" t="str">
+      <x:c r="D52" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E52" s="19" t="str">
+      <x:c r="E52" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/6vOaimpIj2ovYu7OZHuTpPOTzkbQjbTkVt_PtqmfjFBwXKziJ4XPZkNEhNRYd0lT2dsnVcdZQ0SwIjyOnMgHqFC1OYFcCE8aKZhu-jKgSgJ4Gt1BsBkt7BiGywep25FCAeUbwvt7hShbEoif2b_TR13gy9F8yS6z7APIN1gzrzSHIcVLxBM-jVP37zwR55MD?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F52" s="19" t="str"/>
-      <x:c r="G52" s="19" t="str"/>
+      <x:c r="F52" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/hongdae</x:v>
+      </x:c>
+      <x:c r="G52" s="82" t="str"/>
+      <x:c r="H52" s="81"/>
+      <x:c r="I52" s="81"/>
+      <x:c r="J52" s="81"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="19" t="str">
+      <x:c r="A53" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B53" s="19" t="str">
+      <x:c r="B53" s="82" t="str">
         <x:v>HBD-GYM-0052</x:v>
       </x:c>
-      <x:c r="C53" s="19" t="str">
+      <x:c r="C53" s="82" t="str">
         <x:v>망원클라이밍피트니스</x:v>
       </x:c>
-      <x:c r="D53" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E53" s="19" t="str"/>
-      <x:c r="F53" s="19" t="str"/>
-      <x:c r="G53" s="19" t="str"/>
+      <x:c r="D53" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E53" s="82"/>
+      <x:c r="F53" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/hongdae</x:v>
+      </x:c>
+      <x:c r="G53" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H53" s="81"/>
+      <x:c r="I53" s="81"/>
+      <x:c r="J53" s="81"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="19" t="str">
+      <x:c r="A54" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B54" s="19" t="str">
+      <x:c r="B54" s="82" t="str">
         <x:v>HBD-GYM-0053</x:v>
       </x:c>
-      <x:c r="C54" s="19" t="str">
+      <x:c r="C54" s="82" t="str">
         <x:v>볼더그라운드</x:v>
       </x:c>
-      <x:c r="D54" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E54" s="19" t="str"/>
-      <x:c r="F54" s="19" t="str"/>
-      <x:c r="G54" s="19" t="str"/>
+      <x:c r="D54" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E54" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dn/xAqFe/btsE0gwxvzF/aBzRuqLX9j7voqpuhgASZ1/img.jpg</x:v>
+      </x:c>
+      <x:c r="F54" s="82" t="str">
+        <x:v>https://kimazae.tistory.com/8</x:v>
+      </x:c>
+      <x:c r="G54" s="82" t="str">
+        <x:v>내부 볼더링 벽 · 볼더그라운드 방문 후기 + 주소/2026 운영 데이터 매칭</x:v>
+      </x:c>
+      <x:c r="H54" s="81"/>
+      <x:c r="I54" s="81"/>
+      <x:c r="J54" s="81"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="19" t="str">
+      <x:c r="A55" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B55" s="19" t="str">
+      <x:c r="B55" s="82" t="str">
         <x:v>HBD-GYM-0054</x:v>
       </x:c>
-      <x:c r="C55" s="19" t="str">
+      <x:c r="C55" s="82" t="str">
         <x:v>볼더프렌즈 클라이밍</x:v>
       </x:c>
-      <x:c r="D55" s="19" t="str">
+      <x:c r="D55" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E55" s="19" t="str">
+      <x:c r="E55" s="82" t="str">
         <x:v>https://cdn.datepop.co.kr/image/seoul/mapo/256981_1080_720_02cfcf.jpg%3Ds0-l70</x:v>
       </x:c>
-      <x:c r="F55" s="19" t="str">
+      <x:c r="F55" s="82" t="str">
         <x:v>https://www.datepop.co.kr/view/spot/%EB%B3%BC%EB%8D%94%ED%94%84%EB%A0%8C%EC%A6%88-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D/</x:v>
       </x:c>
-      <x:c r="G55" s="19" t="str">
+      <x:c r="G55" s="82" t="str">
         <x:v>높은 벽 전경. URL 다운로드 여부 추후 확인</x:v>
       </x:c>
+      <x:c r="H55" s="81"/>
+      <x:c r="I55" s="81"/>
+      <x:c r="J55" s="81"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="19" t="str">
+      <x:c r="A56" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B56" s="19" t="str">
+      <x:c r="B56" s="82" t="str">
         <x:v>HBD-GYM-0055</x:v>
       </x:c>
-      <x:c r="C56" s="19" t="str">
+      <x:c r="C56" s="82" t="str">
         <x:v>써미트클라이밍센터</x:v>
       </x:c>
-      <x:c r="D56" s="19" t="str">
+      <x:c r="D56" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E56" s="19" t="str">
+      <x:c r="E56" s="82" t="str">
         <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEgSMkHoBqtPwcISDEp_UZXcXnc0dYJ54nJtAmzJyteZxsaPOa5EI7522mtrUHDsGPtkkz2HBwhbfvqZBpqs2Qm0EG_lU7nBMp1ODWtsLOqW4kk8UGrNNXYBiKPxzM9N0-Cz5BiDQGpI_qOk/s320/Summit%2BClimbing%2BCenter%2B%2528%25E1%2584%258A%25E1%2585%25A5%25E1%2584%2586%25E1%2585%25B5%25E1%2584%2590%25E1%2585%25B3%25E1%2584%258F%25E1%2585%25B3%25E1%2586%25AF%25E1%2584%2585%25E1%2585%25A1%25E1%2584%258B%25E1%2585%25B5%25E1%2584%2586%25E1%2585%25B5%25E1%2586%25BC%25E1%2584%2589%25E1%2585%25A6%25E1%2586%25AB%25E1%2584%2590%25E1%2585%25A5%2529.jpg</x:v>
       </x:c>
-      <x:c r="F56" s="19" t="str">
+      <x:c r="F56" s="82" t="str">
         <x:v>https://climbinginkorea.blogspot.com/2018/04/summit-climbing-center.html</x:v>
       </x:c>
-      <x:c r="G56" s="19" t="str">
+      <x:c r="G56" s="82" t="str">
         <x:v>대표 시설 사진</x:v>
       </x:c>
+      <x:c r="H56" s="81"/>
+      <x:c r="I56" s="81"/>
+      <x:c r="J56" s="81"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="19" t="str">
+      <x:c r="A57" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B57" s="19" t="str">
+      <x:c r="B57" s="82" t="str">
         <x:v>HBD-GYM-0056</x:v>
       </x:c>
-      <x:c r="C57" s="19" t="str">
+      <x:c r="C57" s="82" t="str">
         <x:v>코알라클라이밍 상암</x:v>
       </x:c>
-      <x:c r="D57" s="19" t="str">
+      <x:c r="D57" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E57" s="19" t="str">
+      <x:c r="E57" s="82" t="str">
         <x:v>https://i0.wp.com/blog.waug.com/wp-content/uploads/2020/10/best-wall-climbing-seoul-korea.jpg?resize=1024%2C1024&amp;ssl=1</x:v>
       </x:c>
-      <x:c r="F57" s="19" t="str">
+      <x:c r="F57" s="82" t="str">
         <x:v>https://blog.waug.com/wall-climbing-seoul/</x:v>
       </x:c>
-      <x:c r="G57" s="19" t="str">
+      <x:c r="G57" s="82" t="str">
         <x:v>상암 코알라 내부 볼더링 벽</x:v>
       </x:c>
+      <x:c r="H57" s="81"/>
+      <x:c r="I57" s="81"/>
+      <x:c r="J57" s="81"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="19" t="str">
+      <x:c r="A58" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B58" s="19" t="str">
+      <x:c r="B58" s="82" t="str">
         <x:v>HBD-GYM-0057</x:v>
       </x:c>
-      <x:c r="C58" s="19" t="str">
+      <x:c r="C58" s="82" t="str">
         <x:v>홍대클라이밍센터</x:v>
       </x:c>
-      <x:c r="D58" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E58" s="19" t="str"/>
-      <x:c r="F58" s="19" t="str"/>
-      <x:c r="G58" s="19" t="str"/>
+      <x:c r="D58" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E58" s="82"/>
+      <x:c r="F58" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/hongdae</x:v>
+      </x:c>
+      <x:c r="G58" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H58" s="81"/>
+      <x:c r="I58" s="81"/>
+      <x:c r="J58" s="81"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="19" t="str">
+      <x:c r="A59" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B59" s="19" t="str">
+      <x:c r="B59" s="82" t="str">
         <x:v>HBD-GYM-0058</x:v>
       </x:c>
-      <x:c r="C59" s="19" t="str">
+      <x:c r="C59" s="82" t="str">
         <x:v>신촌담장</x:v>
       </x:c>
-      <x:c r="D59" s="19" t="str">
+      <x:c r="D59" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E59" s="19" t="str">
+      <x:c r="E59" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/JuKBO/btsMGzVpL01/AAAAAAAAAAAAAAAAAAAAADHn1v1GeLVgt6fQXKRzcA4-fpkv5N7H8yQkXVvrYd61/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1769871599&amp;signature=3sWCQ9Qx9XkorhaLSz4aFLDODC4%3D</x:v>
       </x:c>
-      <x:c r="F59" s="19" t="str">
+      <x:c r="F59" s="82" t="str">
         <x:v>https://start2025.tistory.com/42</x:v>
       </x:c>
-      <x:c r="G59" s="19" t="str">
+      <x:c r="G59" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H59" s="81"/>
+      <x:c r="I59" s="81"/>
+      <x:c r="J59" s="81"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="19" t="str">
+      <x:c r="A60" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B60" s="19" t="str">
+      <x:c r="B60" s="82" t="str">
         <x:v>HBD-GYM-0059</x:v>
       </x:c>
-      <x:c r="C60" s="19" t="str">
+      <x:c r="C60" s="82" t="str">
         <x:v>피커스 클라이밍 신촌점</x:v>
       </x:c>
-      <x:c r="D60" s="19" t="str">
+      <x:c r="D60" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E60" s="19" t="str">
+      <x:c r="E60" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/c5mma_wU_AnODQ_vFsKgR5It8Fs1vSm6--VfenIlukAlMX8mBw1aKWihNBvLBeFcuAt4HTj7vQTWQYyfRvWM_tQQgJE5vKpbDHQf2dOtgy9hSFGVaCOhbHfq-ifNKYMMPtX06B1v6Ig53e10_oR0AjDkeyFdTNGaZFZRdxYYKSug9ka4oYkE1Hv__o3Tidar?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F60" s="19" t="str"/>
-      <x:c r="G60" s="19" t="str"/>
+      <x:c r="F60" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%94%BC%EC%BB%A4%EC%8A%A4%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EC%8B%A0%EC%B4%8C%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G60" s="82" t="str"/>
+      <x:c r="H60" s="81"/>
+      <x:c r="I60" s="81"/>
+      <x:c r="J60" s="81"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="19" t="str">
+      <x:c r="A61" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B61" s="19" t="str">
+      <x:c r="B61" s="82" t="str">
         <x:v>HBD-GYM-0060</x:v>
       </x:c>
-      <x:c r="C61" s="19" t="str">
+      <x:c r="C61" s="82" t="str">
         <x:v>더클라임 논현점</x:v>
       </x:c>
-      <x:c r="D61" s="19" t="str">
+      <x:c r="D61" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E61" s="19" t="str">
+      <x:c r="E61" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/vDvQnzAvE3GevAVMXDakRuI-xwlslgqPKVJZT-6Pu1-QO2HywBgyW7psF82PgGN1SMo-ZsjBQbeNKXiaD0eFk5IlGzrKXeSDNRiyuwhMpMNYcU_GWKc46wLoguHhYk9hIfkimsgF0iRn-gTxYNggJzQtVQJ_SsPcyx3ufY2F5pihYB1brfNm2qCzSQsfVaeY?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F61" s="19" t="str"/>
-      <x:c r="G61" s="19" t="str"/>
+      <x:c r="F61" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/gangnam</x:v>
+      </x:c>
+      <x:c r="G61" s="82" t="str"/>
+      <x:c r="H61" s="81"/>
+      <x:c r="I61" s="81"/>
+      <x:c r="J61" s="81"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="19" t="str">
+      <x:c r="A62" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B62" s="19" t="str">
+      <x:c r="B62" s="82" t="str">
         <x:v>HBD-GYM-0061</x:v>
       </x:c>
-      <x:c r="C62" s="19" t="str">
+      <x:c r="C62" s="82" t="str">
         <x:v>손상원클라이밍짐 강남점</x:v>
       </x:c>
-      <x:c r="D62" s="19" t="str">
+      <x:c r="D62" s="82" t="str">
         <x:v>임시</x:v>
       </x:c>
-      <x:c r="E62" s="19" t="str">
+      <x:c r="E62" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/sV-bIUA5z2PAKDa-1EgN1ktPCHiLa_MjqGzn4x6d2eWTBnI-pMotY_NkjHvWXsbdoLrFZTVPv3BSvPTklFTuNV4ohjdtDH3kYZ8ixfYFYJ9_Jb1ALvDtiwO26T3FDX6aAykYvDA9iRMw9N8dzkwtcdbBhrUOhM0RdxiAKmYzJBsjCoKfHaD0EWYLlr5j5D8h?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F62" s="19" t="str"/>
-      <x:c r="G62" s="19" t="str"/>
+      <x:c r="F62" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/gangnam</x:v>
+      </x:c>
+      <x:c r="G62" s="82" t="str"/>
+      <x:c r="H62" s="81"/>
+      <x:c r="I62" s="81"/>
+      <x:c r="J62" s="81"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="19" t="str">
+      <x:c r="A63" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B63" s="19" t="str">
+      <x:c r="B63" s="82" t="str">
         <x:v>HBD-GYM-0062</x:v>
       </x:c>
-      <x:c r="C63" s="19" t="str">
+      <x:c r="C63" s="82" t="str">
         <x:v>엠씨씨실내암벽클럽</x:v>
       </x:c>
-      <x:c r="D63" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E63" s="19" t="str"/>
-      <x:c r="F63" s="19" t="str"/>
-      <x:c r="G63" s="19" t="str"/>
+      <x:c r="D63" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E63" s="82"/>
+      <x:c r="F63" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/gangnam</x:v>
+      </x:c>
+      <x:c r="G63" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H63" s="81"/>
+      <x:c r="I63" s="81"/>
+      <x:c r="J63" s="81"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="19" t="str">
+      <x:c r="A64" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B64" s="19" t="str">
+      <x:c r="B64" s="82" t="str">
         <x:v>HBD-GYM-0063</x:v>
       </x:c>
-      <x:c r="C64" s="19" t="str">
+      <x:c r="C64" s="82" t="str">
         <x:v>그루트클라이밍</x:v>
       </x:c>
-      <x:c r="D64" s="19" t="str">
+      <x:c r="D64" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E64" s="19" t="str">
+      <x:c r="E64" s="82" t="str">
         <x:v>https://img.kr.gcp-karroter.net/capri/bizPlatform/profile/100504564/1753774275905/ZmRmYjExNzc4YTM1ODEwZTE5NTM4NzM2MzVmOWQyNTQxNTU1NzUxYzIyNTI5MmU5M2YyNGEyMWVjZDNiMDNkY181LmpwZWc%3D.jpeg?q=95&amp;s=1440x1440&amp;t=inside</x:v>
       </x:c>
-      <x:c r="F64" s="19" t="str">
+      <x:c r="F64" s="82" t="str">
         <x:v>https://www.daangn.com/kr/local-profile/%EA%B7%B8%EB%A3%A8%ED%8A%B8%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-zm516gcpjurv/</x:v>
       </x:c>
-      <x:c r="G64" s="19" t="str">
+      <x:c r="G64" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H64" s="81"/>
+      <x:c r="I64" s="81"/>
+      <x:c r="J64" s="81"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="19" t="str">
+      <x:c r="A65" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B65" s="19" t="str">
+      <x:c r="B65" s="82" t="str">
         <x:v>HBD-GYM-0064</x:v>
       </x:c>
-      <x:c r="C65" s="19" t="str">
+      <x:c r="C65" s="82" t="str">
         <x:v>더클라임 성수점</x:v>
       </x:c>
-      <x:c r="D65" s="19" t="str">
+      <x:c r="D65" s="82" t="str">
         <x:v>임시</x:v>
       </x:c>
-      <x:c r="E65" s="19" t="str">
+      <x:c r="E65" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/6F8eTjL-TNHP-pWNWqQY2Zjjq5h1syczvdx8NF0wpMIKVoT45JCijwOoAeHkq0b9IK7kbb4dnzWoe8pcNB38CJ_5o5z4psdHvx01wo_t4lW08SOaV0xTQpJYt-Ti_E8tOCSMcB7pZOmyp59XUiUdMI9So2WlxgTkKtczqIWdg_pXFacoMS8i01gN1tWY-sre?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F65" s="19" t="str"/>
-      <x:c r="G65" s="19" t="str"/>
+      <x:c r="F65" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%8D%94%ED%81%B4%EB%9D%BC%EC%9E%84%20%EC%84%B1%EC%88%98%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G65" s="82" t="str"/>
+      <x:c r="H65" s="81"/>
+      <x:c r="I65" s="81"/>
+      <x:c r="J65" s="81"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="19" t="str">
+      <x:c r="A66" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B66" s="19" t="str">
+      <x:c r="B66" s="82" t="str">
         <x:v>HBD-GYM-0065</x:v>
       </x:c>
-      <x:c r="C66" s="19" t="str">
+      <x:c r="C66" s="82" t="str">
         <x:v>클라이밍파크 성수점</x:v>
       </x:c>
-      <x:c r="D66" s="19" t="str">
+      <x:c r="D66" s="82" t="str">
         <x:v>임시</x:v>
       </x:c>
-      <x:c r="E66" s="19" t="str">
+      <x:c r="E66" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/yd2F6QD7Vvb6KP0KvjlkAEnkKKSlNgEVtv9fpw_Z9gNvkJJ_clZZwjZfwRsinEL0cXG7hzdI1ODPXEfTLcu8PZwxkZomnWTNc3Pkz-33B06ESQJ94431KPvPOCX3UG1n1kAQffwqRLTe47OA6TQDIFujiKyRvi4BzFDme_6pzI4ienpTMj-yoEGvQNrqMdkx?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F66" s="19" t="str"/>
-      <x:c r="G66" s="19" t="str"/>
+      <x:c r="F66" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G66" s="82" t="str"/>
+      <x:c r="H66" s="81"/>
+      <x:c r="I66" s="81"/>
+      <x:c r="J66" s="81"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="19" t="str">
+      <x:c r="A67" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B67" s="19" t="str">
+      <x:c r="B67" s="82" t="str">
         <x:v>HBD-GYM-0066</x:v>
       </x:c>
-      <x:c r="C67" s="19" t="str">
+      <x:c r="C67" s="82" t="str">
         <x:v>훅클라이밍 성수점</x:v>
       </x:c>
-      <x:c r="D67" s="19" t="str">
+      <x:c r="D67" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E67" s="19" t="str">
+      <x:c r="E67" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/BbnbT/btsCxHCRkCd/AAAAAAAAAAAAAAAAAAAAABCLptmCiEZV8f9FK1jziRL_o47a5haS4pHjpKf-r5BF/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=efjj0ijdaM0kS%2FCXUFz8BENsrpI%3D</x:v>
       </x:c>
-      <x:c r="F67" s="19" t="str">
+      <x:c r="F67" s="82" t="str">
         <x:v>https://skewed.tistory.com/84</x:v>
       </x:c>
-      <x:c r="G67" s="19" t="str">
+      <x:c r="G67" s="82" t="str">
         <x:v>볼더링/지구력 공간</x:v>
       </x:c>
+      <x:c r="H67" s="81"/>
+      <x:c r="I67" s="81"/>
+      <x:c r="J67" s="81"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="19" t="str">
+      <x:c r="A68" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B68" s="19" t="str">
+      <x:c r="B68" s="82" t="str">
         <x:v>HBD-GYM-0067</x:v>
       </x:c>
-      <x:c r="C68" s="19" t="str">
+      <x:c r="C68" s="82" t="str">
         <x:v>훅클라이밍 왕십리점</x:v>
       </x:c>
-      <x:c r="D68" s="19" t="str">
+      <x:c r="D68" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E68" s="19" t="str">
+      <x:c r="E68" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/XFW33/btrISAdKzPh/AAAAAAAAAAAAAAAAAAAAAAclc_GCEaBUSepHS_4lsKGCA3TQsQ9V2WoZlIXXyB9b/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=C1yinYQL3w4vBg38Wg4O5dsWSWA%3D</x:v>
       </x:c>
-      <x:c r="F68" s="19" t="str">
+      <x:c r="F68" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EC%99%95%EC%8B%AD%EB%A6%AC-%ED%9B%85%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
       </x:c>
-      <x:c r="G68" s="19" t="str">
+      <x:c r="G68" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H68" s="81"/>
+      <x:c r="I68" s="81"/>
+      <x:c r="J68" s="81"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="19" t="str">
+      <x:c r="A69" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B69" s="19" t="str">
+      <x:c r="B69" s="82" t="str">
         <x:v>HBD-GYM-0068</x:v>
       </x:c>
-      <x:c r="C69" s="19" t="str">
+      <x:c r="C69" s="82" t="str">
         <x:v>경동클라이밍센터</x:v>
       </x:c>
-      <x:c r="D69" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E69" s="19" t="str"/>
-      <x:c r="F69" s="19" t="str"/>
-      <x:c r="G69" s="19" t="str"/>
+      <x:c r="D69" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E69" s="82"/>
+      <x:c r="F69" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EA%B2%BD%EB%8F%99%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G69" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H69" s="81"/>
+      <x:c r="I69" s="81"/>
+      <x:c r="J69" s="81"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="19" t="str">
+      <x:c r="A70" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B70" s="19" t="str">
+      <x:c r="B70" s="82" t="str">
         <x:v>HBD-GYM-0069</x:v>
       </x:c>
-      <x:c r="C70" s="19" t="str">
+      <x:c r="C70" s="82" t="str">
         <x:v>닷클라이밍짐</x:v>
       </x:c>
-      <x:c r="D70" s="19" t="str">
+      <x:c r="D70" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E70" s="19" t="str">
+      <x:c r="E70" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/wXTAd/btrIRGdUrZP/AAAAAAAAAAAAAAAAAAAAAPVKBbokAz1w8k3gaUQ-Mbro9EraIjkbtCGWhdS49PKR/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=zWqIiRmy9ce5gFynGCJJOx0r0FE%3D</x:v>
       </x:c>
-      <x:c r="F70" s="19" t="str">
+      <x:c r="F70" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EB%AC%B8%EC%A0%95%EC%97%AD-%EB%8B%B7%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
       </x:c>
-      <x:c r="G70" s="19" t="str">
+      <x:c r="G70" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H70" s="81"/>
+      <x:c r="I70" s="81"/>
+      <x:c r="J70" s="81"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="19" t="str">
+      <x:c r="A71" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B71" s="19" t="str">
+      <x:c r="B71" s="82" t="str">
         <x:v>HBD-GYM-0070</x:v>
       </x:c>
-      <x:c r="C71" s="19" t="str">
+      <x:c r="C71" s="82" t="str">
         <x:v>더탑실내암벽 송파점</x:v>
       </x:c>
-      <x:c r="D71" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E71" s="19" t="str"/>
-      <x:c r="F71" s="19" t="str"/>
-      <x:c r="G71" s="19" t="str"/>
+      <x:c r="D71" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E71" s="82"/>
+      <x:c r="F71" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G71" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H71" s="81"/>
+      <x:c r="I71" s="81"/>
+      <x:c r="J71" s="81"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="19" t="str">
+      <x:c r="A72" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B72" s="19" t="str">
+      <x:c r="B72" s="82" t="str">
         <x:v>HBD-GYM-0071</x:v>
       </x:c>
-      <x:c r="C72" s="19" t="str">
+      <x:c r="C72" s="82" t="str">
         <x:v>락스타 클라이밍</x:v>
       </x:c>
-      <x:c r="D72" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E72" s="19" t="str"/>
-      <x:c r="F72" s="19" t="str"/>
-      <x:c r="G72" s="19" t="str"/>
+      <x:c r="D72" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E72" s="82"/>
+      <x:c r="F72" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%9D%BD%EC%8A%A4%ED%83%80%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G72" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H72" s="81"/>
+      <x:c r="I72" s="81"/>
+      <x:c r="J72" s="81"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="19" t="str">
+      <x:c r="A73" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B73" s="19" t="str">
+      <x:c r="B73" s="82" t="str">
         <x:v>HBD-GYM-0072</x:v>
       </x:c>
-      <x:c r="C73" s="19" t="str">
+      <x:c r="C73" s="82" t="str">
         <x:v>루트클라이밍</x:v>
       </x:c>
-      <x:c r="D73" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E73" s="19" t="str"/>
-      <x:c r="F73" s="19" t="str"/>
-      <x:c r="G73" s="19" t="str"/>
+      <x:c r="D73" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E73" s="82"/>
+      <x:c r="F73" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%A3%A8%ED%8A%B8%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G73" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H73" s="81"/>
+      <x:c r="I73" s="81"/>
+      <x:c r="J73" s="81"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="19" t="str">
+      <x:c r="A74" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B74" s="19" t="str">
+      <x:c r="B74" s="82" t="str">
         <x:v>HBD-GYM-0073</x:v>
       </x:c>
-      <x:c r="C74" s="19" t="str">
+      <x:c r="C74" s="82" t="str">
         <x:v>브릭스클라이밍짐</x:v>
       </x:c>
-      <x:c r="D74" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E74" s="19" t="str"/>
-      <x:c r="F74" s="19" t="str"/>
-      <x:c r="G74" s="19" t="str"/>
+      <x:c r="D74" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E74" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dna/QOXKG/btrQ2SwKW62/AAAAAAAAAAAAAAAAAAAAAJQm9XY9MGlLi9n0Y95_r8ndJ84nC7hANH2NNz7-K3WZ/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=tm0dc9M0qA%2FkegMfI4Lj6gufICY%3D</x:v>
+      </x:c>
+      <x:c r="F74" s="82" t="str">
+        <x:v>https://fwfhowe.tistory.com/entry/%EC%86%A1%ED%8C%8C-%EB%B8%8C%EB%A6%AD%EC%8A%A4</x:v>
+      </x:c>
+      <x:c r="G74" s="82" t="str">
+        <x:v>내부 전경 · 브릭스클라이밍짐 실제 방문 후기 사진</x:v>
+      </x:c>
+      <x:c r="H74" s="81"/>
+      <x:c r="I74" s="81"/>
+      <x:c r="J74" s="81"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="19" t="str">
+      <x:c r="A75" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B75" s="19" t="str">
+      <x:c r="B75" s="82" t="str">
         <x:v>HBD-GYM-0074</x:v>
       </x:c>
-      <x:c r="C75" s="19" t="str">
+      <x:c r="C75" s="82" t="str">
         <x:v>서울숲클라이밍 잠실점</x:v>
       </x:c>
-      <x:c r="D75" s="19" t="str">
+      <x:c r="D75" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E75" s="19" t="str">
+      <x:c r="E75" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/uiSJj/btsL4c1rJfd/AAAAAAAAAAAAAAAAAAAAAPPIH2vBQ5Rfvwk_vuk3Fy0MlGZhIbjaQOidCgRbX2-c/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=3bCNHAAVHr%2B3Cb%2FY2F4JR6KRu64%3D</x:v>
       </x:c>
-      <x:c r="F75" s="19" t="str">
+      <x:c r="F75" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EC%84%9C%EC%9A%B8%EC%88%B2%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%9E%A0%EC%8B%A4%EC%A0%90-%EB%8F%84%EC%8B%AC-%EC%86%8D-%EC%A7%9C%EB%A6%BF%ED%95%9C-%EC%95%94%EB%B2%BD-%EC%B2%B4%ED%97%98</x:v>
       </x:c>
-      <x:c r="G75" s="19" t="str">
+      <x:c r="G75" s="82" t="str">
         <x:v>대표 배경/내부</x:v>
       </x:c>
+      <x:c r="H75" s="81"/>
+      <x:c r="I75" s="81"/>
+      <x:c r="J75" s="81"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="19" t="str">
+      <x:c r="A76" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B76" s="19" t="str">
+      <x:c r="B76" s="82" t="str">
         <x:v>HBD-GYM-0075</x:v>
       </x:c>
-      <x:c r="C76" s="19" t="str">
+      <x:c r="C76" s="82" t="str">
         <x:v>에어즈락 클라이밍</x:v>
       </x:c>
-      <x:c r="D76" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E76" s="19" t="str"/>
-      <x:c r="F76" s="19" t="str"/>
-      <x:c r="G76" s="19" t="str"/>
+      <x:c r="D76" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E76" s="82" t="str">
+        <x:v>https://tong.visitkorea.or.kr/cms/resource/15/3054215_image2_1.jpg</x:v>
+      </x:c>
+      <x:c r="F76" s="82" t="str">
+        <x:v>https://data.visitkorea.or.kr/resource/3060932</x:v>
+      </x:c>
+      <x:c r="G76" s="82" t="str">
+        <x:v>내부 전경 · 한국관광공사 에어즈락 클라이밍 위례점 공식 관광 데이터 사진</x:v>
+      </x:c>
+      <x:c r="H76" s="81"/>
+      <x:c r="I76" s="81"/>
+      <x:c r="J76" s="81"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="19" t="str">
+      <x:c r="A77" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B77" s="19" t="str">
+      <x:c r="B77" s="82" t="str">
         <x:v>HBD-GYM-0076</x:v>
       </x:c>
-      <x:c r="C77" s="19" t="str">
+      <x:c r="C77" s="82" t="str">
         <x:v>클라임투더문</x:v>
       </x:c>
-      <x:c r="D77" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E77" s="19" t="str"/>
-      <x:c r="F77" s="19" t="str"/>
-      <x:c r="G77" s="19" t="str"/>
+      <x:c r="D77" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E77" s="82" t="str">
+        <x:v>https://climbatlas.app/api/places/photo/ChIJAabRpqilfDURiyAy04lXW6M/Ab43m-uJAdChQPARb3Q5ROHbWvpJxJNwzGknV0-t8ODGWevU-7CPOjizeUk1A3z7bZJkM3-FrgPwru4aW9a_D0t-rkYu6tz8e3DEfCrf9k7DCCZw8CR_7_2hooOuCsTAAfdqnGsOZfKNGWMm095XoNEIzN7f9VeoLCKCxZglzYsMbl3msh9-tR7pkMxIUAU3dXqY_kKZ4qos-KD_iIyGmUXhv2pDQFfYY9rzKN9liFj4dxIS7xV-4BoZ2Ex7N-4cqqK3d7rEb9JUMWKzeADcm8u3yUQLyWk-xe_vHkVSvf1j1Gk</x:v>
+      </x:c>
+      <x:c r="F77" s="82" t="str">
+        <x:v>https://climbatlas.app/indoor/bouldering/kr/seoulteugbyeolsi/15756/keullaimtudeomun</x:v>
+      </x:c>
+      <x:c r="G77" s="82" t="str">
+        <x:v>ClimbAtlas 지점 페이지·사진 일치</x:v>
+      </x:c>
+      <x:c r="H77" s="81"/>
+      <x:c r="I77" s="81"/>
+      <x:c r="J77" s="81"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="19" t="str">
+      <x:c r="A78" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B78" s="19" t="str">
+      <x:c r="B78" s="82" t="str">
         <x:v>HBD-GYM-0077</x:v>
       </x:c>
-      <x:c r="C78" s="19" t="str">
+      <x:c r="C78" s="82" t="str">
         <x:v>서울볼더스 목동</x:v>
       </x:c>
-      <x:c r="D78" s="19" t="str">
+      <x:c r="D78" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E78" s="19" t="str">
+      <x:c r="E78" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/2JIgG_PdXbe7js59WSqXFAa-Y6OU60r7b7COIczSoRH4Xn7jYrSqBui3b6T5-60lDAN1aUz0B6HDHAOaPujCgRkN0vyCn8sUiYGZ9FHhLEynWeAH4ehvYkNnPZDEFKF9h0VPDXtwRE7xzAtZru0mp6q0ECnLzmxv1DzESnCZghldFj7S4GCBdddGiHKh1cAu?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F78" s="19" t="str"/>
-      <x:c r="G78" s="19" t="str"/>
+      <x:c r="F78" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G78" s="82" t="str"/>
+      <x:c r="H78" s="81"/>
+      <x:c r="I78" s="81"/>
+      <x:c r="J78" s="81"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="19" t="str">
+      <x:c r="A79" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B79" s="19" t="str">
+      <x:c r="B79" s="82" t="str">
         <x:v>HBD-GYM-0078</x:v>
       </x:c>
-      <x:c r="C79" s="19" t="str">
+      <x:c r="C79" s="82" t="str">
         <x:v>YDP오름실내암벽장</x:v>
       </x:c>
-      <x:c r="D79" s="19" t="str">
+      <x:c r="D79" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E79" s="19" t="str">
+      <x:c r="E79" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/XpVs5DMNR_1RY08-zKS8lxOGFoxS-za_BQrs8Ctqxz3EKtF5t-qSd9V0r3TZIMXZzlwCN2cg4UCq8oBafRcdAdCQBmhyr86nMkAu06IDkQe7vxCFl43izVA07U6C4qYefcudHDLRwEsSHbx5dcI9UFXgdGr-jU8T0K06dgorz7X0MljQJqfWl7vLfWcq8p73?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F79" s="19" t="str"/>
-      <x:c r="G79" s="19" t="str"/>
+      <x:c r="F79" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/yeongdeungpo</x:v>
+      </x:c>
+      <x:c r="G79" s="82" t="str"/>
+      <x:c r="H79" s="81"/>
+      <x:c r="I79" s="81"/>
+      <x:c r="J79" s="81"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="19" t="str">
+      <x:c r="A80" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B80" s="19" t="str">
+      <x:c r="B80" s="82" t="str">
         <x:v>HBD-GYM-0079</x:v>
       </x:c>
-      <x:c r="C80" s="19" t="str">
+      <x:c r="C80" s="82" t="str">
         <x:v>더클라임 문래점</x:v>
       </x:c>
-      <x:c r="D80" s="19" t="str">
+      <x:c r="D80" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E80" s="19" t="str">
+      <x:c r="E80" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/YjDvBByA9km6GsKu9MfGTMEhLo-FSOg3Uo3PGPE8_KF5BRAjlCBvzYE8jFlAvfL9scmkx9Mg4I-AIjAyDHmEgdlNADkZ8xRxZ_ijj9ig-qDzmfvJvjCDKz_9OXmhRa9S9VoIaM2VU08BMGmjutO5Dr5iMp1f90GbNev6oKtloXr9_1HkN7ui2HAaX0aWplXd?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F80" s="19" t="str"/>
-      <x:c r="G80" s="19" t="str"/>
+      <x:c r="F80" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/yeongdeungpo</x:v>
+      </x:c>
+      <x:c r="G80" s="82" t="str"/>
+      <x:c r="H80" s="81"/>
+      <x:c r="I80" s="81"/>
+      <x:c r="J80" s="81"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="19" t="str">
+      <x:c r="A81" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B81" s="19" t="str">
+      <x:c r="B81" s="82" t="str">
         <x:v>HBD-GYM-0080</x:v>
       </x:c>
-      <x:c r="C81" s="19" t="str">
+      <x:c r="C81" s="82" t="str">
         <x:v>더플라스틱 클라이밍 문래점</x:v>
       </x:c>
-      <x:c r="D81" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E81" s="19" t="str"/>
-      <x:c r="F81" s="19" t="str"/>
-      <x:c r="G81" s="19" t="str"/>
+      <x:c r="D81" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E81" s="82" t="str">
+        <x:v>https://dnvefa72aowie.cloudfront.net/business/bizPlatform/profile/3940804/1675315393037/QUJERDVCODItOTlDNS00NjM2LUI2QjQtODE1RUUyN0YwQTBBLmpwZWc%3D.jpeg?q=82&amp;s=640x640&amp;t=crop</x:v>
+      </x:c>
+      <x:c r="F81" s="82" t="str">
+        <x:v>https://www.daangn.com/kr/local-profile/%EB%8D%94%ED%94%8C%EB%9D%BC%EC%8A%A4%ED%8B%B1%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EB%AC%B8%EB%9E%98%EC%A0%90-e9zb4kar2o2b/</x:v>
+      </x:c>
+      <x:c r="G81" s="82" t="str">
+        <x:v>당근 동네업체 · 문래점 지점명/주소 일치 · 입구와 내부 벽 확인</x:v>
+      </x:c>
+      <x:c r="H81" s="81"/>
+      <x:c r="I81" s="81"/>
+      <x:c r="J81" s="81"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="19" t="str">
+      <x:c r="A82" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B82" s="19" t="str">
+      <x:c r="B82" s="82" t="str">
         <x:v>HBD-GYM-0081</x:v>
       </x:c>
-      <x:c r="C82" s="19" t="str">
+      <x:c r="C82" s="82" t="str">
         <x:v>서울볼더스 선유</x:v>
       </x:c>
-      <x:c r="D82" s="19" t="str">
+      <x:c r="D82" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E82" s="19" t="str">
+      <x:c r="E82" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/R4pCIe-QiZPX-7caeYXAa2TnRsue_SIRh_1XRr-XmN-YDcJtatN8GAkG3Klvu8bA11l60z-RvEZE0POwy471_qzHhhawaFux3oVHQpF3PLFzqzKIcTntaCbAjnViars9S1a0vbA5Bo9qoyWoUpyV-S8YV1dg0E3ewiYIVyci8SsPbPOD80RfCqI5zF1xvjdN?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F82" s="19" t="str"/>
-      <x:c r="G82" s="19" t="str"/>
+      <x:c r="F82" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/yeongdeungpo</x:v>
+      </x:c>
+      <x:c r="G82" s="82" t="str"/>
+      <x:c r="H82" s="81"/>
+      <x:c r="I82" s="81"/>
+      <x:c r="J82" s="81"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="19" t="str">
+      <x:c r="A83" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B83" s="19" t="str">
+      <x:c r="B83" s="82" t="str">
         <x:v>HBD-GYM-0082</x:v>
       </x:c>
-      <x:c r="C83" s="19" t="str">
+      <x:c r="C83" s="82" t="str">
         <x:v>서울숲클라이밍 영등포점</x:v>
       </x:c>
-      <x:c r="D83" s="19" t="str">
+      <x:c r="D83" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E83" s="19" t="str">
+      <x:c r="E83" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/Bwmx4Zd5YcRFqtU0rcIHbl9mu-IB9GuhkFHgJZPFremSUYtZ937JfEpksnpbuEKGVI1hs9_BK8jXsKTP5fhBEAcK9d6vWXDQp-XCoweBJM1upfjaSYZojqvMXRlZtHlQKqpmqaQNm7jwdHR7VyrHOUe-a6mmmTZBRCZZVs__P44MoCL3RAacrVNwp-NgrMJC?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F83" s="19" t="str"/>
-      <x:c r="G83" s="19" t="str"/>
+      <x:c r="F83" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/yeongdeungpo</x:v>
+      </x:c>
+      <x:c r="G83" s="82" t="str"/>
+      <x:c r="H83" s="81"/>
+      <x:c r="I83" s="81"/>
+      <x:c r="J83" s="81"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="19" t="str">
+      <x:c r="A84" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B84" s="19" t="str">
+      <x:c r="B84" s="82" t="str">
         <x:v>HBD-GYM-0083</x:v>
       </x:c>
-      <x:c r="C84" s="19" t="str">
+      <x:c r="C84" s="82" t="str">
         <x:v>알레클라임 영등포점</x:v>
       </x:c>
-      <x:c r="D84" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E84" s="19" t="str"/>
-      <x:c r="F84" s="19" t="str"/>
-      <x:c r="G84" s="19" t="str"/>
+      <x:c r="D84" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E84" s="82"/>
+      <x:c r="F84" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/yeongdeungpo</x:v>
+      </x:c>
+      <x:c r="G84" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H84" s="81"/>
+      <x:c r="I84" s="81"/>
+      <x:c r="J84" s="81"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="19" t="str">
+      <x:c r="A85" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B85" s="19" t="str">
+      <x:c r="B85" s="82" t="str">
         <x:v>HBD-GYM-0084</x:v>
       </x:c>
-      <x:c r="C85" s="19" t="str">
+      <x:c r="C85" s="82" t="str">
         <x:v>클라임웍스</x:v>
       </x:c>
-      <x:c r="D85" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E85" s="19" t="str"/>
-      <x:c r="F85" s="19" t="str"/>
-      <x:c r="G85" s="19" t="str"/>
+      <x:c r="D85" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E85" s="82" t="str">
+        <x:v>https://img1.daumcdn.net/thumb/R658x0.q70/?fname=https%3A%2F%2Ft1.daumcdn.net%2Fnews%2F202603%2F12%2Fsan%2F20260312075703101dnqz.jpg</x:v>
+      </x:c>
+      <x:c r="F85" s="82" t="str">
+        <x:v>https://v.daum.net/v/20260312075643531</x:v>
+      </x:c>
+      <x:c r="G85" s="82" t="str">
+        <x:v>내부 전경 · 2026.03 기사에서 클라임웍스 영등포(버드나루로 85) 캡션 매칭</x:v>
+      </x:c>
+      <x:c r="H85" s="81"/>
+      <x:c r="I85" s="81"/>
+      <x:c r="J85" s="81"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="19" t="str">
+      <x:c r="A86" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B86" s="19" t="str">
+      <x:c r="B86" s="82" t="str">
         <x:v>HBD-GYM-0085</x:v>
       </x:c>
-      <x:c r="C86" s="19" t="str">
+      <x:c r="C86" s="82" t="str">
         <x:v>볼더룸</x:v>
       </x:c>
-      <x:c r="D86" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E86" s="19" t="str"/>
-      <x:c r="F86" s="19" t="str"/>
-      <x:c r="G86" s="19" t="str"/>
+      <x:c r="D86" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E86" s="82" t="str">
+        <x:v>https://img.vogue.co.kr/vogue/2024/04/style_660d04a3e665d-744x930.jpg</x:v>
+      </x:c>
+      <x:c r="F86" s="82" t="str">
+        <x:v>https://www.vogue.co.kr/2024/04/03/%EA%B0%95%EB%AF%BC%EA%B2%BD%EB%B6%80%ED%84%B0-%EC%95%88%EC%86%8C%ED%9D%AC%EA%B9%8C%EC%A7%80-%EC%85%80%EB%9F%BD-pick-%EC%B9%B4%ED%8E%98-3/</x:v>
+      </x:c>
+      <x:c r="G86" s="82" t="str">
+        <x:v>외관/간판 · 볼더룸 주소(임정로13길 6)와 기사 내 지점명 매칭</x:v>
+      </x:c>
+      <x:c r="H86" s="81"/>
+      <x:c r="I86" s="81"/>
+      <x:c r="J86" s="81"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="19" t="str">
+      <x:c r="A87" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B87" s="19" t="str">
+      <x:c r="B87" s="82" t="str">
         <x:v>HBD-GYM-0086</x:v>
       </x:c>
-      <x:c r="C87" s="19" t="str">
+      <x:c r="C87" s="82" t="str">
         <x:v>오프더월클라이밍</x:v>
       </x:c>
-      <x:c r="D87" s="19" t="str">
+      <x:c r="D87" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E87" s="19" t="str">
+      <x:c r="E87" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/C8oVLRNt8IC1qWVPdhjOL7wF1aRnOM5hb4bYUqynRVfdCmGL7ptQqRWxTzgeqKlTDQ0FtQmLQ8zIFSAsXrCHZTUbt6q7CKRRgrIWdqckvdXnRehUfsHV7WATogTUaIdnAmY8D0xCZT_7AzkgG8IoacpdHh76MqOloaPv4MuY1ipPPe_48y6cqiLG0o2clQfv?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F87" s="19" t="str"/>
-      <x:c r="G87" s="19" t="str"/>
+      <x:c r="F87" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G87" s="82" t="str"/>
+      <x:c r="H87" s="81"/>
+      <x:c r="I87" s="81"/>
+      <x:c r="J87" s="81"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="19" t="str">
+      <x:c r="A88" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B88" s="19" t="str">
+      <x:c r="B88" s="82" t="str">
         <x:v>HBD-GYM-0087</x:v>
       </x:c>
-      <x:c r="C88" s="19" t="str">
+      <x:c r="C88" s="82" t="str">
         <x:v>치즈 클라이밍</x:v>
       </x:c>
-      <x:c r="D88" s="19" t="str">
+      <x:c r="D88" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E88" s="19" t="str">
+      <x:c r="E88" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/od4aB/btsrEsohWzh/AAAAAAAAAAAAAAAAAAAAAPr8L4R5cC-BFtis9JSgK2wW7CqaaiMp2eLZ3aRaS9nm/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=Bz0IgmhoJ0Gc8WKVz%2FRrpD4gGvs%3D</x:v>
       </x:c>
-      <x:c r="F88" s="19" t="str">
+      <x:c r="F88" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EC%B9%98%EC%A6%88%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
       </x:c>
-      <x:c r="G88" s="19" t="str">
+      <x:c r="G88" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H88" s="81"/>
+      <x:c r="I88" s="81"/>
+      <x:c r="J88" s="81"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="19" t="str">
+      <x:c r="A89" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B89" s="19" t="str">
+      <x:c r="B89" s="82" t="str">
         <x:v>HBD-GYM-0088</x:v>
       </x:c>
-      <x:c r="C89" s="19" t="str">
+      <x:c r="C89" s="82" t="str">
         <x:v>써니사이드클라이밍</x:v>
       </x:c>
-      <x:c r="D89" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E89" s="19" t="str"/>
-      <x:c r="F89" s="19" t="str"/>
-      <x:c r="G89" s="19" t="str"/>
+      <x:c r="D89" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E89" s="82"/>
+      <x:c r="F89" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G89" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H89" s="81"/>
+      <x:c r="I89" s="81"/>
+      <x:c r="J89" s="81"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="19" t="str">
+      <x:c r="A90" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B90" s="19" t="str">
+      <x:c r="B90" s="82" t="str">
         <x:v>HBD-GYM-0089</x:v>
       </x:c>
-      <x:c r="C90" s="19" t="str">
+      <x:c r="C90" s="82" t="str">
         <x:v>행클라임 클라이밍짐 구파발점</x:v>
       </x:c>
-      <x:c r="D90" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E90" s="19" t="str"/>
-      <x:c r="F90" s="19" t="str"/>
-      <x:c r="G90" s="19" t="str"/>
+      <x:c r="D90" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E90" s="82"/>
+      <x:c r="F90" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G90" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H90" s="81"/>
+      <x:c r="I90" s="81"/>
+      <x:c r="J90" s="81"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="19" t="str">
+      <x:c r="A91" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B91" s="19" t="str">
+      <x:c r="B91" s="82" t="str">
         <x:v>HBD-GYM-0090</x:v>
       </x:c>
-      <x:c r="C91" s="19" t="str">
+      <x:c r="C91" s="82" t="str">
         <x:v>서울숲클라이밍 종로점</x:v>
       </x:c>
-      <x:c r="D91" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E91" s="19" t="str"/>
-      <x:c r="F91" s="19" t="str"/>
-      <x:c r="G91" s="19" t="str"/>
+      <x:c r="D91" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E91" s="82" t="str">
+        <x:v>https://img3.daumcdn.net/thumb/R658x0.q70/?fname=https%3A%2F%2Ft1.daumcdn.net%2Fnews%2F202507%2F08%2Fsan%2F20250708072701455htir.jpg</x:v>
+      </x:c>
+      <x:c r="F91" s="82" t="str">
+        <x:v>https://v.daum.net/v/20250708072631560?s=print_news</x:v>
+      </x:c>
+      <x:c r="G91" s="82" t="str">
+        <x:v>내부 전경 · 기사 사진 캡션에서 서울숲클라이밍 종로점 지점 매칭</x:v>
+      </x:c>
+      <x:c r="H91" s="81"/>
+      <x:c r="I91" s="81"/>
+      <x:c r="J91" s="81"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="19" t="str">
+      <x:c r="A92" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B92" s="19" t="str">
+      <x:c r="B92" s="82" t="str">
         <x:v>HBD-GYM-0091</x:v>
       </x:c>
-      <x:c r="C92" s="19" t="str">
+      <x:c r="C92" s="82" t="str">
         <x:v>알레클라이밍 혜화점</x:v>
       </x:c>
-      <x:c r="D92" s="19" t="str">
+      <x:c r="D92" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E92" s="19" t="str">
+      <x:c r="E92" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/HcpAaLS9ouAjbPR9O29nGn_9NaOe2wZ1Q3TemT8S4j2ucNdM9MQL3jKbBLQWIFQkWhvQZrzQh2zGoBRWe3A2q0hkHulxrphwJVIIhimU65e8vfgLRDSNVm0akrDbUr_k_A9HTum9Ha4Qi-MyI7iiWJfQDfLYfZtmR3FNi2XsVgMLK8lheSl4lm8DsnLkuD0c?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F92" s="19" t="str"/>
-      <x:c r="G92" s="19" t="str"/>
+      <x:c r="F92" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G92" s="82" t="str"/>
+      <x:c r="H92" s="81"/>
+      <x:c r="I92" s="81"/>
+      <x:c r="J92" s="81"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="19" t="str">
+      <x:c r="A93" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B93" s="19" t="str">
+      <x:c r="B93" s="82" t="str">
         <x:v>HBD-GYM-0092</x:v>
       </x:c>
-      <x:c r="C93" s="19" t="str">
+      <x:c r="C93" s="82" t="str">
         <x:v>클라이밍파크 종로점</x:v>
       </x:c>
-      <x:c r="D93" s="19" t="str">
+      <x:c r="D93" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E93" s="19" t="str">
+      <x:c r="E93" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/bdSKZX/btroYk1nnfL/AAAAAAAAAAAAAAAAAAAAAP03f8CFWopoZ-fNhWXLtGdoPiflOz6gQkiyvfFr1aMo/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1774969199&amp;signature=d9Aygxg99CPySCqJILNeCOXVxSw%3D</x:v>
       </x:c>
-      <x:c r="F93" s="19" t="str">
+      <x:c r="F93" s="82" t="str">
         <x:v>https://seoulchoi.tistory.com/10</x:v>
       </x:c>
-      <x:c r="G93" s="19" t="str">
+      <x:c r="G93" s="82" t="str">
         <x:v>기존 외관 후보를 내부 전경으로 교체</x:v>
       </x:c>
+      <x:c r="H93" s="81"/>
+      <x:c r="I93" s="81"/>
+      <x:c r="J93" s="81"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="19" t="str">
+      <x:c r="A94" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B94" s="19" t="str">
+      <x:c r="B94" s="82" t="str">
         <x:v>HBD-GYM-0093</x:v>
       </x:c>
-      <x:c r="C94" s="19" t="str">
+      <x:c r="C94" s="82" t="str">
         <x:v>피커스 클라이밍 종로점</x:v>
       </x:c>
-      <x:c r="D94" s="19" t="str">
+      <x:c r="D94" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E94" s="19" t="str">
+      <x:c r="E94" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/V-LY5RIMU8tVpf8CDRI-tzo5IwTPjxbIi3f6pqrT0xzSNcECyb40uCPjqhinwR78Hif9GHV-Uez3M5OV1Flsn2JqAntxAmbvng3LhmPjO2EZ2wN4R6wzBIxXm1tbcbFFVNJX_aQ-6tHb56bzT7BT0Ye_3MNNDdtYgSfkAsYZp77t7rPZrhUMvPkoAwgyXOWL?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F94" s="19" t="str"/>
-      <x:c r="G94" s="19" t="str"/>
+      <x:c r="F94" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%94%BC%EC%BB%A4%EC%8A%A4%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EC%A2%85%EB%A1%9C%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G94" s="82" t="str"/>
+      <x:c r="H94" s="81"/>
+      <x:c r="I94" s="81"/>
+      <x:c r="J94" s="81"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="19" t="str">
+      <x:c r="A95" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B95" s="19" t="str">
+      <x:c r="B95" s="82" t="str">
         <x:v>HBD-GYM-0094</x:v>
       </x:c>
-      <x:c r="C95" s="19" t="str">
+      <x:c r="C95" s="82" t="str">
         <x:v>손상원 클라이밍짐 을지로점</x:v>
       </x:c>
-      <x:c r="D95" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E95" s="19" t="str"/>
-      <x:c r="F95" s="19" t="str"/>
-      <x:c r="G95" s="19" t="str"/>
+      <x:c r="D95" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E95" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dna/bo7Jy4/dJMcah3VAjI/AAAAAAAAAAAAAAAAAAAAAKy5ibCFBAwHLj3lYukOhuN0pBEnyfIlg517uGdJfWIc/tfile.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=lHPmsq6XtMsZ1CQ8l3iu5vzKOmM%3D</x:v>
+      </x:c>
+      <x:c r="F95" s="82" t="str">
+        <x:v>https://creamystar.tistory.com/2035</x:v>
+      </x:c>
+      <x:c r="G95" s="82" t="str">
+        <x:v>내부 전경 · Son Climb 간판이 보이는 을지로점 방문 후기 사진</x:v>
+      </x:c>
+      <x:c r="H95" s="81"/>
+      <x:c r="I95" s="81"/>
+      <x:c r="J95" s="81"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="19" t="str">
+      <x:c r="A96" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B96" s="19" t="str">
+      <x:c r="B96" s="82" t="str">
         <x:v>HBD-GYM-0095</x:v>
       </x:c>
-      <x:c r="C96" s="19" t="str">
+      <x:c r="C96" s="82" t="str">
         <x:v>을지로 담장 클라이밍</x:v>
       </x:c>
-      <x:c r="D96" s="19" t="str">
+      <x:c r="D96" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E96" s="19" t="str">
+      <x:c r="E96" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/cvduBK/btrJikBTdoI/AAAAAAAAAAAAAAAAAAAAAH91nDmOx2fx8dnCBbxctsFsIb8Yif4bZbhBPlu284KV/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=ooM5XrTLrKrfHIH20BehbdH5ieM%3D</x:v>
       </x:c>
-      <x:c r="F96" s="19" t="str">
+      <x:c r="F96" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EC%9D%84%EC%A7%80%EB%A1%9C-%EB%8B%B4%EC%9E%A5</x:v>
       </x:c>
-      <x:c r="G96" s="19" t="str">
+      <x:c r="G96" s="82" t="str">
         <x:v>내부 전경</x:v>
       </x:c>
+      <x:c r="H96" s="81"/>
+      <x:c r="I96" s="81"/>
+      <x:c r="J96" s="81"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="19" t="str">
+      <x:c r="A97" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B97" s="19" t="str">
+      <x:c r="B97" s="82" t="str">
         <x:v>HBD-GYM-0096</x:v>
       </x:c>
-      <x:c r="C97" s="19" t="str">
+      <x:c r="C97" s="82" t="str">
         <x:v>플래시볼더스 클라이밍</x:v>
       </x:c>
-      <x:c r="D97" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E97" s="19" t="str"/>
-      <x:c r="F97" s="19" t="str"/>
-      <x:c r="G97" s="19" t="str"/>
+      <x:c r="D97" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E97" s="82"/>
+      <x:c r="F97" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G97" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H97" s="81"/>
+      <x:c r="I97" s="81"/>
+      <x:c r="J97" s="81"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="19" t="str">
+      <x:c r="A98" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B98" s="19" t="str">
+      <x:c r="B98" s="82" t="str">
         <x:v>HBD-GYM-0097</x:v>
       </x:c>
-      <x:c r="C98" s="19" t="str">
+      <x:c r="C98" s="82" t="str">
         <x:v>마스터클라이밍</x:v>
       </x:c>
-      <x:c r="D98" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E98" s="19" t="str"/>
-      <x:c r="F98" s="19" t="str"/>
-      <x:c r="G98" s="19" t="str"/>
+      <x:c r="D98" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E98" s="82"/>
+      <x:c r="F98" s="82" t="str">
+        <x:v>https://climbmap.life/places/kr/seoul/indoor/bouldering</x:v>
+      </x:c>
+      <x:c r="G98" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H98" s="81"/>
+      <x:c r="I98" s="81"/>
+      <x:c r="J98" s="81"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="19" t="str">
+      <x:c r="A99" s="82" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B99" s="19" t="str">
+      <x:c r="B99" s="82" t="str">
         <x:v>HBD-GYM-0098</x:v>
       </x:c>
-      <x:c r="C99" s="19" t="str">
+      <x:c r="C99" s="82" t="str">
         <x:v>크래커 클라이밍</x:v>
       </x:c>
-      <x:c r="D99" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E99" s="19" t="str"/>
-      <x:c r="F99" s="19" t="str"/>
-      <x:c r="G99" s="19" t="str"/>
+      <x:c r="D99" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E99" s="82" t="str">
+        <x:v>https://spiri7.com/_next/image?q=75&amp;url=https%3A%2F%2Fspirit-files-bucket.s3.ap-northeast-2.amazonaws.com%2F4j5v01lsek6srxs3mabiptziuw75&amp;w=3840</x:v>
+      </x:c>
+      <x:c r="F99" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%AC%EB%9E%98%EC%BB%A4%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G99" s="82" t="str">
+        <x:v>내부 볼더링 벽 · 상봉 크래커클라이밍 주소/2026 운영정보와 지점 매칭</x:v>
+      </x:c>
+      <x:c r="H99" s="81"/>
+      <x:c r="I99" s="81"/>
+      <x:c r="J99" s="81"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="19" t="str">
+      <x:c r="A100" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B100" s="19" t="str">
+      <x:c r="B100" s="82" t="str">
         <x:v>HBD-GYM-0099</x:v>
       </x:c>
-      <x:c r="C100" s="19" t="str">
+      <x:c r="C100" s="82" t="str">
         <x:v>더클라임 일산점</x:v>
       </x:c>
-      <x:c r="D100" s="19" t="str">
+      <x:c r="D100" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E100" s="19" t="str">
+      <x:c r="E100" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/MHiNshLJ7Ze8wL5Gkk7jVMOQgCCkaRUFMkC2yONvHkympc0DK_LrCmBl6AjTX4lgi3n35wkdqX7jBoMZB-r3jE06CJt256ySTX-nCjGrnI2UopX8OgmHYYxHpnX80P0vcEhVZirSpSgPoOidVzzzM9fQywEnfacohGxSHq14tcYXVUr3KiR8H757hEnUiryJ?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F100" s="19" t="str"/>
-      <x:c r="G100" s="19" t="str"/>
+      <x:c r="F100" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%8D%94%ED%81%B4%EB%9D%BC%EC%9E%84%20%EC%9D%BC%EC%82%B0%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G100" s="82" t="str"/>
+      <x:c r="H100" s="81"/>
+      <x:c r="I100" s="81"/>
+      <x:c r="J100" s="81"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="19" t="str">
+      <x:c r="A101" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B101" s="19" t="str">
+      <x:c r="B101" s="82" t="str">
         <x:v>HBD-GYM-0100</x:v>
       </x:c>
-      <x:c r="C101" s="19" t="str">
+      <x:c r="C101" s="82" t="str">
         <x:v>일산SK클라이밍</x:v>
       </x:c>
-      <x:c r="D101" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E101" s="19" t="str"/>
-      <x:c r="F101" s="19" t="str"/>
-      <x:c r="G101" s="19" t="str"/>
+      <x:c r="D101" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E101" s="82" t="str">
+        <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEihFwRtJwSSyQqTbdJ2dP4z3_9yHILhtRnk3XKN-JrKvIc-Cu0JPtgX7S1m1e3Nyo_kMFMtX3GH9dNVwm5ot1dtjfDs9OE2xw60RdHd1J1q3R2atTsh8ARRvqbB9eEkL_ietkyYDvjt92SG/s320/SK%2BClimbing%2BCenter%2B%2528SK%2B%25E1%2584%258F%25E1%2585%25B3%25E1%2586%25AF%25E1%2584%2585%25E1%2585%25A1%25E1%2584%258B%25E1%2585%25B5%25E1%2584%2586%25E1%2585%25B5%25E1%2586%25BC%2B%25E1%2584%2589%25E1%2585%25A6%25E1%2586%25AB%25E1%2584%2590%25E1%2585%25A5%2529%2B.jpg</x:v>
+      </x:c>
+      <x:c r="F101" s="82" t="str">
+        <x:v>https://climbinginkorea.blogspot.com/2018/04/sk-climbing-center-sk.html</x:v>
+      </x:c>
+      <x:c r="G101" s="82" t="str">
+        <x:v>일산SK클라이밍 지점·주소 일치, 과거 실내 사진</x:v>
+      </x:c>
+      <x:c r="H101" s="81"/>
+      <x:c r="I101" s="81"/>
+      <x:c r="J101" s="81"/>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="19" t="str">
+      <x:c r="A102" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B102" s="19" t="str">
+      <x:c r="B102" s="82" t="str">
         <x:v>HBD-GYM-0101</x:v>
       </x:c>
-      <x:c r="C102" s="19" t="str">
+      <x:c r="C102" s="82" t="str">
         <x:v>일산클라이밍센터</x:v>
       </x:c>
-      <x:c r="D102" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E102" s="19" t="str"/>
-      <x:c r="F102" s="19" t="str"/>
-      <x:c r="G102" s="19" t="str"/>
+      <x:c r="D102" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E102" s="82" t="str">
+        <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEhPE_xz7HEJvf1C1w_e6jj_Lyu6h9wkBUscEfscaC3IJ1_PGZ-EukzagwNa9POxB_XQ7yY6LuUY9ocgnhe_hK-VNleu_Qakdy3YV_jaV1hVu5T4lZa4RFDKAqv3dvXmQMQGkvGr8s7fC3-g/s320/Ilsan%2BClimbing%2BCenter%2B%2528%25E1%2584%258B%25E1%2585%25B5%25E1%2586%25AF%25E1%2584%2589%25E1%2585%25A1%25E1%2586%25AB%2B%25E1%2584%258F%25E1%2585%25B3%25E1%2586%25AF%25E1%2584%2585%25E1%2585%25A1%25E1%2584%258B%25E1%2585%25B5%25E1%2584%2586%25E1%2585%25B5%25E1%2586%25BC%2B%25E1%2584%2589%25E1%2585%25A6%25E1%2586%25AB%25E1%2584%2590%25E1%2585%25A5%2529.jpg</x:v>
+      </x:c>
+      <x:c r="F102" s="82" t="str">
+        <x:v>https://climbinginkorea.blogspot.com/2018/04/ilsan-climbing-center.html</x:v>
+      </x:c>
+      <x:c r="G102" s="82" t="str">
+        <x:v>일산클라이밍센터 지점·주소 일치, 과거 지점 이미지</x:v>
+      </x:c>
+      <x:c r="H102" s="81"/>
+      <x:c r="I102" s="81"/>
+      <x:c r="J102" s="81"/>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="19" t="str">
+      <x:c r="A103" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B103" s="19" t="str">
+      <x:c r="B103" s="82" t="str">
         <x:v>HBD-GYM-0102</x:v>
       </x:c>
-      <x:c r="C103" s="19" t="str">
+      <x:c r="C103" s="82" t="str">
         <x:v>코알라클라이밍 킨텍스점</x:v>
       </x:c>
-      <x:c r="D103" s="19" t="str">
+      <x:c r="D103" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E103" s="19" t="str">
+      <x:c r="E103" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/bjFUrz/btsNlXPYNZY/AAAAAAAAAAAAAAAAAAAAAG1pS1rqHogyGoECYWlDCFfoPxOpuVuv2nlBU6-V4f14/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=uVqFvRRVHxb4Vxn9p6nQ05wNLP0%3D</x:v>
       </x:c>
-      <x:c r="F103" s="19" t="str">
+      <x:c r="F103" s="82" t="str">
         <x:v>https://start2025.tistory.com/77</x:v>
       </x:c>
-      <x:c r="G103" s="19" t="str">
+      <x:c r="G103" s="82" t="str">
         <x:v>내부 섹터 사진</x:v>
       </x:c>
+      <x:c r="H103" s="81"/>
+      <x:c r="I103" s="81"/>
+      <x:c r="J103" s="81"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="19" t="str">
+      <x:c r="A104" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B104" s="19" t="str">
+      <x:c r="B104" s="82" t="str">
         <x:v>HBD-GYM-0103</x:v>
       </x:c>
-      <x:c r="C104" s="19" t="str">
+      <x:c r="C104" s="82" t="str">
         <x:v>클라이밍 업더월</x:v>
       </x:c>
-      <x:c r="D104" s="19" t="str">
+      <x:c r="D104" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E104" s="19" t="str">
+      <x:c r="E104" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/oQV9a/btstr238d0W/AAAAAAAAAAAAAAAAAAAAADynLLGnQIQjmpoSNNJHaqI8VFdLyzeVBIDGN5f5U_No/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1782831599&amp;signature=C3WMOXEo3DMgF6ucpEdEQvekGbY%3D</x:v>
       </x:c>
-      <x:c r="F104" s="19" t="str">
+      <x:c r="F104" s="82" t="str">
         <x:v>https://fwfhowe.tistory.com/entry/%EC%97%85%EB%8D%94%EC%9B%94</x:v>
       </x:c>
-      <x:c r="G104" s="19" t="str">
+      <x:c r="G104" s="82" t="str">
         <x:v>일산 업더월 내부</x:v>
       </x:c>
+      <x:c r="H104" s="81"/>
+      <x:c r="I104" s="81"/>
+      <x:c r="J104" s="81"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="19" t="str">
+      <x:c r="A105" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B105" s="19" t="str">
+      <x:c r="B105" s="82" t="str">
         <x:v>HBD-GYM-0104</x:v>
       </x:c>
-      <x:c r="C105" s="19" t="str">
+      <x:c r="C105" s="82" t="str">
         <x:v>클라이밍 하이프렉스</x:v>
       </x:c>
-      <x:c r="D105" s="19" t="str">
+      <x:c r="D105" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E105" s="19" t="str">
+      <x:c r="E105" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/Dk2RsmXE3n4dguHr0-539MJgZO8ReULSvzsYwAS3-dg4NxawLD8Oq2kV4jvpGuqrTndex0aH_iSLiZL6CwvsScgw_4dufPyI04-q28zeMxbXBdfWSM8NpXlj7WGEEBY6HleVj6H5fBIyPq5q-C-VnAI4CKEK2QJDYrhhaelwRQD5vnEhwkaJcbPNV-mocdxy?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F105" s="19" t="str"/>
-      <x:c r="G105" s="19" t="str"/>
+      <x:c r="F105" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%ED%95%98%EC%9D%B4%ED%94%84%EB%A0%89%EC%8A%A4</x:v>
+      </x:c>
+      <x:c r="G105" s="82" t="str"/>
+      <x:c r="H105" s="81"/>
+      <x:c r="I105" s="81"/>
+      <x:c r="J105" s="81"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="19" t="str">
+      <x:c r="A106" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B106" s="19" t="str">
+      <x:c r="B106" s="82" t="str">
         <x:v>HBD-GYM-0105</x:v>
       </x:c>
-      <x:c r="C106" s="19" t="str">
+      <x:c r="C106" s="82" t="str">
         <x:v>페퍼클라이밍</x:v>
       </x:c>
-      <x:c r="D106" s="19" t="str">
+      <x:c r="D106" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E106" s="19" t="str">
+      <x:c r="E106" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/ZqFsO/btsL5OMJMSO/AAAAAAAAAAAAAAAAAAAAAM12OI0h9MSj9Qj8YsyfDyJyd6FJZ_vudQxGbrBFtfT6/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=%2FznGhDBniQtu3RitXEpepomDcag%3D</x:v>
       </x:c>
-      <x:c r="F106" s="19" t="str">
+      <x:c r="F106" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%B4%88%EB%B3%B4%EB%B6%80%ED%84%B0-%EA%B3%A0%EC%88%98%EA%B9%8C%EC%A7%80-%ED%8E%98%ED%8D%BC%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%9B%90%ED%9D%A5%EC%A0%90%EC%97%90%EC%84%9C-%EB%8F%84%EC%A0%84%ED%95%98%EB%9D%BC</x:v>
       </x:c>
-      <x:c r="G106" s="19" t="str">
+      <x:c r="G106" s="82" t="str">
         <x:v>원흥점 내부 사진</x:v>
       </x:c>
+      <x:c r="H106" s="81"/>
+      <x:c r="I106" s="81"/>
+      <x:c r="J106" s="81"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" s="19" t="str">
+      <x:c r="A107" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B107" s="19" t="str">
+      <x:c r="B107" s="82" t="str">
         <x:v>HBD-GYM-0113</x:v>
       </x:c>
-      <x:c r="C107" s="19" t="str">
+      <x:c r="C107" s="82" t="str">
         <x:v>디스커버리 클라임스퀘어 구래점</x:v>
       </x:c>
-      <x:c r="D107" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E107" s="19" t="str"/>
-      <x:c r="F107" s="19" t="str"/>
-      <x:c r="G107" s="19" t="str"/>
+      <x:c r="D107" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E107" s="82"/>
+      <x:c r="F107" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%94%94%EC%8A%A4%EC%BB%A4%EB%B2%84%EB%A6%AC%20%ED%81%B4%EB%9D%BC%EC%9E%84%EC%8A%A4%ED%80%98%EC%96%B4%20%EA%B5%AC%EB%9E%98%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G107" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H107" s="81"/>
+      <x:c r="I107" s="81"/>
+      <x:c r="J107" s="81"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" s="19" t="str">
+      <x:c r="A108" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B108" s="19" t="str">
+      <x:c r="B108" s="82" t="str">
         <x:v>HBD-GYM-0114</x:v>
       </x:c>
-      <x:c r="C108" s="19" t="str">
+      <x:c r="C108" s="82" t="str">
         <x:v>잼클라이밍</x:v>
       </x:c>
-      <x:c r="D108" s="19" t="str">
+      <x:c r="D108" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E108" s="19" t="str">
+      <x:c r="E108" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/cAPhIr/btsL9rKZVpJ/AAAAAAAAAAAAAAAAAAAAABzHc1VOA1n3r5_UC7KDzLwfntBp4vg7OgtiPlmtMU6E/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1777561199&amp;signature=feFvI85EDnYAvxn5yUzQiDyG4ZY%3D</x:v>
       </x:c>
-      <x:c r="F108" s="19" t="str">
+      <x:c r="F108" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EA%B9%80%ED%8F%AC%EC%97%90%EC%84%9C-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%9D%84-%EC%A6%90%EA%B8%B4%EB%8B%A4%EB%A9%B4-%EC%9E%BC%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%9D%B4-%EB%8B%B5%EC%9D%B4%EB%8B%A4</x:v>
       </x:c>
-      <x:c r="G108" s="19" t="str">
+      <x:c r="G108" s="82" t="str">
         <x:v>김포 잼클라이밍 내부</x:v>
       </x:c>
+      <x:c r="H108" s="81"/>
+      <x:c r="I108" s="81"/>
+      <x:c r="J108" s="81"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" s="19" t="str">
+      <x:c r="A109" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B109" s="19" t="str">
+      <x:c r="B109" s="82" t="str">
         <x:v>HBD-GYM-0115</x:v>
       </x:c>
-      <x:c r="C109" s="19" t="str">
+      <x:c r="C109" s="82" t="str">
         <x:v>키클 클라이밍 풍무점</x:v>
       </x:c>
-      <x:c r="D109" s="19" t="str">
+      <x:c r="D109" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E109" s="19" t="str">
+      <x:c r="E109" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/nol1K/btsL9QRa3pE/AAAAAAAAAAAAAAAAAAAAACKK_46SihzSd3A2MJYYPnSxJize4s_pgU31cRbEDph4/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1780239599&amp;signature=iFKEYmumb6geBF34ADUylFghbQs%3D</x:v>
       </x:c>
-      <x:c r="F109" s="19" t="str">
+      <x:c r="F109" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EA%B9%80%ED%8F%AC%EC%97%90%EC%84%9C-%EB%A7%8C%EB%82%98%EB%8A%94-%EC%8B%A4%EB%82%B4-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EB%AA%85%EC%86%8C-%ED%82%A4%ED%81%B4-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%ED%92%8D%EB%AC%B4%EC%A0%90</x:v>
       </x:c>
-      <x:c r="G109" s="19" t="str">
+      <x:c r="G109" s="82" t="str">
         <x:v>풍무점 내부 사진</x:v>
       </x:c>
+      <x:c r="H109" s="81"/>
+      <x:c r="I109" s="81"/>
+      <x:c r="J109" s="81"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" s="19" t="str">
+      <x:c r="A110" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B110" s="19" t="str">
+      <x:c r="B110" s="82" t="str">
         <x:v>HBD-GYM-0116</x:v>
       </x:c>
-      <x:c r="C110" s="19" t="str">
+      <x:c r="C110" s="82" t="str">
         <x:v>픽클라이밍</x:v>
       </x:c>
-      <x:c r="D110" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E110" s="19" t="str"/>
-      <x:c r="F110" s="19" t="str"/>
-      <x:c r="G110" s="19" t="str"/>
+      <x:c r="D110" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E110" s="82"/>
+      <x:c r="F110" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%94%BD%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G110" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H110" s="81"/>
+      <x:c r="I110" s="81"/>
+      <x:c r="J110" s="81"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" s="19" t="str">
+      <x:c r="A111" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B111" s="19" t="str">
+      <x:c r="B111" s="82" t="str">
         <x:v>HBD-GYM-0122</x:v>
       </x:c>
-      <x:c r="C111" s="19" t="str">
+      <x:c r="C111" s="82" t="str">
         <x:v>부천 클라이밍센터</x:v>
       </x:c>
-      <x:c r="D111" s="19" t="str">
+      <x:c r="D111" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E111" s="19" t="str">
+      <x:c r="E111" s="82" t="str">
         <x:v>https://dnvefa72aowie.cloudfront.net/origin/article/202007/bf7ebe4493ae6c0d2f8a063240c95b0a3ba7363daff5cf153ec01b224a284b1d.webp?q=95&amp;s=1440x1440&amp;t=inside</x:v>
       </x:c>
-      <x:c r="F111" s="19" t="str">
+      <x:c r="F111" s="82" t="str">
         <x:v>https://www.daangn.com/kr/business-post/%EB%B6%80%EC%B2%9C%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%8B%A4%EB%82%B4%EC%95%94%EB%B2%BD-6bdhivzhhud4/</x:v>
       </x:c>
-      <x:c r="G111" s="19" t="str">
+      <x:c r="G111" s="82" t="str">
         <x:v>부천 상동 내부 전경</x:v>
       </x:c>
+      <x:c r="H111" s="81"/>
+      <x:c r="I111" s="81"/>
+      <x:c r="J111" s="81"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" s="19" t="str">
+      <x:c r="A112" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B112" s="19" t="str">
+      <x:c r="B112" s="82" t="str">
         <x:v>HBD-GYM-0123</x:v>
       </x:c>
-      <x:c r="C112" s="19" t="str">
+      <x:c r="C112" s="82" t="str">
         <x:v>월드클라이밍</x:v>
       </x:c>
-      <x:c r="D112" s="19" t="str">
+      <x:c r="D112" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E112" s="19" t="str">
+      <x:c r="E112" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/c5bDLq/btsL8Nz09SW/AAAAAAAAAAAAAAAAAAAAAEf-22CYUlMi31aPjyVDQhMqQTdRNUJ6T8BogHcdVmMU/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1774969199&amp;signature=3mMkhA1Xv5fPzkVrlSSQVy8bAqo%3D</x:v>
       </x:c>
-      <x:c r="F112" s="19" t="str">
+      <x:c r="F112" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EB%B6%80%EC%B2%9C%EC%97%90%EC%84%9C-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%9D%84-%EC%A6%90%EA%B8%B4%EB%8B%A4%EB%A9%B4-%EC%9B%94%EB%93%9C%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%99%84%EB%B2%BD-%EB%B6%84%EC%84%9D</x:v>
       </x:c>
-      <x:c r="G112" s="19" t="str">
+      <x:c r="G112" s="82" t="str">
         <x:v>부천 상동 월드클라이밍 내부</x:v>
       </x:c>
+      <x:c r="H112" s="81"/>
+      <x:c r="I112" s="81"/>
+      <x:c r="J112" s="81"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="19" t="str">
+      <x:c r="A113" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B113" s="19" t="str">
+      <x:c r="B113" s="82" t="str">
         <x:v>HBD-GYM-0124</x:v>
       </x:c>
-      <x:c r="C113" s="19" t="str">
+      <x:c r="C113" s="82" t="str">
         <x:v>캐치스톤 클라이밍 부천시청점</x:v>
       </x:c>
-      <x:c r="D113" s="19" t="str">
+      <x:c r="D113" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E113" s="19" t="str">
+      <x:c r="E113" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/49MaDWtlpCigtwhI74-tEgMAZAC0KRSRiaHsJbYO6_UWkaTwU5e-P4KEteTx3EqiaQ2BqZpYoLZm0WIdtYGhCG32gLh_AVobNzTlkIOreJfMTXve758Shggfmmj2Py8086uKaIwnrrwFtVEGus43ZX3AONULoSRCrRbxeGHdIcXDhNPqLOMhMDJNd4GHF6IR?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F113" s="19" t="str"/>
-      <x:c r="G113" s="19" t="str"/>
+      <x:c r="F113" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%BA%90%EC%B9%98%EC%8A%A4%ED%86%A4%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EB%B6%80%EC%B2%9C%EC%8B%9C%EC%B2%AD%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G113" s="82" t="str"/>
+      <x:c r="H113" s="81"/>
+      <x:c r="I113" s="81"/>
+      <x:c r="J113" s="81"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="19" t="str">
+      <x:c r="A114" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B114" s="19" t="str">
+      <x:c r="B114" s="82" t="str">
         <x:v>HBD-GYM-0125</x:v>
       </x:c>
-      <x:c r="C114" s="19" t="str">
+      <x:c r="C114" s="82" t="str">
         <x:v>캐치스톤클라이밍짐</x:v>
       </x:c>
-      <x:c r="D114" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E114" s="19" t="str"/>
-      <x:c r="F114" s="19" t="str"/>
-      <x:c r="G114" s="19" t="str"/>
+      <x:c r="D114" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E114" s="82"/>
+      <x:c r="F114" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/region/%EB%B6%80%EC%B2%9C%EC%8B%9C</x:v>
+      </x:c>
+      <x:c r="G114" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H114" s="81"/>
+      <x:c r="I114" s="81"/>
+      <x:c r="J114" s="81"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="19" t="str">
+      <x:c r="A115" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B115" s="19" t="str">
+      <x:c r="B115" s="82" t="str">
         <x:v>HBD-GYM-0126</x:v>
       </x:c>
-      <x:c r="C115" s="19" t="str">
+      <x:c r="C115" s="82" t="str">
         <x:v>팍스클라이밍센터</x:v>
       </x:c>
-      <x:c r="D115" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E115" s="19" t="str"/>
-      <x:c r="F115" s="19" t="str"/>
-      <x:c r="G115" s="19" t="str"/>
+      <x:c r="D115" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E115" s="82"/>
+      <x:c r="F115" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/region/%EB%B6%80%EC%B2%9C%EC%8B%9C</x:v>
+      </x:c>
+      <x:c r="G115" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H115" s="81"/>
+      <x:c r="I115" s="81"/>
+      <x:c r="J115" s="81"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="19" t="str">
+      <x:c r="A116" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B116" s="19" t="str">
+      <x:c r="B116" s="82" t="str">
         <x:v>HBD-GYM-0127</x:v>
       </x:c>
-      <x:c r="C116" s="19" t="str">
+      <x:c r="C116" s="82" t="str">
         <x:v>그립픽 클라이밍짐</x:v>
       </x:c>
-      <x:c r="D116" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E116" s="19" t="str"/>
-      <x:c r="F116" s="19" t="str"/>
-      <x:c r="G116" s="19" t="str"/>
+      <x:c r="D116" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E116" s="82"/>
+      <x:c r="F116" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EA%B7%B8%EB%A6%BD%ED%94%BD%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90</x:v>
+      </x:c>
+      <x:c r="G116" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H116" s="81"/>
+      <x:c r="I116" s="81"/>
+      <x:c r="J116" s="81"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="19" t="str">
+      <x:c r="A117" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B117" s="19" t="str">
+      <x:c r="B117" s="82" t="str">
         <x:v>HBD-GYM-0128</x:v>
       </x:c>
-      <x:c r="C117" s="19" t="str">
+      <x:c r="C117" s="82" t="str">
         <x:v>더볼더</x:v>
       </x:c>
-      <x:c r="D117" s="19" t="str">
+      <x:c r="D117" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E117" s="19" t="str">
+      <x:c r="E117" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/bvawg8/btsL7MokGfx/AAAAAAAAAAAAAAAAAAAAACtdU8Q873H7qPk4y_49_bDknuAboCVxzPX4vD2Aj3uc/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1780239599&amp;signature=4esBWvi4aa%2FH6PDPWdCZGFigbhA%3D</x:v>
       </x:c>
-      <x:c r="F117" s="19" t="str">
+      <x:c r="F117" s="82" t="str">
         <x:v>https://tentisori.tistory.com/entry/%EB%AF%B8%EA%B8%88%EC%97%AD-%EC%8B%A4%EB%82%B4-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EB%81%9D%ED%8C%90%EC%99%95-%EB%8D%94%EB%B3%BC%EB%8D%94-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90-%EC%99%84%EB%B2%BD-%EB%B6%84%EC%84%9D</x:v>
       </x:c>
-      <x:c r="G117" s="19" t="str">
+      <x:c r="G117" s="82" t="str">
         <x:v>미금역 더볼더 내부</x:v>
       </x:c>
+      <x:c r="H117" s="81"/>
+      <x:c r="I117" s="81"/>
+      <x:c r="J117" s="81"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="19" t="str">
+      <x:c r="A118" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B118" s="19" t="str">
+      <x:c r="B118" s="82" t="str">
         <x:v>HBD-GYM-0129</x:v>
       </x:c>
-      <x:c r="C118" s="19" t="str">
+      <x:c r="C118" s="82" t="str">
         <x:v>락트리 클라이밍 분당</x:v>
       </x:c>
-      <x:c r="D118" s="19" t="str">
+      <x:c r="D118" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E118" s="19" t="str">
+      <x:c r="E118" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/pn88TgEkHwN1NGKlpwll8wVKW98tQJ8jMkihzrXbopb-DKALiIFZdXKlbWIBMIk9vrM4b7nqtcqsnRa7iAVcaC8Rohl30DWn5imF98m-4gpWjvxTJO1PxUpx-FyxK1FGXmBLPz4HBESGZhL9j5KTiwX2LTUNTCYSdqX3cnrsS5_pgRzAqsxyGlTdPlFavbYt?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F118" s="19" t="str"/>
-      <x:c r="G118" s="19" t="str"/>
+      <x:c r="F118" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%9D%BD%ED%8A%B8%EB%A6%AC%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EB%B6%84%EB%8B%B9</x:v>
+      </x:c>
+      <x:c r="G118" s="82" t="str"/>
+      <x:c r="H118" s="81"/>
+      <x:c r="I118" s="81"/>
+      <x:c r="J118" s="81"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="19" t="str">
+      <x:c r="A119" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B119" s="19" t="str">
+      <x:c r="B119" s="82" t="str">
         <x:v>HBD-GYM-0130</x:v>
       </x:c>
-      <x:c r="C119" s="19" t="str">
+      <x:c r="C119" s="82" t="str">
         <x:v>락페이스클라이밍</x:v>
       </x:c>
-      <x:c r="D119" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E119" s="19" t="str"/>
-      <x:c r="F119" s="19" t="str"/>
-      <x:c r="G119" s="19" t="str"/>
+      <x:c r="D119" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E119" s="82"/>
+      <x:c r="F119" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%9D%BD%ED%8E%98%EC%9D%B4%EC%8A%A4%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G119" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H119" s="81"/>
+      <x:c r="I119" s="81"/>
+      <x:c r="J119" s="81"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="19" t="str">
+      <x:c r="A120" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B120" s="19" t="str">
+      <x:c r="B120" s="82" t="str">
         <x:v>HBD-GYM-0131</x:v>
       </x:c>
-      <x:c r="C120" s="19" t="str">
+      <x:c r="C120" s="82" t="str">
         <x:v>비클라이밍</x:v>
       </x:c>
-      <x:c r="D120" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E120" s="19" t="str"/>
-      <x:c r="F120" s="19" t="str"/>
-      <x:c r="G120" s="19" t="str"/>
+      <x:c r="D120" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E120" s="82" t="str">
+        <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEgK1VIVnK-ask9cl_ggBbtXX1PscDK4phQvI1B1npsCRNrYob4-qiA0fY-smy-AcRkhzilqUwgS-69EYVrWORKIGUEdhLZhXiAPVCFJox_nagI86NoDEv4z6ocV-FVdsEGN5UP-foV_7w12/s320/B-Climbing%2BBundang%2B%2528%25E1%2584%2587%25E1%2585%25B5%25E1%2584%258F%25E1%2585%25B3%25E1%2586%25AF%25E1%2584%2585%25E1%2585%25A1%25E1%2584%258B%25E1%2585%25B5%25E1%2584%2586%25E1%2585%25B5%25E1%2586%25BC%2B%25E1%2584%2587%25E1%2585%25AE%25E1%2586%25AB%25E1%2584%2583%25E1%2585%25A1%25E1%2586%25BC%25E1%2584%258C%25E1%2585%25A5%25E1%2586%25B7%2529.png</x:v>
+      </x:c>
+      <x:c r="F120" s="82" t="str">
+        <x:v>https://climbinginkorea.blogspot.com/2018/04/b-climbing-bundang.html</x:v>
+      </x:c>
+      <x:c r="G120" s="82" t="str">
+        <x:v>주소 일치 지점 자료 · 현재 확보 이미지는 로고형이라 교체 권장</x:v>
+      </x:c>
+      <x:c r="H120" s="81"/>
+      <x:c r="I120" s="81"/>
+      <x:c r="J120" s="81"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="19" t="str">
+      <x:c r="A121" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B121" s="19" t="str">
+      <x:c r="B121" s="82" t="str">
         <x:v>HBD-GYM-0132</x:v>
       </x:c>
-      <x:c r="C121" s="19" t="str">
+      <x:c r="C121" s="82" t="str">
         <x:v>성남스포츠클라이밍센터</x:v>
       </x:c>
-      <x:c r="D121" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E121" s="19" t="str"/>
-      <x:c r="F121" s="19" t="str"/>
-      <x:c r="G121" s="19" t="str"/>
+      <x:c r="D121" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E121" s="82"/>
+      <x:c r="F121" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/region/%EC%84%B1%EB%82%A8%EC%8B%9C</x:v>
+      </x:c>
+      <x:c r="G121" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H121" s="81"/>
+      <x:c r="I121" s="81"/>
+      <x:c r="J121" s="81"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="19" t="str">
+      <x:c r="A122" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B122" s="19" t="str">
+      <x:c r="B122" s="82" t="str">
         <x:v>HBD-GYM-0133</x:v>
       </x:c>
-      <x:c r="C122" s="19" t="str">
+      <x:c r="C122" s="82" t="str">
         <x:v>손상원 클라이밍짐 판교점</x:v>
       </x:c>
-      <x:c r="D122" s="19" t="str">
+      <x:c r="D122" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E122" s="19" t="str">
+      <x:c r="E122" s="82" t="str">
         <x:v>https://blog.kakaocdn.net/dna/bgYiaE/btsP11Beg86/AAAAAAAAAAAAAAAAAAAAANCoK4oLQpxCZF8fCQ47vUm__Vc-nmaf2fEZ2WwuNTJC/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=cY3shL6qtP71B6EqvK7iJGhLGw8%3D</x:v>
       </x:c>
-      <x:c r="F122" s="19" t="str">
+      <x:c r="F122" s="82" t="str">
         <x:v>https://ljh1700.tistory.com/13</x:v>
       </x:c>
-      <x:c r="G122" s="19" t="str">
+      <x:c r="G122" s="82" t="str">
         <x:v>판교점 볼더링/트레이닝 공간</x:v>
       </x:c>
+      <x:c r="H122" s="81"/>
+      <x:c r="I122" s="81"/>
+      <x:c r="J122" s="81"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="19" t="str">
+      <x:c r="A123" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B123" s="19" t="str">
+      <x:c r="B123" s="82" t="str">
         <x:v>HBD-GYM-0134</x:v>
       </x:c>
-      <x:c r="C123" s="19" t="str">
+      <x:c r="C123" s="82" t="str">
         <x:v>스파이더실내암벽클라이밍</x:v>
       </x:c>
-      <x:c r="D123" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E123" s="19" t="str"/>
-      <x:c r="F123" s="19" t="str"/>
-      <x:c r="G123" s="19" t="str"/>
+      <x:c r="D123" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E123" s="82"/>
+      <x:c r="F123" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/4bc97777-2545-4773-8ea7-8eaa117969cd</x:v>
+      </x:c>
+      <x:c r="G123" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H123" s="81"/>
+      <x:c r="I123" s="81"/>
+      <x:c r="J123" s="81"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="19" t="str">
+      <x:c r="A124" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B124" s="19" t="str">
+      <x:c r="B124" s="82" t="str">
         <x:v>HBD-GYM-0135</x:v>
       </x:c>
-      <x:c r="C124" s="19" t="str">
+      <x:c r="C124" s="82" t="str">
         <x:v>클라임 어스 모란점</x:v>
       </x:c>
-      <x:c r="D124" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E124" s="19" t="str"/>
-      <x:c r="F124" s="19" t="str"/>
-      <x:c r="G124" s="19" t="str"/>
+      <x:c r="D124" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E124" s="82"/>
+      <x:c r="F124" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9E%84%20%EC%96%B4%EC%8A%A4%20%EB%AA%A8%EB%9E%80%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G124" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H124" s="81"/>
+      <x:c r="I124" s="81"/>
+      <x:c r="J124" s="81"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="19" t="str">
+      <x:c r="A125" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B125" s="19" t="str">
+      <x:c r="B125" s="82" t="str">
         <x:v>HBD-GYM-0136</x:v>
       </x:c>
-      <x:c r="C125" s="19" t="str">
+      <x:c r="C125" s="82" t="str">
         <x:v>그래비티 클라이밍 수원역점</x:v>
       </x:c>
-      <x:c r="D125" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E125" s="19" t="str"/>
-      <x:c r="F125" s="19" t="str"/>
-      <x:c r="G125" s="19" t="str"/>
+      <x:c r="D125" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E125" s="82" t="str">
+        <x:v>https://image.dcinside.com/download.php?f_no=c4.png&amp;no=24b0d769e1d32ca73de887fa1bd62531bf8cbc57c7de00bb7d030155d82191cb834555b07ceb2aa479f34e59e5039e862eb66dc2ba5a97c340582f6fadcdc4fb99e2f595d3d506</x:v>
+      </x:c>
+      <x:c r="F125" s="82" t="str">
+        <x:v>https://gall.dcinside.com/mgallery/board/view/?id=sports_climbing&amp;no=6698</x:v>
+      </x:c>
+      <x:c r="G125" s="82" t="str">
+        <x:v>실방문 기록 · 수원역점 섹션 이미지</x:v>
+      </x:c>
+      <x:c r="H125" s="81"/>
+      <x:c r="I125" s="81"/>
+      <x:c r="J125" s="81"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="19" t="str">
+      <x:c r="A126" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B126" s="19" t="str">
+      <x:c r="B126" s="82" t="str">
         <x:v>HBD-GYM-0137</x:v>
       </x:c>
-      <x:c r="C126" s="19" t="str">
+      <x:c r="C126" s="82" t="str">
         <x:v>그래비티클라이밍</x:v>
       </x:c>
-      <x:c r="D126" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E126" s="19" t="str"/>
-      <x:c r="F126" s="19" t="str"/>
-      <x:c r="G126" s="19" t="str"/>
+      <x:c r="D126" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E126" s="82" t="str">
+        <x:v>https://image.dcinside.com/download.php?f_no=c5.png&amp;no=24b0d769e1d32ca73de887fa1bd62531bf8cbc57c7de00bb7d030155d82191cb834555b07ceb2aa479f34e59e5039e862eb66dc2ba5a97c340582f3bac9b91f925d8d23dceefc6</x:v>
+      </x:c>
+      <x:c r="F126" s="82" t="str">
+        <x:v>https://gall.dcinside.com/mgallery/board/view/?id=sports_climbing&amp;no=6698</x:v>
+      </x:c>
+      <x:c r="G126" s="82" t="str">
+        <x:v>실방문 기록 · 영통구청점 섹션 이미지</x:v>
+      </x:c>
+      <x:c r="H126" s="81"/>
+      <x:c r="I126" s="81"/>
+      <x:c r="J126" s="81"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="19" t="str">
+      <x:c r="A127" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B127" s="19" t="str">
+      <x:c r="B127" s="82" t="str">
         <x:v>HBD-GYM-0138</x:v>
       </x:c>
-      <x:c r="C127" s="19" t="str">
+      <x:c r="C127" s="82" t="str">
         <x:v>뀨클라임</x:v>
       </x:c>
-      <x:c r="D127" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E127" s="19" t="str"/>
-      <x:c r="F127" s="19" t="str"/>
-      <x:c r="G127" s="19" t="str"/>
+      <x:c r="D127" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E127" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dna/vbQTm/btsIrrnxqw2/AAAAAAAAAAAAAAAAAAAAAKa2XSE9FpykplY_hhA4o0NxhNbpdHpet2ymmGjztXCK/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=L16pAg0K%2F9aMbSjYJePahXcay6Q%3D</x:v>
+      </x:c>
+      <x:c r="F127" s="82" t="str">
+        <x:v>https://selfcaresudal.com/entry/%EC%88%98%EC%9B%90-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%9E%A5-%EB%80%A8%ED%81%B4%EB%9D%BC%EC%9E%84%EC%97%90%EC%84%9C-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EC%9E%85%EB%AC%B8%ED%95%98%EA%B8%B0</x:v>
+      </x:c>
+      <x:c r="G127" s="82" t="str">
+        <x:v>실방문 후기 · 주소 일치 · 암장 내부 전경</x:v>
+      </x:c>
+      <x:c r="H127" s="81"/>
+      <x:c r="I127" s="81"/>
+      <x:c r="J127" s="81"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="19" t="str">
+      <x:c r="A128" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B128" s="19" t="str">
+      <x:c r="B128" s="82" t="str">
         <x:v>HBD-GYM-0139</x:v>
       </x:c>
-      <x:c r="C128" s="19" t="str">
+      <x:c r="C128" s="82" t="str">
         <x:v>서수원클라이밍센터</x:v>
       </x:c>
-      <x:c r="D128" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E128" s="19" t="str"/>
-      <x:c r="F128" s="19" t="str"/>
-      <x:c r="G128" s="19" t="str"/>
+      <x:c r="D128" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E128" s="82"/>
+      <x:c r="F128" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%84%9C%EC%88%98%EC%9B%90%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G128" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H128" s="81"/>
+      <x:c r="I128" s="81"/>
+      <x:c r="J128" s="81"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="19" t="str">
+      <x:c r="A129" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B129" s="19" t="str">
+      <x:c r="B129" s="82" t="str">
         <x:v>HBD-GYM-0140</x:v>
       </x:c>
-      <x:c r="C129" s="19" t="str">
+      <x:c r="C129" s="82" t="str">
         <x:v>수원라온클라이밍센터</x:v>
       </x:c>
-      <x:c r="D129" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E129" s="19" t="str"/>
-      <x:c r="F129" s="19" t="str"/>
-      <x:c r="G129" s="19" t="str"/>
+      <x:c r="D129" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E129" s="82"/>
+      <x:c r="F129" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%88%98%EC%9B%90%EB%9D%BC%EC%98%A8%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G129" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H129" s="81"/>
+      <x:c r="I129" s="81"/>
+      <x:c r="J129" s="81"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="19" t="str">
+      <x:c r="A130" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B130" s="19" t="str">
+      <x:c r="B130" s="82" t="str">
         <x:v>HBD-GYM-0141</x:v>
       </x:c>
-      <x:c r="C130" s="19" t="str">
+      <x:c r="C130" s="82" t="str">
         <x:v>수원크럭스존클라이밍</x:v>
       </x:c>
-      <x:c r="D130" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E130" s="19" t="str"/>
-      <x:c r="F130" s="19" t="str"/>
-      <x:c r="G130" s="19" t="str"/>
+      <x:c r="D130" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E130" s="82" t="str">
+        <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEi3stctFYwBhRSe0kj9wVDXTdSKvruCQ8Iai3VEc_jos9INO-_RX5EsczjFEBKxkfyZ5krsgR8WbNV2sf7vl-QXy1Unu25MF9HSytn-2dINz7roOBEy31Ai446GTzV6xRUjw3tuW1_E7A7M/s320/Suwon%2BCruxzone%2528%25E1%2584%2589%25E1%2585%25AE%25E1%2584%258B%25E1%2585%25AF%25E1%2586%25AB%2B%25E1%2584%258F%25E1%2585%25B3%25E1%2584%2585%25E1%2585%25A5%25E1%2586%25A8%25E1%2584%2589%25E1%2585%25B3%25E1%2584%258C%25E1%2585%25A9%25E1%2586%25AB%2529.jpg</x:v>
+      </x:c>
+      <x:c r="F130" s="82" t="str">
+        <x:v>https://climbinginkorea.blogspot.com/2018/04/suwon-cruxzone.html</x:v>
+      </x:c>
+      <x:c r="G130" s="82" t="str">
+        <x:v>수원크럭스존 지점 이미지(과거 촬영), 지점명 일치</x:v>
+      </x:c>
+      <x:c r="H130" s="81"/>
+      <x:c r="I130" s="81"/>
+      <x:c r="J130" s="81"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="19" t="str">
+      <x:c r="A131" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B131" s="19" t="str">
+      <x:c r="B131" s="82" t="str">
         <x:v>HBD-GYM-0142</x:v>
       </x:c>
-      <x:c r="C131" s="19" t="str">
+      <x:c r="C131" s="82" t="str">
         <x:v>수원클라이밍센터</x:v>
       </x:c>
-      <x:c r="D131" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E131" s="19" t="str"/>
-      <x:c r="F131" s="19" t="str"/>
-      <x:c r="G131" s="19" t="str"/>
+      <x:c r="D131" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E131" s="82"/>
+      <x:c r="F131" s="82" t="str">
+        <x:v>https://www.koreatriptips.com/leisure-sports/231984.html</x:v>
+      </x:c>
+      <x:c r="G131" s="82" t="str">
+        <x:v>수원크럭스존 사진 오매칭 교정 · 대표사진 직접 URL 재검증 필요</x:v>
+      </x:c>
+      <x:c r="H131" s="81"/>
+      <x:c r="I131" s="81"/>
+      <x:c r="J131" s="81"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="19" t="str">
+      <x:c r="A132" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B132" s="19" t="str">
+      <x:c r="B132" s="82" t="str">
         <x:v>HBD-GYM-0143</x:v>
       </x:c>
-      <x:c r="C132" s="19" t="str">
+      <x:c r="C132" s="82" t="str">
         <x:v>슈퍼비클라이밍</x:v>
       </x:c>
-      <x:c r="D132" s="19" t="str">
+      <x:c r="D132" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E132" s="19" t="str">
+      <x:c r="E132" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/Vi350dZcrtJfuntHbBRBaQe7GfyuFRgRwiI2dDpO-xQc2lJlsqKUO5d7A0ZggiCEcqENoZM4sJurRBG9NtuhmVuDP7k-E6aSdFxpm42xCrYjzzax1Y_YFGBR8V7MliLHUCaBq5CiKH-PCxXQKB61THvTq59WR3JPkuxuPHGP9YEbW8DZkFMIaX1qtp1L9fZx?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F132" s="19" t="str"/>
-      <x:c r="G132" s="19" t="str"/>
+      <x:c r="F132" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%8A%88%ED%8D%BC%EB%B9%84%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G132" s="82" t="str"/>
+      <x:c r="H132" s="81"/>
+      <x:c r="I132" s="81"/>
+      <x:c r="J132" s="81"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="19" t="str">
+      <x:c r="A133" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B133" s="19" t="str">
+      <x:c r="B133" s="82" t="str">
         <x:v>HBD-GYM-0144</x:v>
       </x:c>
-      <x:c r="C133" s="19" t="str">
+      <x:c r="C133" s="82" t="str">
         <x:v>에픽클라임 망포점</x:v>
       </x:c>
-      <x:c r="D133" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E133" s="19" t="str"/>
-      <x:c r="F133" s="19" t="str"/>
-      <x:c r="G133" s="19" t="str"/>
+      <x:c r="D133" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E133" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dna/mu7QP/btrCImelmAx/AAAAAAAAAAAAAAAAAAAAAGSTFQ1S78IUmWT0OfKuWAFNwpW_MemJs7xNXBYDMlDg/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=NHnFU76R5d7BTM0Q%2Br%2FyDbtG0Yw%3D</x:v>
+      </x:c>
+      <x:c r="F133" s="82" t="str">
+        <x:v>https://hellmonkey.tistory.com/43</x:v>
+      </x:c>
+      <x:c r="G133" s="82" t="str">
+        <x:v>실방문 후기 · 망포점 주소 일치 · 오버행 벽 내부 전경</x:v>
+      </x:c>
+      <x:c r="H133" s="81"/>
+      <x:c r="I133" s="81"/>
+      <x:c r="J133" s="81"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="19" t="str">
+      <x:c r="A134" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B134" s="19" t="str">
+      <x:c r="B134" s="82" t="str">
         <x:v>HBD-GYM-0145</x:v>
       </x:c>
-      <x:c r="C134" s="19" t="str">
+      <x:c r="C134" s="82" t="str">
         <x:v>클라임바운스 수원점</x:v>
       </x:c>
-      <x:c r="D134" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E134" s="19" t="str"/>
-      <x:c r="F134" s="19" t="str"/>
-      <x:c r="G134" s="19" t="str"/>
+      <x:c r="D134" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E134" s="82" t="str">
+        <x:v>https://tong.visitkorea.or.kr/cms/resource/00/3071600_image2_1.jpg</x:v>
+      </x:c>
+      <x:c r="F134" s="82" t="str">
+        <x:v>https://www.koreatriptips.com/leisure-sports/3071612.html</x:v>
+      </x:c>
+      <x:c r="G134" s="82" t="str">
+        <x:v>한국관광공사 계열 지점 소개 사진 · 클라임바운스 수원점</x:v>
+      </x:c>
+      <x:c r="H134" s="81"/>
+      <x:c r="I134" s="81"/>
+      <x:c r="J134" s="81"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="19" t="str">
+      <x:c r="A135" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B135" s="19" t="str">
+      <x:c r="B135" s="82" t="str">
         <x:v>HBD-GYM-0146</x:v>
       </x:c>
-      <x:c r="C135" s="19" t="str">
+      <x:c r="C135" s="82" t="str">
         <x:v>클라임업 수원점</x:v>
       </x:c>
-      <x:c r="D135" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E135" s="19" t="str"/>
-      <x:c r="F135" s="19" t="str"/>
-      <x:c r="G135" s="19" t="str"/>
+      <x:c r="D135" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E135" s="82"/>
+      <x:c r="F135" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9E%84%EC%97%85%20%EC%88%98%EC%9B%90%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G135" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H135" s="81"/>
+      <x:c r="I135" s="81"/>
+      <x:c r="J135" s="81"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="19" t="str">
+      <x:c r="A136" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B136" s="19" t="str">
+      <x:c r="B136" s="82" t="str">
         <x:v>HBD-GYM-0147</x:v>
       </x:c>
-      <x:c r="C136" s="19" t="str">
+      <x:c r="C136" s="82" t="str">
         <x:v>킨디클라이밍</x:v>
       </x:c>
-      <x:c r="D136" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E136" s="19" t="str"/>
-      <x:c r="F136" s="19" t="str"/>
-      <x:c r="G136" s="19" t="str"/>
+      <x:c r="D136" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E136" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dna/cLUWn0/btsN7BqLjfe/AAAAAAAAAAAAAAAAAAAAADoeFXbQP3rHFeT2hfme6ymeNJ1BEoB3hERG_aTelp6J/img.png?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=BEQxrxjM%2FbSxqNQH47ap%2FR%2FC3%2Bs%3D</x:v>
+      </x:c>
+      <x:c r="F136" s="82" t="str">
+        <x:v>https://spacejoy.tistory.com/77</x:v>
+      </x:c>
+      <x:c r="G136" s="82" t="str">
+        <x:v>실방문 후기 · 주소 일치 · 대형 내부 전경</x:v>
+      </x:c>
+      <x:c r="H136" s="81"/>
+      <x:c r="I136" s="81"/>
+      <x:c r="J136" s="81"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="19" t="str">
+      <x:c r="A137" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B137" s="19" t="str">
+      <x:c r="B137" s="82" t="str">
         <x:v>HBD-GYM-0148</x:v>
       </x:c>
-      <x:c r="C137" s="19" t="str">
+      <x:c r="C137" s="82" t="str">
         <x:v>킹콩클라이밍 수원</x:v>
       </x:c>
-      <x:c r="D137" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E137" s="19" t="str"/>
-      <x:c r="F137" s="19" t="str"/>
-      <x:c r="G137" s="19" t="str"/>
+      <x:c r="D137" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E137" s="82"/>
+      <x:c r="F137" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%82%B9%EC%BD%A9%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EC%88%98%EC%9B%90</x:v>
+      </x:c>
+      <x:c r="G137" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H137" s="81"/>
+      <x:c r="I137" s="81"/>
+      <x:c r="J137" s="81"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="19" t="str">
+      <x:c r="A138" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B138" s="19" t="str">
+      <x:c r="B138" s="82" t="str">
         <x:v>HBD-GYM-0149</x:v>
       </x:c>
-      <x:c r="C138" s="19" t="str">
+      <x:c r="C138" s="82" t="str">
         <x:v>포에버클라이밍</x:v>
       </x:c>
-      <x:c r="D138" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E138" s="19" t="str"/>
-      <x:c r="F138" s="19" t="str"/>
-      <x:c r="G138" s="19" t="str"/>
+      <x:c r="D138" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E138" s="82"/>
+      <x:c r="F138" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%8F%AC%EC%97%90%EB%B2%84%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G138" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H138" s="81"/>
+      <x:c r="I138" s="81"/>
+      <x:c r="J138" s="81"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="19" t="str">
+      <x:c r="A139" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B139" s="19" t="str">
+      <x:c r="B139" s="82" t="str">
         <x:v>HBD-GYM-0150</x:v>
       </x:c>
-      <x:c r="C139" s="19" t="str">
+      <x:c r="C139" s="82" t="str">
         <x:v>피크닉클라이밍</x:v>
       </x:c>
-      <x:c r="D139" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E139" s="19" t="str"/>
-      <x:c r="F139" s="19" t="str"/>
-      <x:c r="G139" s="19" t="str"/>
+      <x:c r="D139" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E139" s="82"/>
+      <x:c r="F139" s="82" t="str">
+        <x:v>https://cruxlog.kr/posts/DX3KsRGkdSt</x:v>
+      </x:c>
+      <x:c r="G139" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H139" s="81"/>
+      <x:c r="I139" s="81"/>
+      <x:c r="J139" s="81"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="19" t="str">
+      <x:c r="A140" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B140" s="19" t="str">
+      <x:c r="B140" s="82" t="str">
         <x:v>HBD-GYM-0151</x:v>
       </x:c>
-      <x:c r="C140" s="19" t="str">
+      <x:c r="C140" s="82" t="str">
         <x:v>볼더가든</x:v>
       </x:c>
-      <x:c r="D140" s="19" t="str">
+      <x:c r="D140" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E140" s="19" t="str">
+      <x:c r="E140" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/2zYpGSfTWjy8-oY66E8GYAF7oEQBovTob25hVs9qu13TUKj6KKzHH1_4EwCNingtS92Mf0Y_EvADsH6Iy0LL0E6sdNvsJZz2W3ToY_6XAgxyybVXGX7A0EJKG8SbhfT3vwy-brOd0a-Py5O_2Hx_fVGVlNQK5cU7RmNIISeG7KHBNR83UMDv_SfZFu9QIX90?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F140" s="19" t="str"/>
-      <x:c r="G140" s="19" t="str"/>
+      <x:c r="F140" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%B3%BC%EB%8D%94%EA%B0%80%EB%93%A0</x:v>
+      </x:c>
+      <x:c r="G140" s="82" t="str"/>
+      <x:c r="H140" s="81"/>
+      <x:c r="I140" s="81"/>
+      <x:c r="J140" s="81"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="19" t="str">
+      <x:c r="A141" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B141" s="19" t="str">
+      <x:c r="B141" s="82" t="str">
         <x:v>HBD-GYM-0152</x:v>
       </x:c>
-      <x:c r="C141" s="19" t="str">
+      <x:c r="C141" s="82" t="str">
         <x:v>캐치클라이밍짐</x:v>
       </x:c>
-      <x:c r="D141" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E141" s="19" t="str"/>
-      <x:c r="F141" s="19" t="str"/>
-      <x:c r="G141" s="19" t="str"/>
+      <x:c r="D141" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E141" s="82"/>
+      <x:c r="F141" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%BA%90%EC%B9%98%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90</x:v>
+      </x:c>
+      <x:c r="G141" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H141" s="81"/>
+      <x:c r="I141" s="81"/>
+      <x:c r="J141" s="81"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="19" t="str">
+      <x:c r="A142" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B142" s="19" t="str">
+      <x:c r="B142" s="82" t="str">
         <x:v>HBD-GYM-0153</x:v>
       </x:c>
-      <x:c r="C142" s="19" t="str">
+      <x:c r="C142" s="82" t="str">
         <x:v>클라임잇 클라이밍 목감점</x:v>
       </x:c>
-      <x:c r="D142" s="19" t="str">
+      <x:c r="D142" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E142" s="19" t="str">
+      <x:c r="E142" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/Ia84afolunXQZ0gPUES6NEz5E2Ie0hKEjbsCUBuhODuKK7GyfUTQdzptqAxRsntrh0vurmBgEbk4vM7Td3olQqZWrUYrlFg1yK7B7vPMg3VI-fL_vhJfLLmzxDrbvCqkaivVajcwrGhdYv5Ul6ZPpiLO7aVc6wkvFI2HIZhWAHt1EG7186Z7MBH3hVTzaZiV?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F142" s="19" t="str"/>
-      <x:c r="G142" s="19" t="str"/>
+      <x:c r="F142" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/region/%EC%8B%9C%ED%9D%A5%EC%8B%9C</x:v>
+      </x:c>
+      <x:c r="G142" s="82" t="str"/>
+      <x:c r="H142" s="81"/>
+      <x:c r="I142" s="81"/>
+      <x:c r="J142" s="81"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="19" t="str">
+      <x:c r="A143" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B143" s="19" t="str">
+      <x:c r="B143" s="82" t="str">
         <x:v>HBD-GYM-0161</x:v>
       </x:c>
-      <x:c r="C143" s="19" t="str">
+      <x:c r="C143" s="82" t="str">
         <x:v>김종헌클라이밍센터</x:v>
       </x:c>
-      <x:c r="D143" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E143" s="19" t="str"/>
-      <x:c r="F143" s="19" t="str"/>
-      <x:c r="G143" s="19" t="str"/>
+      <x:c r="D143" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E143" s="82" t="str">
+        <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEiGy2B1qlMWYJtQYmBDstLZ9v3pIGfC25PGn45JyAngjVGk4CF5EI78lHqjCnR6WwiamJbr2nNZ52mASgX1uB-4I33tNjRd-q4ToZlde_LTviUODJ3wJ1K-cebDQDdCt0J96TO0A6BT54aC/s320/KJH%2BClimbing%2B%2528%25E1%2584%2580%25E1%2585%25B5%25E1%2586%25B7%25E1%2584%258C%25E1%2585%25A9%25E1%2586%25BC%25E1%2584%2592%25E1%2585%25A5%25E1%2586%25AB%2B%25E1%2584%258F%25E1%2585%25B3%25E1%2586%25AF%25E1%2584%2585%25E1%2585%25A1%25E1%2584%258B%25E1%2585%25B5%25E1%2584%2586%25E1%2585%25B5%25E1%2586%25BC%25E1%2584%2589%25E1%2585%25A6%25E1%2586%25AB%25E1%2584%2590%25E1%2585%25A5%2529.png</x:v>
+      </x:c>
+      <x:c r="F143" s="82" t="str">
+        <x:v>https://climbinginkorea.blogspot.com/2018/04/kjh-climbing.html</x:v>
+      </x:c>
+      <x:c r="G143" s="82" t="str">
+        <x:v>김종헌클라이밍센터 지점 이미지(과거 촬영)</x:v>
+      </x:c>
+      <x:c r="H143" s="81"/>
+      <x:c r="I143" s="81"/>
+      <x:c r="J143" s="81"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="19" t="str">
+      <x:c r="A144" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B144" s="19" t="str">
+      <x:c r="B144" s="82" t="str">
         <x:v>HBD-GYM-0162</x:v>
       </x:c>
-      <x:c r="C144" s="19" t="str">
+      <x:c r="C144" s="82" t="str">
         <x:v>더렛지 클라이밍</x:v>
       </x:c>
-      <x:c r="D144" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E144" s="19" t="str"/>
-      <x:c r="F144" s="19" t="str"/>
-      <x:c r="G144" s="19" t="str"/>
+      <x:c r="D144" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E144" s="82" t="str">
+        <x:v>https://climbatlas.app/api/places/photo/ChIJeU0KS-ZhezUR1ooEufWqYKs/Ab43m-th6NkUAtTKXke4fqaH5BdqkBu5c63RXW9zLGdziYzx7yV6XNcTWsveqBs4iLivlyyYXwfYb2Unm5uxVLdI-peDtf_OfOVovBH9Ypo0WQMsp-P4fP-1v11UrkDweU1i6Pr85d9YjCcIU3omE7M5grhU8ynwlgz2leyGhclkNXuXp9F5xSRq7mX4nqu0aW_253MeNB1yJPmjhy4jm71tAvx9lpl2GW9i4VynHNBhI6v0CmwZmQtdd9ehiD_Y1a6It2SyHCszn4CQDHvbFtTpkaYbLfQmSLt-2HvZpU3vCFrpAQ</x:v>
+      </x:c>
+      <x:c r="F144" s="82" t="str">
+        <x:v>https://climbatlas.app/indoor/bouldering/kr/an-yangsi/16061/deolesjikeullaiming-theledge-climbing-gym</x:v>
+      </x:c>
+      <x:c r="G144" s="82" t="str">
+        <x:v>ClimbAtlas 지점 페이지·사진 일치</x:v>
+      </x:c>
+      <x:c r="H144" s="81"/>
+      <x:c r="I144" s="81"/>
+      <x:c r="J144" s="81"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="19" t="str">
+      <x:c r="A145" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B145" s="19" t="str">
+      <x:c r="B145" s="82" t="str">
         <x:v>HBD-GYM-0163</x:v>
       </x:c>
-      <x:c r="C145" s="19" t="str">
+      <x:c r="C145" s="82" t="str">
         <x:v>아람클라이밍</x:v>
       </x:c>
-      <x:c r="D145" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E145" s="19" t="str"/>
-      <x:c r="F145" s="19" t="str"/>
-      <x:c r="G145" s="19" t="str"/>
+      <x:c r="D145" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E145" s="82" t="str">
+        <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEgget331ZHwbdhysxkngEv9CS91nlSs8owO1X4f3hlrSS6oituaBw6AvYdAanIjjGAKo0ravQpAbcVZEphsV-w2MNMlF9hLYBVsplGQ1IcJD8S_eDKR1SKrLu4UE9Gg83h8UcmfPzwJGHtn/s320/Aram%2BClimbing%2B%2528%25E1%2584%258B%25E1%2585%25A1%25E1%2584%2585%25E1%2585%25A1%25E1%2586%25B7%25E1%2584%258F%25E1%2585%25B3%25E1%2586%25AF%25E1%2584%2585%25E1%2585%25A1%25E1%2584%258B%25E1%2585%25B5%25E1%2584%2586%25E1%2585%25B5%25E1%2586%25BC%2529.png</x:v>
+      </x:c>
+      <x:c r="F145" s="82" t="str">
+        <x:v>https://climbinginkorea.blogspot.com/2018/04/aram-climbing.html</x:v>
+      </x:c>
+      <x:c r="G145" s="82" t="str">
+        <x:v>아람클라이밍 지점 이미지(과거 촬영)</x:v>
+      </x:c>
+      <x:c r="H145" s="81"/>
+      <x:c r="I145" s="81"/>
+      <x:c r="J145" s="81"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="19" t="str">
+      <x:c r="A146" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B146" s="19" t="str">
+      <x:c r="B146" s="82" t="str">
         <x:v>HBD-GYM-0164</x:v>
       </x:c>
-      <x:c r="C146" s="19" t="str">
+      <x:c r="C146" s="82" t="str">
         <x:v>에어즈락 클라이밍 범계점</x:v>
       </x:c>
-      <x:c r="D146" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E146" s="19" t="str"/>
-      <x:c r="F146" s="19" t="str"/>
-      <x:c r="G146" s="19" t="str"/>
+      <x:c r="D146" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E146" s="82" t="str">
+        <x:v>https://climbatlas.app/api/places/photo/ChIJcx0jhWdhezURxXbIryMNkMM/Ab43m-tO1VX4ufZcM5vAMA7IIWfjf69cbAsGHHQOBodPU0kEUdPlVGccsdGLlKxSDfEKAklYWgO6vkdeZdk8IqT4ZS0EJX97c9AxtsgDgdgAMYuTrFMOjYGFj_LA5oYDVRpmCnU2rvncYNro8yuHpRn0pK5kOtyZhddXViYQXrzHteyJq-_sWEeJDPu9zpYa5HsqiNbUvillatAU2SoTAxVAKPX8fb1OBJRqzd2FiI0sl3-UkQDPUPjjq2HSrYZ40r4xM0oLBuP8xA1AxqzId04lNcvswuHxCFMbTGHxq0Yg2vTI--pabZfvHmCB2ot6l7OF9QwppPVnU0N-agH9kwvSFfIRn93ImfX4zrO3ptxQ3-nOTJZwFI6wQaoheQ9DGQQ3gpw4ZD_7NmZbOu1m7YZ_bcLh3DDud5ywOppLC7y2gKnixA</x:v>
+      </x:c>
+      <x:c r="F146" s="82" t="str">
+        <x:v>https://climbatlas.app/indoor/bouldering/kr/an-yangsi/20166/eeojeulag-keullaiming-beomgyejeom</x:v>
+      </x:c>
+      <x:c r="G146" s="82" t="str">
+        <x:v>ClimbAtlas 범계점 페이지·사진 일치</x:v>
+      </x:c>
+      <x:c r="H146" s="81"/>
+      <x:c r="I146" s="81"/>
+      <x:c r="J146" s="81"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="19" t="str">
+      <x:c r="A147" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B147" s="19" t="str">
+      <x:c r="B147" s="82" t="str">
         <x:v>HBD-GYM-0165</x:v>
       </x:c>
-      <x:c r="C147" s="19" t="str">
+      <x:c r="C147" s="82" t="str">
         <x:v>클라임홀릭</x:v>
       </x:c>
-      <x:c r="D147" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E147" s="19" t="str"/>
-      <x:c r="F147" s="19" t="str"/>
-      <x:c r="G147" s="19" t="str"/>
+      <x:c r="D147" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E147" s="82" t="str">
+        <x:v>https://climbatlas.app/api/places/photo/ChIJu4rJ-TdeezURTIZ9wNwN28U/Ab43m-vv-qIcLRNq3dL-cJ66qqNg9ZCySR9vd8qh5Jsfe3kMbfWDcIQK8zOPjo9hcKK46SxVQK8qMb4CYPtezBAnal72P2fUu31ESIBUP0HxRdGWgze8PTczAIf5z1Mz6ukMhnU4_gs5kcOVALdS2-Mk73_YclZKtqVGSp3bq5vuKbkQHDfbOBfTRWs9nq690oU7RcBU6Hd33gPiNi6dJeRd6QXRtvcu0BLUeJVkTzkNs888n8qDcGhj-GBsbFPXNAVwaen06MBt-81Z-KBj0GN9b4aX6dqth5du7Bmg2Awm8_Ct1rK0WdkxoSAUWn92iz7sxR0vOcmXoSL8J9y3KSMf7coMyOs-XSji4Ls8zHCCrqvPdDEloYR1kDG-snw_tCdVfcHPidL8VtSusZHfBryfZwQC3VvtyO4UFBIi4KsHLLIJ9g</x:v>
+      </x:c>
+      <x:c r="F147" s="82" t="str">
+        <x:v>https://climbatlas.app/indoor/bouldering/kr/gunposi/20126/keullaimhollig-keullaimingjim</x:v>
+      </x:c>
+      <x:c r="G147" s="82" t="str">
+        <x:v>ClimbAtlas 지점 페이지·사진 일치</x:v>
+      </x:c>
+      <x:c r="H147" s="81"/>
+      <x:c r="I147" s="81"/>
+      <x:c r="J147" s="81"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="19" t="str">
+      <x:c r="A148" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B148" s="19" t="str">
+      <x:c r="B148" s="82" t="str">
         <x:v>HBD-GYM-0166</x:v>
       </x:c>
-      <x:c r="C148" s="19" t="str">
+      <x:c r="C148" s="82" t="str">
         <x:v>펀클라임짐</x:v>
       </x:c>
-      <x:c r="D148" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E148" s="19" t="str"/>
-      <x:c r="F148" s="19" t="str"/>
-      <x:c r="G148" s="19" t="str"/>
+      <x:c r="D148" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E148" s="82"/>
+      <x:c r="F148" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/2164ea8c-a188-4880-825c-2f79b7b8309c</x:v>
+      </x:c>
+      <x:c r="G148" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H148" s="81"/>
+      <x:c r="I148" s="81"/>
+      <x:c r="J148" s="81"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="19" t="str">
+      <x:c r="A149" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B149" s="19" t="str">
+      <x:c r="B149" s="82" t="str">
         <x:v>HBD-GYM-0169</x:v>
       </x:c>
-      <x:c r="C149" s="19" t="str">
+      <x:c r="C149" s="82" t="str">
         <x:v>경기레포츠 클라이밍</x:v>
       </x:c>
-      <x:c r="D149" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E149" s="19" t="str"/>
-      <x:c r="F149" s="19" t="str"/>
-      <x:c r="G149" s="19" t="str"/>
+      <x:c r="D149" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E149" s="82"/>
+      <x:c r="F149" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EA%B2%BD%EA%B8%B0%EB%A0%88%ED%8F%AC%EC%B8%A0%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G149" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H149" s="81"/>
+      <x:c r="I149" s="81"/>
+      <x:c r="J149" s="81"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="19" t="str">
+      <x:c r="A150" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B150" s="19" t="str">
+      <x:c r="B150" s="82" t="str">
         <x:v>HBD-GYM-0170</x:v>
       </x:c>
-      <x:c r="C150" s="19" t="str">
+      <x:c r="C150" s="82" t="str">
         <x:v>더그릿클라이밍</x:v>
       </x:c>
-      <x:c r="D150" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E150" s="19" t="str"/>
-      <x:c r="F150" s="19" t="str"/>
-      <x:c r="G150" s="19" t="str"/>
+      <x:c r="D150" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E150" s="82"/>
+      <x:c r="F150" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%8D%94%EA%B7%B8%EB%A6%BF%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G150" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H150" s="81"/>
+      <x:c r="I150" s="81"/>
+      <x:c r="J150" s="81"/>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="19" t="str">
+      <x:c r="A151" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B151" s="19" t="str">
+      <x:c r="B151" s="82" t="str">
         <x:v>HBD-GYM-0171</x:v>
       </x:c>
-      <x:c r="C151" s="19" t="str">
+      <x:c r="C151" s="82" t="str">
         <x:v>볼더메이트 수지</x:v>
       </x:c>
-      <x:c r="D151" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E151" s="19" t="str"/>
-      <x:c r="F151" s="19" t="str"/>
-      <x:c r="G151" s="19" t="str"/>
+      <x:c r="D151" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E151" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dna/bKX033/btsOUyOTotV/AAAAAAAAAAAAAAAAAAAAAFQmAQwDBn9l0qTiIo815Hx9omIpIRv0BXN6Sne248o8/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=CXFTJ7FTn2jHuWKwq0GawI6uCUY%3D</x:v>
+      </x:c>
+      <x:c r="F151" s="82" t="str">
+        <x:v>https://yogyui.tistory.com/entry/250626-%EC%8B%A4%EB%82%B4-%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-%EB%B3%BC%EB%8D%94%EB%A9%94%EC%9D%B4%ED%8A%B8-%EC%88%98%EC%A7%80</x:v>
+      </x:c>
+      <x:c r="G151" s="82" t="str">
+        <x:v>실방문 후기 · 수지점 주소 일치 · 암장 내부 전경</x:v>
+      </x:c>
+      <x:c r="H151" s="81"/>
+      <x:c r="I151" s="81"/>
+      <x:c r="J151" s="81"/>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="19" t="str">
+      <x:c r="A152" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B152" s="19" t="str">
+      <x:c r="B152" s="82" t="str">
         <x:v>HBD-GYM-0172</x:v>
       </x:c>
-      <x:c r="C152" s="19" t="str">
+      <x:c r="C152" s="82" t="str">
         <x:v>볼더메이트 클라이밍 기흥점</x:v>
       </x:c>
-      <x:c r="D152" s="19" t="str">
+      <x:c r="D152" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E152" s="19" t="str">
+      <x:c r="E152" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/_ekzfpPNfASY8f6cSEJrEBrtyBpNUkjP2L1RD1RY7HFhSXI1AwS0S_eI_f_eCJPKWsA2Pil8L8Ka6pfD3VvhPDA1u-J5LSExrCdx-jJjig51WMQK_JqSg7g_3E51Z94YP46MJxjTmmom3uUqpHpCQfWAkZoYBi-R7ZLiWxZAXiYEiE0SvH3r1k6U0KrT6_hy?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F152" s="19" t="str"/>
-      <x:c r="G152" s="19" t="str"/>
+      <x:c r="F152" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%B3%BC%EB%8D%94%EB%A9%94%EC%9D%B4%ED%8A%B8%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EA%B8%B0%ED%9D%A5%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G152" s="82" t="str"/>
+      <x:c r="H152" s="81"/>
+      <x:c r="I152" s="81"/>
+      <x:c r="J152" s="81"/>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="19" t="str">
+      <x:c r="A153" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B153" s="19" t="str">
+      <x:c r="B153" s="82" t="str">
         <x:v>HBD-GYM-0173</x:v>
       </x:c>
-      <x:c r="C153" s="19" t="str">
+      <x:c r="C153" s="82" t="str">
         <x:v>수지클라이밍</x:v>
       </x:c>
-      <x:c r="D153" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E153" s="19" t="str"/>
-      <x:c r="F153" s="19" t="str"/>
-      <x:c r="G153" s="19" t="str"/>
+      <x:c r="D153" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E153" s="82"/>
+      <x:c r="F153" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%88%98%EC%A7%80%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G153" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H153" s="81"/>
+      <x:c r="I153" s="81"/>
+      <x:c r="J153" s="81"/>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="19" t="str">
+      <x:c r="A154" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B154" s="19" t="str">
+      <x:c r="B154" s="82" t="str">
         <x:v>HBD-GYM-0174</x:v>
       </x:c>
-      <x:c r="C154" s="19" t="str">
+      <x:c r="C154" s="82" t="str">
         <x:v>오르자</x:v>
       </x:c>
-      <x:c r="D154" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E154" s="19" t="str"/>
-      <x:c r="F154" s="19" t="str"/>
-      <x:c r="G154" s="19" t="str"/>
+      <x:c r="D154" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E154" s="82"/>
+      <x:c r="F154" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%98%A4%EB%A5%B4%EC%9E%90</x:v>
+      </x:c>
+      <x:c r="G154" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H154" s="81"/>
+      <x:c r="I154" s="81"/>
+      <x:c r="J154" s="81"/>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="19" t="str">
+      <x:c r="A155" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B155" s="19" t="str">
+      <x:c r="B155" s="82" t="str">
         <x:v>HBD-GYM-0175</x:v>
       </x:c>
-      <x:c r="C155" s="19" t="str">
+      <x:c r="C155" s="82" t="str">
         <x:v>용인시스포츠클라이밍장</x:v>
       </x:c>
-      <x:c r="D155" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E155" s="19" t="str"/>
-      <x:c r="F155" s="19" t="str"/>
-      <x:c r="G155" s="19" t="str"/>
+      <x:c r="D155" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E155" s="82"/>
+      <x:c r="F155" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%9A%A9%EC%9D%B8%EC%8B%9C%EC%8A%A4%ED%8F%AC%EC%B8%A0%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%9E%A5</x:v>
+      </x:c>
+      <x:c r="G155" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H155" s="81"/>
+      <x:c r="I155" s="81"/>
+      <x:c r="J155" s="81"/>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="19" t="str">
+      <x:c r="A156" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B156" s="19" t="str">
+      <x:c r="B156" s="82" t="str">
         <x:v>HBD-GYM-0192</x:v>
       </x:c>
-      <x:c r="C156" s="19" t="str">
+      <x:c r="C156" s="82" t="str">
         <x:v>CL 클라이밍</x:v>
       </x:c>
-      <x:c r="D156" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E156" s="19" t="str"/>
-      <x:c r="F156" s="19" t="str"/>
-      <x:c r="G156" s="19" t="str"/>
+      <x:c r="D156" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E156" s="82"/>
+      <x:c r="F156" s="82" t="str">
+        <x:v>https://spiri7.com/gym/CL%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G156" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H156" s="81"/>
+      <x:c r="I156" s="81"/>
+      <x:c r="J156" s="81"/>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="19" t="str">
+      <x:c r="A157" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B157" s="19" t="str">
+      <x:c r="B157" s="82" t="str">
         <x:v>HBD-GYM-0193</x:v>
       </x:c>
-      <x:c r="C157" s="19" t="str">
+      <x:c r="C157" s="82" t="str">
         <x:v>마운틴그라운드 클라이밍</x:v>
       </x:c>
-      <x:c r="D157" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E157" s="19" t="str"/>
-      <x:c r="F157" s="19" t="str"/>
-      <x:c r="G157" s="19" t="str"/>
+      <x:c r="D157" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E157" s="82"/>
+      <x:c r="F157" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%A7%88%EC%9A%B4%ED%8B%B4%EA%B7%B8%EB%9D%BC%EC%9A%B4%EB%93%9C%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G157" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H157" s="81"/>
+      <x:c r="I157" s="81"/>
+      <x:c r="J157" s="81"/>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="19" t="str">
+      <x:c r="A158" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B158" s="19" t="str">
+      <x:c r="B158" s="82" t="str">
         <x:v>HBD-GYM-0194</x:v>
       </x:c>
-      <x:c r="C158" s="19" t="str">
+      <x:c r="C158" s="82" t="str">
         <x:v>문클라임</x:v>
       </x:c>
-      <x:c r="D158" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E158" s="19" t="str"/>
-      <x:c r="F158" s="19" t="str"/>
-      <x:c r="G158" s="19" t="str"/>
+      <x:c r="D158" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E158" s="82"/>
+      <x:c r="F158" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/db4a1bef-0859-4173-9b2f-00ef5e25dc94</x:v>
+      </x:c>
+      <x:c r="G158" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H158" s="81"/>
+      <x:c r="I158" s="81"/>
+      <x:c r="J158" s="81"/>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="19" t="str">
+      <x:c r="A159" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B159" s="19" t="str">
+      <x:c r="B159" s="82" t="str">
         <x:v>HBD-GYM-0195</x:v>
       </x:c>
-      <x:c r="C159" s="19" t="str">
+      <x:c r="C159" s="82" t="str">
         <x:v>볼더박스 클라임</x:v>
       </x:c>
-      <x:c r="D159" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E159" s="19" t="str"/>
-      <x:c r="F159" s="19" t="str"/>
-      <x:c r="G159" s="19" t="str"/>
+      <x:c r="D159" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E159" s="82"/>
+      <x:c r="F159" s="82" t="str">
+        <x:v>https://www.sports.re.kr/pyxis-api/1/digital-files/98557431-1122-463f-80d5-f5575cc4ec15</x:v>
+      </x:c>
+      <x:c r="G159" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H159" s="81"/>
+      <x:c r="I159" s="81"/>
+      <x:c r="J159" s="81"/>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="19" t="str">
+      <x:c r="A160" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B160" s="19" t="str">
+      <x:c r="B160" s="82" t="str">
         <x:v>HBD-GYM-0196</x:v>
       </x:c>
-      <x:c r="C160" s="19" t="str">
+      <x:c r="C160" s="82" t="str">
         <x:v>아이언팜스 클라이밍센터</x:v>
       </x:c>
-      <x:c r="D160" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E160" s="19" t="str"/>
-      <x:c r="F160" s="19" t="str"/>
-      <x:c r="G160" s="19" t="str"/>
+      <x:c r="D160" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E160" s="82"/>
+      <x:c r="F160" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/region/%ED%99%94%EC%84%B1%EC%8B%9C</x:v>
+      </x:c>
+      <x:c r="G160" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H160" s="81"/>
+      <x:c r="I160" s="81"/>
+      <x:c r="J160" s="81"/>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="19" t="str">
+      <x:c r="A161" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B161" s="19" t="str">
+      <x:c r="B161" s="82" t="str">
         <x:v>HBD-GYM-0197</x:v>
       </x:c>
-      <x:c r="C161" s="19" t="str">
+      <x:c r="C161" s="82" t="str">
         <x:v>엑스클라이밍</x:v>
       </x:c>
-      <x:c r="D161" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E161" s="19" t="str"/>
-      <x:c r="F161" s="19" t="str"/>
-      <x:c r="G161" s="19" t="str"/>
+      <x:c r="D161" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E161" s="82"/>
+      <x:c r="F161" s="82" t="str">
+        <x:v>https://www.daangn.com/kr/local-profile/%EC%97%91%EC%8A%A4%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-ar5pyg3dy687/</x:v>
+      </x:c>
+      <x:c r="G161" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H161" s="81"/>
+      <x:c r="I161" s="81"/>
+      <x:c r="J161" s="81"/>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="19" t="str">
+      <x:c r="A162" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B162" s="19" t="str">
+      <x:c r="B162" s="82" t="str">
         <x:v>HBD-GYM-0198</x:v>
       </x:c>
-      <x:c r="C162" s="19" t="str">
+      <x:c r="C162" s="82" t="str">
         <x:v>클라임어클락</x:v>
       </x:c>
-      <x:c r="D162" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E162" s="19" t="str"/>
-      <x:c r="F162" s="19" t="str"/>
-      <x:c r="G162" s="19" t="str"/>
+      <x:c r="D162" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E162" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dna/xehEt/btsLBerVgbK/AAAAAAAAAAAAAAAAAAAAAMhBE0442NSoIqb9RliDI7B57CWBtJou3eUbgx68rPEe/tfile.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=MO7URFC8LBJMhxI5L%2Bh7eJG76pQ%3D</x:v>
+      </x:c>
+      <x:c r="F162" s="82" t="str">
+        <x:v>https://mamidream.tistory.com/m/104</x:v>
+      </x:c>
+      <x:c r="G162" s="82" t="str">
+        <x:v>실방문 후기 · 동탄기흥로257번가길 33 주소 일치 · 내부 사진</x:v>
+      </x:c>
+      <x:c r="H162" s="81"/>
+      <x:c r="I162" s="81"/>
+      <x:c r="J162" s="81"/>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="19" t="str">
+      <x:c r="A163" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B163" s="19" t="str">
+      <x:c r="B163" s="82" t="str">
         <x:v>HBD-GYM-0199</x:v>
       </x:c>
-      <x:c r="C163" s="19" t="str">
+      <x:c r="C163" s="82" t="str">
         <x:v>홀드앤락클라이밍</x:v>
       </x:c>
-      <x:c r="D163" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E163" s="19" t="str"/>
-      <x:c r="F163" s="19" t="str"/>
-      <x:c r="G163" s="19" t="str"/>
+      <x:c r="D163" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E163" s="82"/>
+      <x:c r="F163" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%99%80%EB%93%9C%EC%95%A4%EB%9D%BD%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G163" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H163" s="81"/>
+      <x:c r="I163" s="81"/>
+      <x:c r="J163" s="81"/>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="19" t="str">
+      <x:c r="A164" s="82" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="B164" s="19" t="str">
+      <x:c r="B164" s="82" t="str">
         <x:v>HBD-GYM-0200</x:v>
       </x:c>
-      <x:c r="C164" s="19" t="str">
+      <x:c r="C164" s="82" t="str">
         <x:v>화성클라이밍클럽</x:v>
       </x:c>
-      <x:c r="D164" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E164" s="19" t="str"/>
-      <x:c r="F164" s="19" t="str"/>
-      <x:c r="G164" s="19" t="str"/>
+      <x:c r="D164" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E164" s="82"/>
+      <x:c r="F164" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%99%94%EC%84%B1%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%ED%81%B4%EB%9F%BD</x:v>
+      </x:c>
+      <x:c r="G164" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H164" s="81"/>
+      <x:c r="I164" s="81"/>
+      <x:c r="J164" s="81"/>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="19" t="str">
+      <x:c r="A165" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B165" s="19" t="str">
+      <x:c r="B165" s="82" t="str">
         <x:v>HBD-GYM-0106</x:v>
       </x:c>
-      <x:c r="C165" s="19" t="str">
+      <x:c r="C165" s="82" t="str">
         <x:v>매드짐 광명클라이밍센터</x:v>
       </x:c>
-      <x:c r="D165" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E165" s="19" t="str"/>
-      <x:c r="F165" s="19" t="str"/>
-      <x:c r="G165" s="19" t="str"/>
+      <x:c r="D165" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E165" s="82"/>
+      <x:c r="F165" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%A7%A4%EB%93%9C%EC%A7%90%20%EA%B4%91%EB%AA%85%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G165" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H165" s="81"/>
+      <x:c r="I165" s="81"/>
+      <x:c r="J165" s="81"/>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="19" t="str">
+      <x:c r="A166" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B166" s="19" t="str">
+      <x:c r="B166" s="82" t="str">
         <x:v>HBD-GYM-0107</x:v>
       </x:c>
-      <x:c r="C166" s="19" t="str">
+      <x:c r="C166" s="82" t="str">
         <x:v>티클라이밍</x:v>
       </x:c>
-      <x:c r="D166" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E166" s="19" t="str"/>
-      <x:c r="F166" s="19" t="str"/>
-      <x:c r="G166" s="19" t="str"/>
+      <x:c r="D166" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E166" s="82"/>
+      <x:c r="F166" s="82" t="str">
+        <x:v>https://www.sports.re.kr/pyxis-api/1/digital-files/98557431-1122-463f-80d5-f5575cc4ec15</x:v>
+      </x:c>
+      <x:c r="G166" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H166" s="81"/>
+      <x:c r="I166" s="81"/>
+      <x:c r="J166" s="81"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="19" t="str">
+      <x:c r="A167" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B167" s="19" t="str">
+      <x:c r="B167" s="82" t="str">
         <x:v>HBD-GYM-0108</x:v>
       </x:c>
-      <x:c r="C167" s="19" t="str">
+      <x:c r="C167" s="82" t="str">
         <x:v>마운틴스타 클라이밍짐</x:v>
       </x:c>
-      <x:c r="D167" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E167" s="19" t="str"/>
-      <x:c r="F167" s="19" t="str"/>
-      <x:c r="G167" s="19" t="str"/>
+      <x:c r="D167" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E167" s="82"/>
+      <x:c r="F167" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%A7%88%EC%9A%B4%ED%8B%B4%EC%8A%A4%ED%83%80%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90</x:v>
+      </x:c>
+      <x:c r="G167" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H167" s="81"/>
+      <x:c r="I167" s="81"/>
+      <x:c r="J167" s="81"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="19" t="str">
+      <x:c r="A168" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B168" s="19" t="str">
+      <x:c r="B168" s="82" t="str">
         <x:v>HBD-GYM-0109</x:v>
       </x:c>
-      <x:c r="C168" s="19" t="str">
+      <x:c r="C168" s="82" t="str">
         <x:v>락클라이밍 산본</x:v>
       </x:c>
-      <x:c r="D168" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E168" s="19" t="str"/>
-      <x:c r="F168" s="19" t="str"/>
-      <x:c r="G168" s="19" t="str"/>
+      <x:c r="D168" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E168" s="82"/>
+      <x:c r="F168" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%9D%BD%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EC%82%B0%EB%B3%B8</x:v>
+      </x:c>
+      <x:c r="G168" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H168" s="81"/>
+      <x:c r="I168" s="81"/>
+      <x:c r="J168" s="81"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="19" t="str">
+      <x:c r="A169" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B169" s="19" t="str">
+      <x:c r="B169" s="82" t="str">
         <x:v>HBD-GYM-0110</x:v>
       </x:c>
-      <x:c r="C169" s="19" t="str">
+      <x:c r="C169" s="82" t="str">
         <x:v>볼더팝 클라이밍</x:v>
       </x:c>
-      <x:c r="D169" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E169" s="19" t="str"/>
-      <x:c r="F169" s="19" t="str"/>
-      <x:c r="G169" s="19" t="str"/>
+      <x:c r="D169" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E169" s="82"/>
+      <x:c r="F169" s="82" t="str">
+        <x:v>https://goup.imweb.me/MAGAZINE/?bmode=view&amp;idx=10749462</x:v>
+      </x:c>
+      <x:c r="G169" s="82" t="str">
+        <x:v>군포 볼더팝 지점·주소 및 사진 출처 확인 · 직접 이미지 URL 재추출 필요</x:v>
+      </x:c>
+      <x:c r="H169" s="81"/>
+      <x:c r="I169" s="81"/>
+      <x:c r="J169" s="81"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="19" t="str">
+      <x:c r="A170" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B170" s="19" t="str">
+      <x:c r="B170" s="82" t="str">
         <x:v>HBD-GYM-0111</x:v>
       </x:c>
-      <x:c r="C170" s="19" t="str">
+      <x:c r="C170" s="82" t="str">
         <x:v>산본클라이밍센터</x:v>
       </x:c>
-      <x:c r="D170" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E170" s="19" t="str"/>
-      <x:c r="F170" s="19" t="str"/>
-      <x:c r="G170" s="19" t="str"/>
+      <x:c r="D170" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E170" s="82"/>
+      <x:c r="F170" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%82%B0%EB%B3%B8%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G170" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H170" s="81"/>
+      <x:c r="I170" s="81"/>
+      <x:c r="J170" s="81"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="19" t="str">
+      <x:c r="A171" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B171" s="19" t="str">
+      <x:c r="B171" s="82" t="str">
         <x:v>HBD-GYM-0112</x:v>
       </x:c>
-      <x:c r="C171" s="19" t="str">
+      <x:c r="C171" s="82" t="str">
         <x:v>스파이시 클라이밍</x:v>
       </x:c>
-      <x:c r="D171" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E171" s="19" t="str"/>
-      <x:c r="F171" s="19" t="str"/>
-      <x:c r="G171" s="19" t="str"/>
+      <x:c r="D171" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E171" s="82"/>
+      <x:c r="F171" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%8A%A4%ED%8C%8C%EC%9D%B4%EC%8B%9C%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G171" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H171" s="81"/>
+      <x:c r="I171" s="81"/>
+      <x:c r="J171" s="81"/>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="19" t="str">
+      <x:c r="A172" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B172" s="19" t="str">
+      <x:c r="B172" s="82" t="str">
         <x:v>HBD-GYM-0117</x:v>
       </x:c>
-      <x:c r="C172" s="19" t="str">
+      <x:c r="C172" s="82" t="str">
         <x:v>M2클라이밍 GYM</x:v>
       </x:c>
-      <x:c r="D172" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E172" s="19" t="str"/>
-      <x:c r="F172" s="19" t="str"/>
-      <x:c r="G172" s="19" t="str"/>
+      <x:c r="D172" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E172" s="82"/>
+      <x:c r="F172" s="82" t="str">
+        <x:v>https://www.sports.re.kr/pyxis-api/1/digital-files/98557431-1122-463f-80d5-f5575cc4ec15</x:v>
+      </x:c>
+      <x:c r="G172" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H172" s="81"/>
+      <x:c r="I172" s="81"/>
+      <x:c r="J172" s="81"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="19" t="str">
+      <x:c r="A173" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B173" s="19" t="str">
+      <x:c r="B173" s="82" t="str">
         <x:v>HBD-GYM-0118</x:v>
       </x:c>
-      <x:c r="C173" s="19" t="str">
+      <x:c r="C173" s="82" t="str">
         <x:v>다이노 클라이밍짐</x:v>
       </x:c>
-      <x:c r="D173" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E173" s="19" t="str"/>
-      <x:c r="F173" s="19" t="str"/>
-      <x:c r="G173" s="19" t="str"/>
+      <x:c r="D173" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E173" s="82"/>
+      <x:c r="F173" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%8B%A4%EC%9D%B4%EB%85%B8%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90</x:v>
+      </x:c>
+      <x:c r="G173" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H173" s="81"/>
+      <x:c r="I173" s="81"/>
+      <x:c r="J173" s="81"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="19" t="str">
+      <x:c r="A174" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B174" s="19" t="str">
+      <x:c r="B174" s="82" t="str">
         <x:v>HBD-GYM-0119</x:v>
       </x:c>
-      <x:c r="C174" s="19" t="str">
+      <x:c r="C174" s="82" t="str">
         <x:v>무브온</x:v>
       </x:c>
-      <x:c r="D174" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E174" s="19" t="str"/>
-      <x:c r="F174" s="19" t="str"/>
-      <x:c r="G174" s="19" t="str"/>
+      <x:c r="D174" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E174" s="82"/>
+      <x:c r="F174" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EB%AC%B4%EB%B8%8C%EC%98%A8</x:v>
+      </x:c>
+      <x:c r="G174" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H174" s="81"/>
+      <x:c r="I174" s="81"/>
+      <x:c r="J174" s="81"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="19" t="str">
+      <x:c r="A175" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B175" s="19" t="str">
+      <x:c r="B175" s="82" t="str">
         <x:v>HBD-GYM-0120</x:v>
       </x:c>
-      <x:c r="C175" s="19" t="str">
+      <x:c r="C175" s="82" t="str">
         <x:v>조규복클라이밍센터 금곡점</x:v>
       </x:c>
-      <x:c r="D175" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E175" s="19" t="str"/>
-      <x:c r="F175" s="19" t="str"/>
-      <x:c r="G175" s="19" t="str"/>
+      <x:c r="D175" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E175" s="82"/>
+      <x:c r="F175" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%A1%B0%EA%B7%9C%EB%B3%B5%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0%20%EA%B8%88%EA%B3%A1%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G175" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H175" s="81"/>
+      <x:c r="I175" s="81"/>
+      <x:c r="J175" s="81"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="19" t="str">
+      <x:c r="A176" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B176" s="19" t="str">
+      <x:c r="B176" s="82" t="str">
         <x:v>HBD-GYM-0121</x:v>
       </x:c>
-      <x:c r="C176" s="19" t="str">
+      <x:c r="C176" s="82" t="str">
         <x:v>퍼즐클라이밍</x:v>
       </x:c>
-      <x:c r="D176" s="19" t="str">
+      <x:c r="D176" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E176" s="19" t="str">
+      <x:c r="E176" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/UPbPduRF8j7ipTyB2rMwyLAi38wQorN--vHYbVqKol-awNKd_jGKuVySEds9xbJtXrqW6UnpvnFGQbd6X2hRIxg4Tl5nWjAjGkP5WULtraDswtui2DHRvlID7z7_QP6EVfnicMPlrOy-J3Sb60nav27Ll2od8W6BYtefp_pRiD-LFMPOV3VQXx40v8HPkcEY?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F176" s="19" t="str"/>
-      <x:c r="G176" s="19" t="str"/>
+      <x:c r="F176" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%8D%BC%EC%A6%90%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G176" s="82" t="str"/>
+      <x:c r="H176" s="81"/>
+      <x:c r="I176" s="81"/>
+      <x:c r="J176" s="81"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="19" t="str">
+      <x:c r="A177" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B177" s="19" t="str">
+      <x:c r="B177" s="82" t="str">
         <x:v>HBD-GYM-0154</x:v>
       </x:c>
-      <x:c r="C177" s="19" t="str">
+      <x:c r="C177" s="82" t="str">
         <x:v>안산 베이스캠프 클라이밍</x:v>
       </x:c>
-      <x:c r="D177" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E177" s="19" t="str"/>
-      <x:c r="F177" s="19" t="str"/>
-      <x:c r="G177" s="19" t="str"/>
+      <x:c r="D177" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E177" s="82"/>
+      <x:c r="F177" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%95%88%EC%82%B0%20%EB%B2%A0%EC%9D%B4%EC%8A%A4%EC%BA%A0%ED%94%84%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G177" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H177" s="81"/>
+      <x:c r="I177" s="81"/>
+      <x:c r="J177" s="81"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" s="19" t="str">
+      <x:c r="A178" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B178" s="19" t="str">
+      <x:c r="B178" s="82" t="str">
         <x:v>HBD-GYM-0155</x:v>
       </x:c>
-      <x:c r="C178" s="19" t="str">
+      <x:c r="C178" s="82" t="str">
         <x:v>안산 클라이밍</x:v>
       </x:c>
-      <x:c r="D178" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E178" s="19" t="str"/>
-      <x:c r="F178" s="19" t="str"/>
-      <x:c r="G178" s="19" t="str"/>
+      <x:c r="D178" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E178" s="82"/>
+      <x:c r="F178" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%95%88%EC%82%B0%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G178" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H178" s="81"/>
+      <x:c r="I178" s="81"/>
+      <x:c r="J178" s="81"/>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" s="19" t="str">
+      <x:c r="A179" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B179" s="19" t="str">
+      <x:c r="B179" s="82" t="str">
         <x:v>HBD-GYM-0156</x:v>
       </x:c>
-      <x:c r="C179" s="19" t="str">
+      <x:c r="C179" s="82" t="str">
         <x:v>클라이밍 트리클</x:v>
       </x:c>
-      <x:c r="D179" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E179" s="19" t="str"/>
-      <x:c r="F179" s="19" t="str"/>
-      <x:c r="G179" s="19" t="str"/>
+      <x:c r="D179" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E179" s="82"/>
+      <x:c r="F179" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%ED%8A%B8%EB%A6%AC%ED%81%B4</x:v>
+      </x:c>
+      <x:c r="G179" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H179" s="81"/>
+      <x:c r="I179" s="81"/>
+      <x:c r="J179" s="81"/>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="19" t="str">
+      <x:c r="A180" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B180" s="19" t="str">
+      <x:c r="B180" s="82" t="str">
         <x:v>HBD-GYM-0157</x:v>
       </x:c>
-      <x:c r="C180" s="19" t="str">
+      <x:c r="C180" s="82" t="str">
         <x:v>클럽클라이밍 안산</x:v>
       </x:c>
-      <x:c r="D180" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E180" s="19" t="str"/>
-      <x:c r="F180" s="19" t="str"/>
-      <x:c r="G180" s="19" t="str"/>
+      <x:c r="D180" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E180" s="82"/>
+      <x:c r="F180" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9F%BD%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EC%95%88%EC%82%B0</x:v>
+      </x:c>
+      <x:c r="G180" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H180" s="81"/>
+      <x:c r="I180" s="81"/>
+      <x:c r="J180" s="81"/>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="19" t="str">
+      <x:c r="A181" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B181" s="19" t="str">
+      <x:c r="B181" s="82" t="str">
         <x:v>HBD-GYM-0158</x:v>
       </x:c>
-      <x:c r="C181" s="19" t="str">
+      <x:c r="C181" s="82" t="str">
         <x:v>안성클라이밍센터</x:v>
       </x:c>
-      <x:c r="D181" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E181" s="19" t="str"/>
-      <x:c r="F181" s="19" t="str"/>
-      <x:c r="G181" s="19" t="str"/>
+      <x:c r="D181" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E181" s="82"/>
+      <x:c r="F181" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%95%88%EC%84%B1%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G181" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H181" s="81"/>
+      <x:c r="I181" s="81"/>
+      <x:c r="J181" s="81"/>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="19" t="str">
+      <x:c r="A182" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B182" s="19" t="str">
+      <x:c r="B182" s="82" t="str">
         <x:v>HBD-GYM-0159</x:v>
       </x:c>
-      <x:c r="C182" s="19" t="str">
+      <x:c r="C182" s="82" t="str">
         <x:v>원더월클라이밍</x:v>
       </x:c>
-      <x:c r="D182" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E182" s="19" t="str"/>
-      <x:c r="F182" s="19" t="str"/>
-      <x:c r="G182" s="19" t="str"/>
+      <x:c r="D182" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E182" s="82"/>
+      <x:c r="F182" s="82" t="str">
+        <x:v>https://place.udanax.org/p/3876531/%EC%9B%90%EB%8D%94%EC%9B%94%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G182" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H182" s="81"/>
+      <x:c r="I182" s="81"/>
+      <x:c r="J182" s="81"/>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="19" t="str">
+      <x:c r="A183" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B183" s="19" t="str">
+      <x:c r="B183" s="82" t="str">
         <x:v>HBD-GYM-0160</x:v>
       </x:c>
-      <x:c r="C183" s="19" t="str">
+      <x:c r="C183" s="82" t="str">
         <x:v>클라이밍 더 하기</x:v>
       </x:c>
-      <x:c r="D183" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E183" s="19" t="str"/>
-      <x:c r="F183" s="19" t="str"/>
-      <x:c r="G183" s="19" t="str"/>
+      <x:c r="D183" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E183" s="82"/>
+      <x:c r="F183" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%20%EB%8D%94%20%ED%95%98%EA%B8%B0</x:v>
+      </x:c>
+      <x:c r="G183" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H183" s="81"/>
+      <x:c r="I183" s="81"/>
+      <x:c r="J183" s="81"/>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="19" t="str">
+      <x:c r="A184" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B184" s="19" t="str">
+      <x:c r="B184" s="82" t="str">
         <x:v>HBD-GYM-0167</x:v>
       </x:c>
-      <x:c r="C184" s="19" t="str">
+      <x:c r="C184" s="82" t="str">
         <x:v>더바이브클라이밍</x:v>
       </x:c>
-      <x:c r="D184" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E184" s="19" t="str"/>
-      <x:c r="F184" s="19" t="str"/>
-      <x:c r="G184" s="19" t="str"/>
+      <x:c r="D184" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E184" s="82"/>
+      <x:c r="F184" s="82" t="str">
+        <x:v>https://climbmap.life/places/%EB%8D%94%EB%B0%94%EC%9D%B4%EB%B8%8C%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-723ce7d5</x:v>
+      </x:c>
+      <x:c r="G184" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H184" s="81"/>
+      <x:c r="I184" s="81"/>
+      <x:c r="J184" s="81"/>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="19" t="str">
+      <x:c r="A185" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B185" s="19" t="str">
+      <x:c r="B185" s="82" t="str">
         <x:v>HBD-GYM-0168</x:v>
       </x:c>
-      <x:c r="C185" s="19" t="str">
+      <x:c r="C185" s="82" t="str">
         <x:v>오산클라이밍</x:v>
       </x:c>
-      <x:c r="D185" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E185" s="19" t="str"/>
-      <x:c r="F185" s="19" t="str"/>
-      <x:c r="G185" s="19" t="str"/>
+      <x:c r="D185" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E185" s="82"/>
+      <x:c r="F185" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%98%A4%EC%82%B0%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G185" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H185" s="81"/>
+      <x:c r="I185" s="81"/>
+      <x:c r="J185" s="81"/>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="19" t="str">
+      <x:c r="A186" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B186" s="19" t="str">
+      <x:c r="B186" s="82" t="str">
         <x:v>HBD-GYM-0176</x:v>
       </x:c>
-      <x:c r="C186" s="19" t="str">
+      <x:c r="C186" s="82" t="str">
         <x:v>샤모니클라이밍</x:v>
       </x:c>
-      <x:c r="D186" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E186" s="19" t="str"/>
-      <x:c r="F186" s="19" t="str"/>
-      <x:c r="G186" s="19" t="str"/>
+      <x:c r="D186" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E186" s="82"/>
+      <x:c r="F186" s="82" t="str">
+        <x:v>https://climbmap.life/places/%EC%83%A4%EB%AA%A8%EB%8B%88%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D-bb9e188a</x:v>
+      </x:c>
+      <x:c r="G186" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H186" s="81"/>
+      <x:c r="I186" s="81"/>
+      <x:c r="J186" s="81"/>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="19" t="str">
+      <x:c r="A187" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B187" s="19" t="str">
+      <x:c r="B187" s="82" t="str">
         <x:v>HBD-GYM-0177</x:v>
       </x:c>
-      <x:c r="C187" s="19" t="str">
+      <x:c r="C187" s="82" t="str">
         <x:v>킹클라이밍</x:v>
       </x:c>
-      <x:c r="D187" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E187" s="19" t="str"/>
-      <x:c r="F187" s="19" t="str"/>
-      <x:c r="G187" s="19" t="str"/>
+      <x:c r="D187" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E187" s="82"/>
+      <x:c r="F187" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%82%B9%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G187" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H187" s="81"/>
+      <x:c r="I187" s="81"/>
+      <x:c r="J187" s="81"/>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="19" t="str">
+      <x:c r="A188" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B188" s="19" t="str">
+      <x:c r="B188" s="82" t="str">
         <x:v>HBD-GYM-0178</x:v>
       </x:c>
-      <x:c r="C188" s="19" t="str">
+      <x:c r="C188" s="82" t="str">
         <x:v>이천굿클라이밍</x:v>
       </x:c>
-      <x:c r="D188" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E188" s="19" t="str"/>
-      <x:c r="F188" s="19" t="str"/>
-      <x:c r="G188" s="19" t="str"/>
+      <x:c r="D188" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E188" s="82"/>
+      <x:c r="F188" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%9D%B4%EC%B2%9C%EA%B5%BF%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G188" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H188" s="81"/>
+      <x:c r="I188" s="81"/>
+      <x:c r="J188" s="81"/>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="19" t="str">
+      <x:c r="A189" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B189" s="19" t="str">
+      <x:c r="B189" s="82" t="str">
         <x:v>HBD-GYM-0179</x:v>
       </x:c>
-      <x:c r="C189" s="19" t="str">
+      <x:c r="C189" s="82" t="str">
         <x:v>클라임바운스 이천점</x:v>
       </x:c>
-      <x:c r="D189" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E189" s="19" t="str"/>
-      <x:c r="F189" s="19" t="str"/>
-      <x:c r="G189" s="19" t="str"/>
+      <x:c r="D189" s="82" t="str">
+        <x:v>확정후보</x:v>
+      </x:c>
+      <x:c r="E189" s="82" t="str">
+        <x:v>https://blog.kakaocdn.net/dna/kAGdq/btruAslQwwE/AAAAAAAAAAAAAAAAAAAAACUZf8jQaYnOqden97AJJ4P_O0XIrH9-wI2jAaml4_pI/img.jpg?allow_ip=&amp;allow_referer=&amp;credential=yqXZFxpELC7KVnFOS48ylbz2pIh7yKj8&amp;expires=1788188399&amp;signature=oYU3nYSlK93B7slEdqnaCTDMc%2Bc%3D</x:v>
+      </x:c>
+      <x:c r="F189" s="82" t="str">
+        <x:v>https://weareyoung0128.tistory.com/610</x:v>
+      </x:c>
+      <x:c r="G189" s="82" t="str">
+        <x:v>실방문 후기 · 클라임바운스 이천점 · 넓은 볼더링 내부 전경</x:v>
+      </x:c>
+      <x:c r="H189" s="81"/>
+      <x:c r="I189" s="81"/>
+      <x:c r="J189" s="81"/>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="19" t="str">
+      <x:c r="A190" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B190" s="19" t="str">
+      <x:c r="B190" s="82" t="str">
         <x:v>HBD-GYM-0180</x:v>
       </x:c>
-      <x:c r="C190" s="19" t="str">
+      <x:c r="C190" s="82" t="str">
         <x:v>클라임바운스 창전점</x:v>
       </x:c>
-      <x:c r="D190" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E190" s="19" t="str"/>
-      <x:c r="F190" s="19" t="str"/>
-      <x:c r="G190" s="19" t="str"/>
+      <x:c r="D190" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E190" s="82"/>
+      <x:c r="F190" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9E%84%EB%B0%94%EC%9A%B4%EC%8A%A4%20%EC%B0%BD%EC%A0%84%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G190" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H190" s="81"/>
+      <x:c r="I190" s="81"/>
+      <x:c r="J190" s="81"/>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="19" t="str">
+      <x:c r="A191" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B191" s="19" t="str">
+      <x:c r="B191" s="82" t="str">
         <x:v>HBD-GYM-0181</x:v>
       </x:c>
-      <x:c r="C191" s="19" t="str">
+      <x:c r="C191" s="82" t="str">
         <x:v>클라임원</x:v>
       </x:c>
-      <x:c r="D191" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E191" s="19" t="str"/>
-      <x:c r="F191" s="19" t="str"/>
-      <x:c r="G191" s="19" t="str"/>
+      <x:c r="D191" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E191" s="82"/>
+      <x:c r="F191" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9E%84%EC%9B%90</x:v>
+      </x:c>
+      <x:c r="G191" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H191" s="81"/>
+      <x:c r="I191" s="81"/>
+      <x:c r="J191" s="81"/>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="19" t="str">
+      <x:c r="A192" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B192" s="19" t="str">
+      <x:c r="B192" s="82" t="str">
         <x:v>HBD-GYM-0182</x:v>
       </x:c>
-      <x:c r="C192" s="19" t="str">
+      <x:c r="C192" s="82" t="str">
         <x:v>교하스포츠클라이밍짐</x:v>
       </x:c>
-      <x:c r="D192" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E192" s="19" t="str"/>
-      <x:c r="F192" s="19" t="str"/>
-      <x:c r="G192" s="19" t="str"/>
+      <x:c r="D192" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E192" s="82"/>
+      <x:c r="F192" s="82" t="str">
+        <x:v>https://www.sports.re.kr/pyxis-api/1/digital-files/98557431-1122-463f-80d5-f5575cc4ec15</x:v>
+      </x:c>
+      <x:c r="G192" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H192" s="81"/>
+      <x:c r="I192" s="81"/>
+      <x:c r="J192" s="81"/>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="19" t="str">
+      <x:c r="A193" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B193" s="19" t="str">
+      <x:c r="B193" s="82" t="str">
         <x:v>HBD-GYM-0183</x:v>
       </x:c>
-      <x:c r="C193" s="19" t="str">
+      <x:c r="C193" s="82" t="str">
         <x:v>애스트로맨 클라이밍센터</x:v>
       </x:c>
-      <x:c r="D193" s="19" t="str">
+      <x:c r="D193" s="82" t="str">
         <x:v>확정후보</x:v>
       </x:c>
-      <x:c r="E193" s="19" t="str">
+      <x:c r="E193" s="82" t="str">
         <x:v>https://images.openai.com/static-rsc-4/KgYaEZRajsFTTsrEiyi2_KnHLV8xPeHRaSxg3BR-MJ2T6SOOPFYm4XCogQR-KSkqJ-hUiF-w0pDQcJuf2-M-KFHvex6Tv-SaABbJPyQJoZQTqe7MR7TgEF42bSWoTVoLvyX2j2RDd7VDJc1L3ANtbE_UdWQWf8Vg63F9Fay3VGzPEJkgy4bg1vn5vZyevzF6?purpose=fullsize</x:v>
       </x:c>
-      <x:c r="F193" s="19" t="str"/>
-      <x:c r="G193" s="19" t="str"/>
+      <x:c r="F193" s="82" t="str">
+        <x:v>https://m.saramin.co.kr/job-search/company-info-view/csn/djBQc0VtUnp6ZkRjQVNIdU1acHZrdz09/company_nm/%EC%95%A0%EC%8A%A4%ED%8A%B8%EB%A1%9C%EB%A7%A8</x:v>
+      </x:c>
+      <x:c r="G193" s="82" t="str"/>
+      <x:c r="H193" s="81"/>
+      <x:c r="I193" s="81"/>
+      <x:c r="J193" s="81"/>
     </x:row>
     <x:row r="194">
-      <x:c r="A194" s="19" t="str">
+      <x:c r="A194" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B194" s="19" t="str">
+      <x:c r="B194" s="82" t="str">
         <x:v>HBD-GYM-0184</x:v>
       </x:c>
-      <x:c r="C194" s="19" t="str">
+      <x:c r="C194" s="82" t="str">
         <x:v>운정점핑클라이밍</x:v>
       </x:c>
-      <x:c r="D194" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E194" s="19" t="str"/>
-      <x:c r="F194" s="19" t="str"/>
-      <x:c r="G194" s="19" t="str"/>
+      <x:c r="D194" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E194" s="82"/>
+      <x:c r="F194" s="82" t="str">
+        <x:v>https://crux-climb.com/gyms/region/%ED%8C%8C%EC%A3%BC%EC%8B%9C</x:v>
+      </x:c>
+      <x:c r="G194" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H194" s="81"/>
+      <x:c r="I194" s="81"/>
+      <x:c r="J194" s="81"/>
     </x:row>
     <x:row r="195">
-      <x:c r="A195" s="19" t="str">
+      <x:c r="A195" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B195" s="19" t="str">
+      <x:c r="B195" s="82" t="str">
         <x:v>HBD-GYM-0185</x:v>
       </x:c>
-      <x:c r="C195" s="19" t="str">
+      <x:c r="C195" s="82" t="str">
         <x:v>정글짐 클라이밍센터</x:v>
       </x:c>
-      <x:c r="D195" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E195" s="19" t="str"/>
-      <x:c r="F195" s="19" t="str"/>
-      <x:c r="G195" s="19" t="str"/>
+      <x:c r="D195" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E195" s="82"/>
+      <x:c r="F195" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%EC%A0%95%EA%B8%80%EC%A7%90%20%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G195" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H195" s="81"/>
+      <x:c r="I195" s="81"/>
+      <x:c r="J195" s="81"/>
     </x:row>
     <x:row r="196">
-      <x:c r="A196" s="19" t="str">
+      <x:c r="A196" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B196" s="19" t="str">
+      <x:c r="B196" s="82" t="str">
         <x:v>HBD-GYM-0186</x:v>
       </x:c>
-      <x:c r="C196" s="19" t="str">
+      <x:c r="C196" s="82" t="str">
         <x:v>파주클라이밍센터</x:v>
       </x:c>
-      <x:c r="D196" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E196" s="19" t="str"/>
-      <x:c r="F196" s="19" t="str"/>
-      <x:c r="G196" s="19" t="str"/>
+      <x:c r="D196" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E196" s="82"/>
+      <x:c r="F196" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%8C%8C%EC%A3%BC%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%84%BC%ED%84%B0</x:v>
+      </x:c>
+      <x:c r="G196" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H196" s="81"/>
+      <x:c r="I196" s="81"/>
+      <x:c r="J196" s="81"/>
     </x:row>
     <x:row r="197">
-      <x:c r="A197" s="19" t="str">
+      <x:c r="A197" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B197" s="19" t="str">
+      <x:c r="B197" s="82" t="str">
         <x:v>HBD-GYM-0187</x:v>
       </x:c>
-      <x:c r="C197" s="19" t="str">
+      <x:c r="C197" s="82" t="str">
         <x:v>트윈클라이밍짐</x:v>
       </x:c>
-      <x:c r="D197" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E197" s="19" t="str"/>
-      <x:c r="F197" s="19" t="str"/>
-      <x:c r="G197" s="19" t="str"/>
+      <x:c r="D197" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E197" s="82"/>
+      <x:c r="F197" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%8A%B8%EC%9C%88%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90</x:v>
+      </x:c>
+      <x:c r="G197" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H197" s="81"/>
+      <x:c r="I197" s="81"/>
+      <x:c r="J197" s="81"/>
     </x:row>
     <x:row r="198">
-      <x:c r="A198" s="19" t="str">
+      <x:c r="A198" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B198" s="19" t="str">
+      <x:c r="B198" s="82" t="str">
         <x:v>HBD-GYM-0188</x:v>
       </x:c>
-      <x:c r="C198" s="19" t="str">
+      <x:c r="C198" s="82" t="str">
         <x:v>프리월클라이밍짐 평택지제점</x:v>
       </x:c>
-      <x:c r="D198" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E198" s="19" t="str"/>
-      <x:c r="F198" s="19" t="str"/>
-      <x:c r="G198" s="19" t="str"/>
+      <x:c r="D198" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E198" s="82"/>
+      <x:c r="F198" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%94%84%EB%A6%AC%EC%9B%94%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D%EC%A7%90%20%ED%8F%89%ED%83%9D%EC%A7%80%EC%A0%9C%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G198" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H198" s="81"/>
+      <x:c r="I198" s="81"/>
+      <x:c r="J198" s="81"/>
     </x:row>
     <x:row r="199">
-      <x:c r="A199" s="19" t="str">
+      <x:c r="A199" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B199" s="19" t="str">
+      <x:c r="B199" s="82" t="str">
         <x:v>HBD-GYM-0189</x:v>
       </x:c>
-      <x:c r="C199" s="19" t="str">
+      <x:c r="C199" s="82" t="str">
         <x:v>홍종열클라이밍짐 평택점</x:v>
       </x:c>
-      <x:c r="D199" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E199" s="19" t="str"/>
-      <x:c r="F199" s="19" t="str"/>
-      <x:c r="G199" s="19" t="str"/>
+      <x:c r="D199" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E199" s="82" t="str">
+        <x:v>https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEhlnWUkN8BTunVmO4akDZwG036Mj6sFqmF04Sos2AIUcofR6GOun4mHgF96qx1Bk6C6fF2UNhKseSmsaypEGMNlZPfo-oVD9igKVzZKEC54MV07VaqgwbWj2iwoP1SKFVeoeAJ5YAME1Cj8/s320/HJY%2BClimbing%2Bgym%2B%2528%25E1%2584%2592%25E1%2585%25A9%25E1%2586%25BC%25E1%2584%258C%25E1%2585%25A9%25E1%2586%25BC%25E1%2584%258B%25E1%2585%25A7%25E1%2586%25AF%25E1%2584%258F%25E1%2585%25B3%25E1%2586%25AF%25E1%2584%2585%25E1%2585%25A1%25E1%2584%258B%25E1%2585%25B5%25E1%2584%2586%25E1%2585%25B5%25E1%2586%25BC%25E1%2584%258C%25E1%2585%25B5%25E1%2586%25B7%2529.jpg</x:v>
+      </x:c>
+      <x:c r="F199" s="82" t="str">
+        <x:v>https://climbinginkorea.blogspot.com/2018/04/hjy-climbing-gym-pyeongtaek.html</x:v>
+      </x:c>
+      <x:c r="G199" s="82" t="str">
+        <x:v>홍종열클라이밍짐 평택점 지점 자료 · 로고형 이미지라 교체 권장</x:v>
+      </x:c>
+      <x:c r="H199" s="81"/>
+      <x:c r="I199" s="81"/>
+      <x:c r="J199" s="81"/>
     </x:row>
     <x:row r="200">
-      <x:c r="A200" s="19" t="str">
+      <x:c r="A200" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B200" s="19" t="str">
+      <x:c r="B200" s="82" t="str">
         <x:v>HBD-GYM-0190</x:v>
       </x:c>
-      <x:c r="C200" s="19" t="str">
+      <x:c r="C200" s="82" t="str">
         <x:v>힐앤토클라이밍</x:v>
       </x:c>
-      <x:c r="D200" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E200" s="19" t="str"/>
-      <x:c r="F200" s="19" t="str"/>
-      <x:c r="G200" s="19" t="str"/>
+      <x:c r="D200" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E200" s="82"/>
+      <x:c r="F200" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%9E%90%EC%95%A4%ED%86%A0%ED%81%B4%EB%9D%BC%EC%9D%B4%EB%B0%8D</x:v>
+      </x:c>
+      <x:c r="G200" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H200" s="81"/>
+      <x:c r="I200" s="81"/>
+      <x:c r="J200" s="81"/>
     </x:row>
     <x:row r="201">
-      <x:c r="A201" s="19" t="str">
+      <x:c r="A201" s="82" t="str">
         <x:v>P3</x:v>
       </x:c>
-      <x:c r="B201" s="19" t="str">
+      <x:c r="B201" s="82" t="str">
         <x:v>HBD-GYM-0191</x:v>
       </x:c>
-      <x:c r="C201" s="19" t="str">
+      <x:c r="C201" s="82" t="str">
         <x:v>클라임 어스 미사점</x:v>
       </x:c>
-      <x:c r="D201" s="19" t="str">
-        <x:v>미수집</x:v>
-      </x:c>
-      <x:c r="E201" s="19" t="str"/>
-      <x:c r="F201" s="19" t="str"/>
-      <x:c r="G201" s="19" t="str"/>
+      <x:c r="D201" s="82" t="str">
+        <x:v>임시</x:v>
+      </x:c>
+      <x:c r="E201" s="82"/>
+      <x:c r="F201" s="82" t="str">
+        <x:v>https://spiri7.com/gym/%ED%81%B4%EB%9D%BC%EC%9E%84%20%EC%96%B4%EC%8A%A4%20%EB%AF%B8%EC%82%AC%EC%A0%90</x:v>
+      </x:c>
+      <x:c r="G201" s="82" t="str">
+        <x:v>지점 출처 페이지 확보 · 대표사진 직접 URL 추가 검증 필요</x:v>
+      </x:c>
+      <x:c r="H201" s="81"/>
+      <x:c r="I201" s="81"/>
+      <x:c r="J201" s="81"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D2:D201">
-    <x:cfRule type="expression" dxfId="1" priority="1">
+    <x:cfRule type="expression" dxfId="4" priority="1">
       <x:formula>D2="확정후보"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="2" priority="2">
+    <x:cfRule type="expression" dxfId="5" priority="2">
+      <x:formula>D2="임시"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="6" priority="3">
       <x:formula>D2="운영재검증"</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="3" priority="3">
+    <x:cfRule type="expression" dxfId="7" priority="4">
       <x:formula>D2="미수집"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="D2:D201">
-      <x:formula1>"미수집,확정후보,임시,운영재검증"</x:formula1>
+      <x:formula1>"확정후보,임시,운영재검증,미수집"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
